--- a/Walking-Setup/G6-Integration-Bill-of-Materials.xlsx
+++ b/Walking-Setup/G6-Integration-Bill-of-Materials.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/lehenbaueri/Documents/GitHub/Fly-Lab-Gear/Walking-Setup/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{765A1A71-C1D7-F04C-97C0-42C3323331A3}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{2B84DA0F-7DE9-5B46-B031-2272896AF708}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="1640" yWindow="660" windowWidth="27460" windowHeight="18980" xr2:uid="{1DD35749-F480-5B49-A82C-F7D601ECF748}"/>
+    <workbookView xWindow="6460" yWindow="1600" windowWidth="27460" windowHeight="18980" xr2:uid="{1DD35749-F480-5B49-A82C-F7D601ECF748}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -39,7 +39,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="262" uniqueCount="127">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="283" uniqueCount="140">
   <si>
     <t>Part No.</t>
   </si>
@@ -119,9 +119,6 @@
     <t>Fly holder stand</t>
   </si>
   <si>
-    <t>3D Printed</t>
-  </si>
-  <si>
     <t>Camera</t>
   </si>
   <si>
@@ -233,9 +230,6 @@
     <t>3D printed</t>
   </si>
   <si>
-    <t>Heat ring</t>
-  </si>
-  <si>
     <t>Thermometer</t>
   </si>
   <si>
@@ -266,9 +260,6 @@
     <t xml:space="preserve">BNC (m) to screw terminals </t>
   </si>
   <si>
-    <t>optostim light rail holder</t>
-  </si>
-  <si>
     <t>90 deg rail slider</t>
   </si>
   <si>
@@ -278,12 +269,6 @@
     <t>LED lamp housing</t>
   </si>
   <si>
-    <t>LED</t>
-  </si>
-  <si>
-    <t>Optic</t>
-  </si>
-  <si>
     <t>Dynamic LED Housing All Thread Nipple</t>
   </si>
   <si>
@@ -320,15 +305,12 @@
     <t>Electrical</t>
   </si>
   <si>
-    <t>Barrel jack power cable (5V)</t>
-  </si>
-  <si>
-    <t>Micro USB to USB cable for computer connection</t>
-  </si>
-  <si>
     <t>Micromanipulator adapter plate</t>
   </si>
   <si>
+    <t>Laser cut</t>
+  </si>
+  <si>
     <t>#8-32 nuts</t>
   </si>
   <si>
@@ -395,15 +377,6 @@
     <t>S-mount Lens</t>
   </si>
   <si>
-    <t>Barrel jack power supply (12V, &gt;=2W)</t>
-  </si>
-  <si>
-    <t>BNC to screw terminals</t>
-  </si>
-  <si>
-    <t>Blunt Needle</t>
-  </si>
-  <si>
     <t>M2x0.4 screws, 10 mm</t>
   </si>
   <si>
@@ -420,6 +393,72 @@
   </si>
   <si>
     <t>91828A111</t>
+  </si>
+  <si>
+    <t>3D printed, resin</t>
+  </si>
+  <si>
+    <t>Electrical Box 12V</t>
+  </si>
+  <si>
+    <t>Note</t>
+  </si>
+  <si>
+    <t>M3x0.5 screws, 16 mm</t>
+  </si>
+  <si>
+    <t>M3x0.5 nut</t>
+  </si>
+  <si>
+    <t>https://www.mcmaster.com/91292A115/</t>
+  </si>
+  <si>
+    <t>91292A115</t>
+  </si>
+  <si>
+    <t>12V, &gt;2W power supply</t>
+  </si>
+  <si>
+    <t>Blunt Needle for Tethering</t>
+  </si>
+  <si>
+    <t>Optostim light rail holder</t>
+  </si>
+  <si>
+    <t>USB3 Micro B to USB cable</t>
+  </si>
+  <si>
+    <t>https://www.amazon.com/External-Seagate-Toshiba-Western-Passport/dp/B0F1N5W6VW/ref=sr_1_1_sspa</t>
+  </si>
+  <si>
+    <t>https://www.amazon.com/Smays-5-Pack-Micro-Transfer-Charging/dp/B0DZ6QRRHJ/ref=sr_1_2_sspa</t>
+  </si>
+  <si>
+    <t>Barrel jack power supply (5V, 10A)</t>
+  </si>
+  <si>
+    <t>Micro USB to USB cable</t>
+  </si>
+  <si>
+    <t>12" x 12" Acrylic sheet</t>
+  </si>
+  <si>
+    <t>8505K721</t>
+  </si>
+  <si>
+    <t>https://www.mcmaster.com/8505K721-8505K112/</t>
+  </si>
+  <si>
+    <t>70 mm circular heating pad</t>
+  </si>
+  <si>
+    <t>https://www.amazon.com/XIITIA-70mmx70mm-Adhesive-Elements-Polyimide/dp/B0D5DC9VWB/ref=sr_1_2?</t>
+  </si>
+  <si>
+    <t>Heating baseplate</t>
+  </si>
+  <si>
+    <t>12"x12" is enough for 2 laser cut boxes, or one box and the heating baseplate. Color choice up to the user</t>
   </si>
 </sst>
 </file>
@@ -554,9 +593,9 @@
 </file>
 
 <file path=xl/tables/table1.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="1" xr:uid="{031F9794-3422-E94F-8BF0-DD73732413E3}" name="Table1" displayName="Table1" ref="A10:J59" totalsRowShown="0">
-  <autoFilter ref="A10:J59" xr:uid="{031F9794-3422-E94F-8BF0-DD73732413E3}"/>
-  <tableColumns count="10">
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="1" xr:uid="{031F9794-3422-E94F-8BF0-DD73732413E3}" name="Table1" displayName="Table1" ref="A10:K62" totalsRowShown="0">
+  <autoFilter ref="A10:K62" xr:uid="{031F9794-3422-E94F-8BF0-DD73732413E3}"/>
+  <tableColumns count="11">
     <tableColumn id="1" xr3:uid="{B56D842A-6524-6042-A636-27D25523BBC2}" name="Category"/>
     <tableColumn id="9" xr3:uid="{A5067F63-B27C-2445-8796-A1DED8D638AE}" name="Subassembly"/>
     <tableColumn id="2" xr3:uid="{9DD3C2A2-C34C-7B4C-86FE-FB0DCD196ADD}" name="Part No." dataDxfId="2"/>
@@ -569,6 +608,7 @@
       <calculatedColumnFormula>Table1[[#This Row],[Qty]]*Table1[[#This Row],[Unit Cost]]</calculatedColumnFormula>
     </tableColumn>
     <tableColumn id="10" xr3:uid="{4704FBC5-16A6-2E46-8B58-60DFB166C669}" name="Link"/>
+    <tableColumn id="13" xr3:uid="{77349C88-CEAA-F945-9E95-011D61FC3D13}" name="Note"/>
   </tableColumns>
   <tableStyleInfo name="TableStyleLight2" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
 </table>
@@ -891,7 +931,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{53CCC03A-E2D2-064D-930B-8D8B4BDB230C}">
-  <dimension ref="A1:J59"/>
+  <dimension ref="A1:K62"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="16" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="22" customWidth="1"/>
@@ -902,30 +942,31 @@
     <col min="7" max="7" width="15.5" style="1" customWidth="1"/>
     <col min="8" max="8" width="12.6640625" style="1" bestFit="1" customWidth="1"/>
     <col min="10" max="10" width="45.5" customWidth="1"/>
+    <col min="11" max="11" width="47.5" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:10" x14ac:dyDescent="0.2">
+    <row r="1" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A1" s="2" t="s">
         <v>8</v>
       </c>
       <c r="B1" t="s">
-        <v>113</v>
-      </c>
-    </row>
-    <row r="2" spans="1:10" x14ac:dyDescent="0.2">
+        <v>107</v>
+      </c>
+    </row>
+    <row r="2" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A2" s="2" t="s">
         <v>9</v>
       </c>
     </row>
-    <row r="3" spans="1:10" x14ac:dyDescent="0.2">
+    <row r="3" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A3" s="2" t="s">
         <v>10</v>
       </c>
       <c r="B3">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="4" spans="1:10" x14ac:dyDescent="0.2">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="4" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A4" s="2" t="s">
         <v>14</v>
       </c>
@@ -933,30 +974,30 @@
         <v>15</v>
       </c>
     </row>
-    <row r="5" spans="1:10" x14ac:dyDescent="0.2">
+    <row r="5" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A5" s="2" t="s">
         <v>11</v>
       </c>
     </row>
-    <row r="6" spans="1:10" x14ac:dyDescent="0.2">
+    <row r="6" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A6" s="2" t="s">
         <v>12</v>
       </c>
       <c r="B6">
         <f>SUM(Table1[Qty])</f>
-        <v>89</v>
-      </c>
-    </row>
-    <row r="7" spans="1:10" x14ac:dyDescent="0.2">
+        <v>101.5</v>
+      </c>
+    </row>
+    <row r="7" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A7" s="2" t="s">
         <v>13</v>
       </c>
       <c r="B7" s="3">
         <f>SUM(Table1[Cost])</f>
-        <v>568.57519999999988</v>
-      </c>
-    </row>
-    <row r="10" spans="1:10" x14ac:dyDescent="0.2">
+        <v>583.59019999999987</v>
+      </c>
+    </row>
+    <row r="10" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A10" t="s">
         <v>3</v>
       </c>
@@ -987,10 +1028,13 @@
       <c r="J10" t="s">
         <v>22</v>
       </c>
-    </row>
-    <row r="11" spans="1:10" x14ac:dyDescent="0.2">
+      <c r="K10" t="s">
+        <v>120</v>
+      </c>
+    </row>
+    <row r="11" spans="1:11" x14ac:dyDescent="0.2">
       <c r="C11" s="5" t="s">
-        <v>51</v>
+        <v>50</v>
       </c>
       <c r="D11" t="s">
         <v>16</v>
@@ -1012,15 +1056,15 @@
         <v>184.47</v>
       </c>
       <c r="J11" s="4" t="s">
-        <v>50</v>
-      </c>
-    </row>
-    <row r="12" spans="1:10" x14ac:dyDescent="0.2">
+        <v>49</v>
+      </c>
+    </row>
+    <row r="12" spans="1:11" x14ac:dyDescent="0.2">
       <c r="B12" t="s">
-        <v>52</v>
+        <v>51</v>
       </c>
       <c r="D12" t="s">
-        <v>52</v>
+        <v>51</v>
       </c>
       <c r="F12">
         <v>1</v>
@@ -1033,18 +1077,18 @@
         <v>0</v>
       </c>
       <c r="J12" s="4" t="s">
-        <v>111</v>
-      </c>
-    </row>
-    <row r="13" spans="1:10" x14ac:dyDescent="0.2">
+        <v>105</v>
+      </c>
+    </row>
+    <row r="13" spans="1:11" x14ac:dyDescent="0.2">
       <c r="B13" t="s">
-        <v>52</v>
+        <v>51</v>
       </c>
       <c r="C13" s="5" t="s">
-        <v>58</v>
+        <v>57</v>
       </c>
       <c r="D13" t="s">
-        <v>56</v>
+        <v>55</v>
       </c>
       <c r="E13" t="s">
         <v>17</v>
@@ -1063,24 +1107,24 @@
         <v>23.04</v>
       </c>
       <c r="J13" s="4" t="s">
-        <v>57</v>
-      </c>
-    </row>
-    <row r="14" spans="1:10" x14ac:dyDescent="0.2">
+        <v>56</v>
+      </c>
+    </row>
+    <row r="14" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A14" t="s">
         <v>20</v>
       </c>
       <c r="B14" t="s">
-        <v>52</v>
+        <v>51</v>
       </c>
       <c r="C14" s="5" t="s">
-        <v>108</v>
+        <v>102</v>
       </c>
       <c r="D14" t="s">
-        <v>107</v>
+        <v>101</v>
       </c>
       <c r="E14" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="F14">
         <v>4</v>
@@ -1097,24 +1141,24 @@
         <v>0.5776</v>
       </c>
       <c r="J14" s="4" t="s">
-        <v>109</v>
-      </c>
-    </row>
-    <row r="15" spans="1:10" x14ac:dyDescent="0.2">
+        <v>103</v>
+      </c>
+    </row>
+    <row r="15" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A15" t="s">
         <v>20</v>
       </c>
       <c r="B15" t="s">
-        <v>52</v>
+        <v>51</v>
       </c>
       <c r="C15" s="5" t="s">
-        <v>100</v>
+        <v>94</v>
       </c>
       <c r="D15" t="s">
-        <v>96</v>
+        <v>90</v>
       </c>
       <c r="E15" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="F15">
         <v>8</v>
@@ -1131,27 +1175,27 @@
         <v>0.16159999999999999</v>
       </c>
       <c r="J15" s="4" t="s">
-        <v>59</v>
-      </c>
-    </row>
-    <row r="16" spans="1:10" x14ac:dyDescent="0.2">
+        <v>58</v>
+      </c>
+    </row>
+    <row r="16" spans="1:11" x14ac:dyDescent="0.2">
       <c r="B16" t="s">
-        <v>52</v>
+        <v>51</v>
       </c>
       <c r="C16" s="5" t="s">
+        <v>60</v>
+      </c>
+      <c r="D16" t="s">
         <v>61</v>
       </c>
-      <c r="D16" t="s">
+      <c r="E16" t="s">
         <v>62</v>
-      </c>
-      <c r="E16" t="s">
-        <v>63</v>
       </c>
       <c r="F16">
         <v>4</v>
       </c>
       <c r="G16" t="s">
-        <v>36</v>
+        <v>35</v>
       </c>
       <c r="I16" s="1">
         <f>Table1[[#This Row],[Qty]]*Table1[[#This Row],[Unit Cost]]</f>
@@ -1161,13 +1205,13 @@
     </row>
     <row r="17" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A17" t="s">
-        <v>92</v>
+        <v>87</v>
       </c>
       <c r="B17" t="s">
-        <v>52</v>
+        <v>51</v>
       </c>
       <c r="D17" t="s">
-        <v>93</v>
+        <v>131</v>
       </c>
       <c r="F17">
         <v>1</v>
@@ -1183,13 +1227,13 @@
     </row>
     <row r="18" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A18" t="s">
-        <v>92</v>
+        <v>87</v>
       </c>
       <c r="B18" t="s">
-        <v>52</v>
+        <v>51</v>
       </c>
       <c r="D18" t="s">
-        <v>94</v>
+        <v>132</v>
       </c>
       <c r="F18">
         <v>1</v>
@@ -1197,11 +1241,16 @@
       <c r="G18" t="s">
         <v>21</v>
       </c>
+      <c r="H18" s="1">
+        <v>4.5</v>
+      </c>
       <c r="I18" s="1">
         <f>Table1[[#This Row],[Qty]]*Table1[[#This Row],[Unit Cost]]</f>
-        <v>0</v>
-      </c>
-      <c r="J18" s="4"/>
+        <v>4.5</v>
+      </c>
+      <c r="J18" s="4" t="s">
+        <v>130</v>
+      </c>
     </row>
     <row r="19" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A19" t="s">
@@ -1211,13 +1260,13 @@
         <v>19</v>
       </c>
       <c r="C19" s="5" t="s">
-        <v>97</v>
+        <v>91</v>
       </c>
       <c r="D19" t="s">
-        <v>98</v>
+        <v>92</v>
       </c>
       <c r="E19" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="F19">
         <v>4</v>
@@ -1234,7 +1283,7 @@
         <v>2.2208000000000001</v>
       </c>
       <c r="J19" s="4" t="s">
-        <v>99</v>
+        <v>93</v>
       </c>
     </row>
     <row r="20" spans="1:10" x14ac:dyDescent="0.2">
@@ -1245,13 +1294,13 @@
         <v>19</v>
       </c>
       <c r="C20" s="5" t="s">
-        <v>100</v>
+        <v>94</v>
       </c>
       <c r="D20" t="s">
-        <v>96</v>
+        <v>90</v>
       </c>
       <c r="E20" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="F20">
         <v>4</v>
@@ -1267,7 +1316,7 @@
         <v>0.08</v>
       </c>
       <c r="J20" s="6" t="s">
-        <v>59</v>
+        <v>58</v>
       </c>
     </row>
     <row r="21" spans="1:10" x14ac:dyDescent="0.2">
@@ -1275,16 +1324,16 @@
         <v>20</v>
       </c>
       <c r="B21" t="s">
-        <v>52</v>
+        <v>51</v>
       </c>
       <c r="C21" s="5" t="s">
-        <v>102</v>
+        <v>96</v>
       </c>
       <c r="D21" t="s">
-        <v>101</v>
+        <v>95</v>
       </c>
       <c r="E21" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="F21">
         <v>4</v>
@@ -1301,7 +1350,7 @@
         <v>0.59319999999999995</v>
       </c>
       <c r="J21" s="4" t="s">
-        <v>103</v>
+        <v>97</v>
       </c>
     </row>
     <row r="22" spans="1:10" x14ac:dyDescent="0.2">
@@ -1309,13 +1358,13 @@
         <v>19</v>
       </c>
       <c r="C22" s="5" t="s">
-        <v>104</v>
+        <v>98</v>
       </c>
       <c r="D22" t="s">
-        <v>105</v>
+        <v>99</v>
       </c>
       <c r="E22" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="F22">
         <v>1</v>
@@ -1331,7 +1380,7 @@
         <v>2.89</v>
       </c>
       <c r="J22" s="4" t="s">
-        <v>106</v>
+        <v>100</v>
       </c>
     </row>
     <row r="23" spans="1:10" x14ac:dyDescent="0.2">
@@ -1339,10 +1388,10 @@
         <v>19</v>
       </c>
       <c r="D23" t="s">
-        <v>75</v>
+        <v>127</v>
       </c>
       <c r="E23" t="s">
-        <v>63</v>
+        <v>62</v>
       </c>
       <c r="F23">
         <v>2</v>
@@ -1361,10 +1410,10 @@
         <v>19</v>
       </c>
       <c r="D24" t="s">
-        <v>76</v>
+        <v>73</v>
       </c>
       <c r="E24" t="s">
-        <v>63</v>
+        <v>62</v>
       </c>
       <c r="F24">
         <v>1</v>
@@ -1383,10 +1432,10 @@
         <v>19</v>
       </c>
       <c r="D25" t="s">
-        <v>88</v>
+        <v>83</v>
       </c>
       <c r="E25" t="s">
-        <v>63</v>
+        <v>62</v>
       </c>
       <c r="F25">
         <v>1</v>
@@ -1402,13 +1451,13 @@
     </row>
     <row r="26" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A26" t="s">
-        <v>92</v>
+        <v>87</v>
       </c>
       <c r="B26" t="s">
         <v>19</v>
       </c>
       <c r="D26" t="s">
-        <v>112</v>
+        <v>106</v>
       </c>
       <c r="F26">
         <v>1</v>
@@ -1419,13 +1468,13 @@
     </row>
     <row r="27" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A27" t="s">
-        <v>92</v>
+        <v>87</v>
       </c>
       <c r="B27" t="s">
         <v>19</v>
       </c>
       <c r="D27" t="s">
-        <v>74</v>
+        <v>72</v>
       </c>
       <c r="F27">
         <v>1</v>
@@ -1436,13 +1485,13 @@
     </row>
     <row r="28" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A28" t="s">
-        <v>92</v>
+        <v>87</v>
       </c>
       <c r="B28" t="s">
         <v>19</v>
       </c>
       <c r="D28" t="s">
-        <v>73</v>
+        <v>71</v>
       </c>
       <c r="F28">
         <v>1</v>
@@ -1458,13 +1507,13 @@
         <v>19</v>
       </c>
       <c r="C29" s="5" t="s">
-        <v>83</v>
+        <v>78</v>
       </c>
       <c r="D29" t="s">
-        <v>78</v>
+        <v>75</v>
       </c>
       <c r="E29" t="s">
-        <v>71</v>
+        <v>69</v>
       </c>
       <c r="F29">
         <v>1</v>
@@ -1480,24 +1529,21 @@
         <v>11.34</v>
       </c>
       <c r="J29" s="4" t="s">
-        <v>77</v>
+        <v>74</v>
       </c>
     </row>
     <row r="30" spans="1:10" x14ac:dyDescent="0.2">
-      <c r="A30" t="s">
-        <v>79</v>
-      </c>
       <c r="B30" t="s">
         <v>19</v>
       </c>
       <c r="C30" s="5" t="s">
-        <v>87</v>
+        <v>82</v>
       </c>
       <c r="D30" t="s">
-        <v>86</v>
+        <v>81</v>
       </c>
       <c r="E30" t="s">
-        <v>71</v>
+        <v>69</v>
       </c>
       <c r="F30">
         <v>1</v>
@@ -1514,9 +1560,6 @@
       </c>
     </row>
     <row r="31" spans="1:10" x14ac:dyDescent="0.2">
-      <c r="A31" t="s">
-        <v>80</v>
-      </c>
       <c r="B31" t="s">
         <v>19</v>
       </c>
@@ -1524,10 +1567,10 @@
         <v>10193</v>
       </c>
       <c r="D31" t="s">
-        <v>84</v>
+        <v>79</v>
       </c>
       <c r="E31" t="s">
-        <v>71</v>
+        <v>69</v>
       </c>
       <c r="F31">
         <v>1</v>
@@ -1551,13 +1594,13 @@
         <v>19</v>
       </c>
       <c r="C32" s="5" t="s">
-        <v>82</v>
+        <v>77</v>
       </c>
       <c r="D32" t="s">
-        <v>81</v>
+        <v>76</v>
       </c>
       <c r="E32" t="s">
-        <v>71</v>
+        <v>69</v>
       </c>
       <c r="F32">
         <v>1</v>
@@ -1575,19 +1618,19 @@
     </row>
     <row r="33" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A33" t="s">
-        <v>92</v>
+        <v>87</v>
       </c>
       <c r="B33" t="s">
         <v>19</v>
       </c>
       <c r="C33" s="5" t="s">
-        <v>85</v>
+        <v>80</v>
       </c>
       <c r="D33" t="s">
-        <v>72</v>
+        <v>70</v>
       </c>
       <c r="E33" t="s">
-        <v>71</v>
+        <v>69</v>
       </c>
       <c r="F33">
         <v>1</v>
@@ -1605,19 +1648,19 @@
     </row>
     <row r="34" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A34" t="s">
-        <v>92</v>
+        <v>87</v>
       </c>
       <c r="B34" t="s">
         <v>19</v>
       </c>
       <c r="C34" s="5" t="s">
-        <v>90</v>
+        <v>85</v>
       </c>
       <c r="D34" t="s">
-        <v>89</v>
+        <v>84</v>
       </c>
       <c r="E34" t="s">
-        <v>71</v>
+        <v>69</v>
       </c>
       <c r="F34">
         <v>1</v>
@@ -1635,13 +1678,13 @@
     </row>
     <row r="35" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A35" t="s">
-        <v>92</v>
+        <v>87</v>
       </c>
       <c r="B35" t="s">
         <v>19</v>
       </c>
       <c r="D35" t="s">
-        <v>70</v>
+        <v>68</v>
       </c>
       <c r="F35">
         <v>1</v>
@@ -1655,14 +1698,11 @@
       </c>
     </row>
     <row r="36" spans="1:10" x14ac:dyDescent="0.2">
-      <c r="A36" t="s">
-        <v>92</v>
-      </c>
       <c r="B36" t="s">
-        <v>19</v>
+        <v>23</v>
       </c>
       <c r="D36" t="s">
-        <v>118</v>
+        <v>24</v>
       </c>
       <c r="F36">
         <v>1</v>
@@ -1670,20 +1710,23 @@
       <c r="G36" t="s">
         <v>21</v>
       </c>
+      <c r="H36" s="1">
+        <v>80</v>
+      </c>
       <c r="I36" s="1">
         <f>Table1[[#This Row],[Qty]]*Table1[[#This Row],[Unit Cost]]</f>
-        <v>0</v>
+        <v>80</v>
       </c>
     </row>
     <row r="37" spans="1:10" x14ac:dyDescent="0.2">
-      <c r="A37" t="s">
-        <v>92</v>
-      </c>
       <c r="B37" t="s">
-        <v>19</v>
+        <v>23</v>
       </c>
       <c r="D37" t="s">
-        <v>119</v>
+        <v>88</v>
+      </c>
+      <c r="E37" t="s">
+        <v>62</v>
       </c>
       <c r="F37">
         <v>1</v>
@@ -1701,20 +1744,20 @@
         <v>23</v>
       </c>
       <c r="D38" t="s">
-        <v>24</v>
+        <v>25</v>
+      </c>
+      <c r="E38" t="s">
+        <v>62</v>
       </c>
       <c r="F38">
         <v>1</v>
       </c>
       <c r="G38" t="s">
-        <v>21</v>
-      </c>
-      <c r="H38" s="1">
-        <v>80</v>
+        <v>35</v>
       </c>
       <c r="I38" s="1">
         <f>Table1[[#This Row],[Qty]]*Table1[[#This Row],[Unit Cost]]</f>
-        <v>80</v>
+        <v>0</v>
       </c>
     </row>
     <row r="39" spans="1:10" x14ac:dyDescent="0.2">
@@ -1722,16 +1765,16 @@
         <v>23</v>
       </c>
       <c r="D39" t="s">
-        <v>95</v>
+        <v>86</v>
       </c>
       <c r="E39" t="s">
-        <v>63</v>
+        <v>62</v>
       </c>
       <c r="F39">
         <v>1</v>
       </c>
       <c r="G39" t="s">
-        <v>21</v>
+        <v>35</v>
       </c>
       <c r="I39" s="1">
         <f>Table1[[#This Row],[Qty]]*Table1[[#This Row],[Unit Cost]]</f>
@@ -1739,20 +1782,17 @@
       </c>
     </row>
     <row r="40" spans="1:10" x14ac:dyDescent="0.2">
-      <c r="A40" t="s">
-        <v>26</v>
-      </c>
       <c r="B40" t="s">
         <v>23</v>
       </c>
       <c r="D40" t="s">
-        <v>25</v>
+        <v>126</v>
       </c>
       <c r="F40">
         <v>1</v>
       </c>
       <c r="G40" t="s">
-        <v>36</v>
+        <v>21</v>
       </c>
       <c r="I40" s="1">
         <f>Table1[[#This Row],[Qty]]*Table1[[#This Row],[Unit Cost]]</f>
@@ -1761,31 +1801,53 @@
     </row>
     <row r="41" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A41" t="s">
-        <v>26</v>
+        <v>20</v>
       </c>
       <c r="B41" t="s">
         <v>23</v>
       </c>
+      <c r="C41" s="5" t="s">
+        <v>44</v>
+      </c>
       <c r="D41" t="s">
-        <v>91</v>
+        <v>39</v>
+      </c>
+      <c r="E41" t="s">
+        <v>32</v>
       </c>
       <c r="F41">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="G41" t="s">
-        <v>36</v>
+        <v>21</v>
+      </c>
+      <c r="H41" s="1">
+        <f>17.78/100</f>
+        <v>0.17780000000000001</v>
       </c>
       <c r="I41" s="1">
         <f>Table1[[#This Row],[Qty]]*Table1[[#This Row],[Unit Cost]]</f>
-        <v>0</v>
+        <v>0.88900000000000001</v>
+      </c>
+      <c r="J41" s="4" t="s">
+        <v>38</v>
       </c>
     </row>
     <row r="42" spans="1:10" x14ac:dyDescent="0.2">
+      <c r="A42" t="s">
+        <v>20</v>
+      </c>
       <c r="B42" t="s">
         <v>23</v>
       </c>
+      <c r="C42" s="5" t="s">
+        <v>46</v>
+      </c>
       <c r="D42" t="s">
-        <v>120</v>
+        <v>40</v>
+      </c>
+      <c r="E42" t="s">
+        <v>32</v>
       </c>
       <c r="F42">
         <v>1</v>
@@ -1793,456 +1855,542 @@
       <c r="G42" t="s">
         <v>21</v>
       </c>
+      <c r="H42" s="1">
+        <f>3.06/100</f>
+        <v>3.0600000000000002E-2</v>
+      </c>
       <c r="I42" s="1">
         <f>Table1[[#This Row],[Qty]]*Table1[[#This Row],[Unit Cost]]</f>
-        <v>0</v>
+        <v>3.0600000000000002E-2</v>
+      </c>
+      <c r="J42" s="4" t="s">
+        <v>45</v>
       </c>
     </row>
     <row r="43" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A43" t="s">
+        <v>26</v>
+      </c>
+      <c r="B43" t="s">
+        <v>26</v>
+      </c>
+      <c r="C43" s="5" t="s">
+        <v>29</v>
+      </c>
+      <c r="D43" t="s">
+        <v>30</v>
+      </c>
+      <c r="E43" t="s">
+        <v>28</v>
+      </c>
+      <c r="F43">
+        <v>1</v>
+      </c>
+      <c r="G43" s="1" t="s">
+        <v>21</v>
+      </c>
+      <c r="H43" s="1">
+        <v>229</v>
+      </c>
+      <c r="I43" s="1">
+        <f>Table1[[#This Row],[Qty]]*Table1[[#This Row],[Unit Cost]]</f>
+        <v>229</v>
+      </c>
+      <c r="J43" s="4" t="s">
+        <v>59</v>
+      </c>
+    </row>
+    <row r="44" spans="1:10" x14ac:dyDescent="0.2">
+      <c r="B44" t="s">
+        <v>26</v>
+      </c>
+      <c r="D44" t="s">
+        <v>111</v>
+      </c>
+      <c r="I44" s="1">
+        <f>Table1[[#This Row],[Qty]]*Table1[[#This Row],[Unit Cost]]</f>
+        <v>0</v>
+      </c>
+      <c r="J44" s="4"/>
+    </row>
+    <row r="45" spans="1:10" x14ac:dyDescent="0.2">
+      <c r="A45" t="s">
         <v>20</v>
       </c>
-      <c r="B43" t="s">
-        <v>23</v>
-      </c>
-      <c r="C43" s="5" t="s">
-        <v>45</v>
-      </c>
-      <c r="D43" t="s">
-        <v>40</v>
-      </c>
-      <c r="E43" t="s">
+      <c r="B45" t="s">
+        <v>26</v>
+      </c>
+      <c r="C45" s="5" t="s">
+        <v>43</v>
+      </c>
+      <c r="D45" t="s">
+        <v>34</v>
+      </c>
+      <c r="E45" t="s">
+        <v>32</v>
+      </c>
+      <c r="F45">
+        <v>6</v>
+      </c>
+      <c r="G45" s="1" t="s">
+        <v>21</v>
+      </c>
+      <c r="H45" s="1">
+        <f>17.63/100</f>
+        <v>0.17629999999999998</v>
+      </c>
+      <c r="I45" s="1">
+        <f>Table1[[#This Row],[Qty]]*Table1[[#This Row],[Unit Cost]]</f>
+        <v>1.0577999999999999</v>
+      </c>
+      <c r="J45" s="4" t="s">
+        <v>41</v>
+      </c>
+    </row>
+    <row r="46" spans="1:10" x14ac:dyDescent="0.2">
+      <c r="A46" t="s">
+        <v>20</v>
+      </c>
+      <c r="B46" t="s">
+        <v>26</v>
+      </c>
+      <c r="C46" s="5" t="s">
+        <v>48</v>
+      </c>
+      <c r="D46" t="s">
+        <v>42</v>
+      </c>
+      <c r="E46" t="s">
+        <v>32</v>
+      </c>
+      <c r="F46">
+        <v>6</v>
+      </c>
+      <c r="G46" s="1" t="s">
+        <v>21</v>
+      </c>
+      <c r="H46" s="1">
+        <f>3/100</f>
+        <v>0.03</v>
+      </c>
+      <c r="I46" s="1">
+        <f>Table1[[#This Row],[Qty]]*Table1[[#This Row],[Unit Cost]]</f>
+        <v>0.18</v>
+      </c>
+      <c r="J46" s="4" t="s">
+        <v>47</v>
+      </c>
+    </row>
+    <row r="47" spans="1:10" x14ac:dyDescent="0.2">
+      <c r="B47" t="s">
+        <v>26</v>
+      </c>
+      <c r="D47" t="s">
+        <v>128</v>
+      </c>
+      <c r="I47" s="1">
+        <f>Table1[[#This Row],[Qty]]*Table1[[#This Row],[Unit Cost]]</f>
+        <v>0</v>
+      </c>
+      <c r="J47" s="4"/>
+    </row>
+    <row r="48" spans="1:10" x14ac:dyDescent="0.2">
+      <c r="A48" t="s">
+        <v>87</v>
+      </c>
+      <c r="B48" t="s">
+        <v>27</v>
+      </c>
+      <c r="D48" t="s">
         <v>33</v>
       </c>
-      <c r="F43">
+      <c r="E48" t="s">
+        <v>118</v>
+      </c>
+      <c r="F48">
+        <v>1</v>
+      </c>
+      <c r="G48" s="1" t="s">
+        <v>21</v>
+      </c>
+      <c r="H48" s="1">
         <v>5</v>
       </c>
-      <c r="G43" t="s">
-        <v>21</v>
-      </c>
-      <c r="H43" s="1">
-        <f>17.78/100</f>
-        <v>0.17780000000000001</v>
-      </c>
-      <c r="I43" s="1">
-        <f>Table1[[#This Row],[Qty]]*Table1[[#This Row],[Unit Cost]]</f>
-        <v>0.88900000000000001</v>
-      </c>
-      <c r="J43" s="4" t="s">
-        <v>39</v>
-      </c>
-    </row>
-    <row r="44" spans="1:10" x14ac:dyDescent="0.2">
-      <c r="A44" t="s">
+      <c r="I48" s="1">
+        <f>Table1[[#This Row],[Qty]]*Table1[[#This Row],[Unit Cost]]</f>
+        <v>5</v>
+      </c>
+      <c r="J48" s="4" t="s">
+        <v>129</v>
+      </c>
+    </row>
+    <row r="49" spans="1:11" x14ac:dyDescent="0.2">
+      <c r="A49" t="s">
         <v>20</v>
       </c>
-      <c r="B44" t="s">
-        <v>23</v>
-      </c>
-      <c r="C44" s="5" t="s">
-        <v>47</v>
-      </c>
-      <c r="D44" t="s">
-        <v>41</v>
-      </c>
-      <c r="E44" t="s">
-        <v>33</v>
-      </c>
-      <c r="F44">
-        <v>1</v>
-      </c>
-      <c r="G44" t="s">
-        <v>21</v>
-      </c>
-      <c r="H44" s="1">
+      <c r="B49" t="s">
+        <v>27</v>
+      </c>
+      <c r="D49" t="s">
+        <v>31</v>
+      </c>
+      <c r="E49" t="s">
+        <v>32</v>
+      </c>
+      <c r="F49">
+        <v>2</v>
+      </c>
+      <c r="H49" s="1">
+        <f>11.38/50</f>
+        <v>0.22760000000000002</v>
+      </c>
+      <c r="I49" s="1">
+        <f>Table1[[#This Row],[Qty]]*Table1[[#This Row],[Unit Cost]]</f>
+        <v>0.45520000000000005</v>
+      </c>
+      <c r="J49" s="4" t="s">
+        <v>37</v>
+      </c>
+    </row>
+    <row r="50" spans="1:11" x14ac:dyDescent="0.2">
+      <c r="B50" t="s">
+        <v>27</v>
+      </c>
+      <c r="D50" t="s">
+        <v>52</v>
+      </c>
+      <c r="E50" t="s">
+        <v>53</v>
+      </c>
+      <c r="F50">
+        <v>1</v>
+      </c>
+      <c r="G50" s="1" t="s">
+        <v>21</v>
+      </c>
+      <c r="I50" s="1">
+        <f>Table1[[#This Row],[Qty]]*Table1[[#This Row],[Unit Cost]]</f>
+        <v>0</v>
+      </c>
+      <c r="J50" s="4" t="s">
+        <v>54</v>
+      </c>
+    </row>
+    <row r="51" spans="1:11" x14ac:dyDescent="0.2">
+      <c r="B51" t="s">
+        <v>27</v>
+      </c>
+      <c r="D51" t="s">
+        <v>104</v>
+      </c>
+      <c r="F51">
+        <v>1</v>
+      </c>
+      <c r="G51" s="1" t="s">
+        <v>21</v>
+      </c>
+      <c r="I51" s="1">
+        <f>Table1[[#This Row],[Qty]]*Table1[[#This Row],[Unit Cost]]</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="52" spans="1:11" x14ac:dyDescent="0.2">
+      <c r="A52" t="s">
+        <v>20</v>
+      </c>
+      <c r="B52" t="s">
+        <v>27</v>
+      </c>
+      <c r="C52" s="5" t="s">
+        <v>114</v>
+      </c>
+      <c r="D52" t="s">
+        <v>112</v>
+      </c>
+      <c r="E52" t="s">
+        <v>32</v>
+      </c>
+      <c r="F52">
+        <v>3</v>
+      </c>
+      <c r="G52" s="1" t="s">
+        <v>21</v>
+      </c>
+      <c r="H52" s="1">
+        <f>7.57/100</f>
+        <v>7.5700000000000003E-2</v>
+      </c>
+      <c r="I52" s="1">
+        <f>Table1[[#This Row],[Qty]]*Table1[[#This Row],[Unit Cost]]</f>
+        <v>0.22710000000000002</v>
+      </c>
+      <c r="J52" t="s">
+        <v>115</v>
+      </c>
+    </row>
+    <row r="53" spans="1:11" x14ac:dyDescent="0.2">
+      <c r="A53" t="s">
+        <v>20</v>
+      </c>
+      <c r="B53" t="s">
+        <v>27</v>
+      </c>
+      <c r="C53" s="5" t="s">
+        <v>117</v>
+      </c>
+      <c r="D53" t="s">
+        <v>113</v>
+      </c>
+      <c r="E53" t="s">
+        <v>32</v>
+      </c>
+      <c r="F53">
+        <v>3</v>
+      </c>
+      <c r="G53" s="1" t="s">
+        <v>21</v>
+      </c>
+      <c r="H53" s="1">
+        <f>7.41/100</f>
+        <v>7.4099999999999999E-2</v>
+      </c>
+      <c r="I53" s="1">
+        <f>Table1[[#This Row],[Qty]]*Table1[[#This Row],[Unit Cost]]</f>
+        <v>0.2223</v>
+      </c>
+      <c r="J53" s="4" t="s">
+        <v>116</v>
+      </c>
+    </row>
+    <row r="54" spans="1:11" x14ac:dyDescent="0.2">
+      <c r="B54" t="s">
+        <v>66</v>
+      </c>
+      <c r="D54" t="s">
+        <v>136</v>
+      </c>
+      <c r="I54" s="1">
+        <f>Table1[[#This Row],[Qty]]*Table1[[#This Row],[Unit Cost]]</f>
+        <v>0</v>
+      </c>
+      <c r="J54" t="s">
+        <v>137</v>
+      </c>
+    </row>
+    <row r="55" spans="1:11" x14ac:dyDescent="0.2">
+      <c r="B55" t="s">
+        <v>66</v>
+      </c>
+      <c r="D55" t="s">
+        <v>138</v>
+      </c>
+      <c r="F55">
+        <v>1</v>
+      </c>
+      <c r="I55" s="1">
+        <f>Table1[[#This Row],[Qty]]*Table1[[#This Row],[Unit Cost]]</f>
+        <v>0</v>
+      </c>
+      <c r="K55" t="s">
+        <v>89</v>
+      </c>
+    </row>
+    <row r="56" spans="1:11" x14ac:dyDescent="0.2">
+      <c r="B56" t="s">
+        <v>66</v>
+      </c>
+      <c r="C56" s="5" t="s">
+        <v>64</v>
+      </c>
+      <c r="D56" t="s">
+        <v>63</v>
+      </c>
+      <c r="E56" t="s">
+        <v>36</v>
+      </c>
+      <c r="F56">
+        <v>1</v>
+      </c>
+      <c r="G56" s="1" t="s">
+        <v>21</v>
+      </c>
+      <c r="H56" s="1">
+        <v>1.08</v>
+      </c>
+      <c r="I56" s="1">
+        <f>Table1[[#This Row],[Qty]]*Table1[[#This Row],[Unit Cost]]</f>
+        <v>1.08</v>
+      </c>
+      <c r="J56" t="s">
+        <v>65</v>
+      </c>
+    </row>
+    <row r="57" spans="1:11" x14ac:dyDescent="0.2">
+      <c r="B57" t="s">
+        <v>66</v>
+      </c>
+      <c r="D57" t="s">
+        <v>67</v>
+      </c>
+      <c r="I57" s="1">
+        <f>Table1[[#This Row],[Qty]]*Table1[[#This Row],[Unit Cost]]</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="58" spans="1:11" x14ac:dyDescent="0.2">
+      <c r="A58" t="s">
+        <v>87</v>
+      </c>
+      <c r="B58" t="s">
+        <v>119</v>
+      </c>
+      <c r="C58" s="5" t="s">
+        <v>109</v>
+      </c>
+      <c r="D58" t="s">
+        <v>108</v>
+      </c>
+      <c r="E58" t="s">
+        <v>69</v>
+      </c>
+      <c r="F58">
+        <v>1</v>
+      </c>
+      <c r="G58" s="1" t="s">
+        <v>21</v>
+      </c>
+      <c r="H58" s="1">
+        <v>1.49</v>
+      </c>
+      <c r="I58" s="1">
+        <f>Table1[[#This Row],[Qty]]*Table1[[#This Row],[Unit Cost]]</f>
+        <v>1.49</v>
+      </c>
+      <c r="J58" s="4" t="s">
+        <v>110</v>
+      </c>
+    </row>
+    <row r="59" spans="1:11" x14ac:dyDescent="0.2">
+      <c r="A59" t="s">
+        <v>20</v>
+      </c>
+      <c r="B59" t="s">
+        <v>119</v>
+      </c>
+      <c r="C59" s="5" t="s">
+        <v>124</v>
+      </c>
+      <c r="D59" t="s">
+        <v>121</v>
+      </c>
+      <c r="E59" t="s">
+        <v>32</v>
+      </c>
+      <c r="F59">
+        <v>6</v>
+      </c>
+      <c r="G59" s="1" t="s">
+        <v>21</v>
+      </c>
+      <c r="H59" s="1">
+        <f>8.44/100</f>
+        <v>8.4399999999999989E-2</v>
+      </c>
+      <c r="I59" s="1">
+        <f>Table1[[#This Row],[Qty]]*Table1[[#This Row],[Unit Cost]]</f>
+        <v>0.50639999999999996</v>
+      </c>
+      <c r="J59" s="4" t="s">
+        <v>123</v>
+      </c>
+    </row>
+    <row r="60" spans="1:11" x14ac:dyDescent="0.2">
+      <c r="A60" t="s">
+        <v>20</v>
+      </c>
+      <c r="B60" t="s">
+        <v>119</v>
+      </c>
+      <c r="C60" s="5" t="s">
+        <v>46</v>
+      </c>
+      <c r="D60" t="s">
+        <v>122</v>
+      </c>
+      <c r="E60" t="s">
+        <v>32</v>
+      </c>
+      <c r="F60">
+        <v>6</v>
+      </c>
+      <c r="G60" t="s">
+        <v>21</v>
+      </c>
+      <c r="H60" s="1">
         <f>3.06/100</f>
         <v>3.0600000000000002E-2</v>
       </c>
-      <c r="I44" s="1">
-        <f>Table1[[#This Row],[Qty]]*Table1[[#This Row],[Unit Cost]]</f>
-        <v>3.0600000000000002E-2</v>
-      </c>
-      <c r="J44" s="4" t="s">
-        <v>46</v>
-      </c>
-    </row>
-    <row r="45" spans="1:10" x14ac:dyDescent="0.2">
-      <c r="A45" t="s">
-        <v>27</v>
-      </c>
-      <c r="B45" t="s">
-        <v>27</v>
-      </c>
-      <c r="C45" s="5" t="s">
-        <v>30</v>
-      </c>
-      <c r="D45" t="s">
-        <v>31</v>
-      </c>
-      <c r="E45" t="s">
-        <v>29</v>
-      </c>
-      <c r="F45">
-        <v>1</v>
-      </c>
-      <c r="G45" s="1" t="s">
-        <v>21</v>
-      </c>
-      <c r="H45" s="1">
-        <v>229</v>
-      </c>
-      <c r="I45" s="1">
-        <f>Table1[[#This Row],[Qty]]*Table1[[#This Row],[Unit Cost]]</f>
-        <v>229</v>
-      </c>
-      <c r="J45" s="4" t="s">
-        <v>60</v>
-      </c>
-    </row>
-    <row r="46" spans="1:10" x14ac:dyDescent="0.2">
-      <c r="B46" t="s">
-        <v>27</v>
-      </c>
-      <c r="D46" t="s">
-        <v>117</v>
-      </c>
-      <c r="I46" s="1">
+      <c r="I60" s="1">
+        <f>Table1[[#This Row],[Qty]]*Table1[[#This Row],[Unit Cost]]</f>
+        <v>0.18360000000000001</v>
+      </c>
+    </row>
+    <row r="61" spans="1:11" x14ac:dyDescent="0.2">
+      <c r="A61" t="s">
+        <v>87</v>
+      </c>
+      <c r="B61" t="s">
+        <v>119</v>
+      </c>
+      <c r="D61" t="s">
+        <v>125</v>
+      </c>
+      <c r="I61" s="1">
         <f>Table1[[#This Row],[Qty]]*Table1[[#This Row],[Unit Cost]]</f>
         <v>0</v>
       </c>
-      <c r="J46" s="4"/>
-    </row>
-    <row r="47" spans="1:10" x14ac:dyDescent="0.2">
-      <c r="A47" t="s">
-        <v>20</v>
-      </c>
-      <c r="B47" t="s">
-        <v>27</v>
-      </c>
-      <c r="C47" s="5" t="s">
-        <v>44</v>
-      </c>
-      <c r="D47" t="s">
-        <v>35</v>
-      </c>
-      <c r="E47" t="s">
-        <v>33</v>
-      </c>
-      <c r="F47">
-        <v>6</v>
-      </c>
-      <c r="G47" s="1" t="s">
-        <v>21</v>
-      </c>
-      <c r="H47" s="1">
-        <f>17.63/100</f>
-        <v>0.17629999999999998</v>
-      </c>
-      <c r="I47" s="1">
-        <f>Table1[[#This Row],[Qty]]*Table1[[#This Row],[Unit Cost]]</f>
-        <v>1.0577999999999999</v>
-      </c>
-      <c r="J47" s="4" t="s">
-        <v>42</v>
-      </c>
-    </row>
-    <row r="48" spans="1:10" x14ac:dyDescent="0.2">
-      <c r="A48" t="s">
-        <v>20</v>
-      </c>
-      <c r="B48" t="s">
-        <v>27</v>
-      </c>
-      <c r="C48" s="5" t="s">
-        <v>49</v>
-      </c>
-      <c r="D48" t="s">
-        <v>43</v>
-      </c>
-      <c r="E48" t="s">
-        <v>33</v>
-      </c>
-      <c r="F48">
-        <v>6</v>
-      </c>
-      <c r="G48" s="1" t="s">
-        <v>21</v>
-      </c>
-      <c r="H48" s="1">
-        <f>3/100</f>
-        <v>0.03</v>
-      </c>
-      <c r="I48" s="1">
-        <f>Table1[[#This Row],[Qty]]*Table1[[#This Row],[Unit Cost]]</f>
-        <v>0.18</v>
-      </c>
-      <c r="J48" s="4" t="s">
-        <v>48</v>
-      </c>
-    </row>
-    <row r="49" spans="1:10" x14ac:dyDescent="0.2">
-      <c r="A49" t="s">
-        <v>26</v>
-      </c>
-      <c r="B49" t="s">
-        <v>28</v>
-      </c>
-      <c r="D49" t="s">
-        <v>34</v>
-      </c>
-      <c r="G49" s="1" t="s">
-        <v>36</v>
-      </c>
-      <c r="I49" s="1">
-        <f>Table1[[#This Row],[Qty]]*Table1[[#This Row],[Unit Cost]]</f>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="50" spans="1:10" x14ac:dyDescent="0.2">
-      <c r="A50" t="s">
-        <v>20</v>
-      </c>
-      <c r="B50" t="s">
-        <v>28</v>
-      </c>
-      <c r="D50" t="s">
+    </row>
+    <row r="62" spans="1:11" x14ac:dyDescent="0.2">
+      <c r="B62" t="s">
+        <v>119</v>
+      </c>
+      <c r="C62" s="5" t="s">
+        <v>134</v>
+      </c>
+      <c r="D62" t="s">
+        <v>133</v>
+      </c>
+      <c r="E62" t="s">
         <v>32</v>
       </c>
-      <c r="E50" t="s">
-        <v>33</v>
-      </c>
-      <c r="F50">
-        <v>2</v>
-      </c>
-      <c r="H50" s="1">
-        <f>11.38/50</f>
-        <v>0.22760000000000002</v>
-      </c>
-      <c r="I50" s="1">
-        <f>Table1[[#This Row],[Qty]]*Table1[[#This Row],[Unit Cost]]</f>
-        <v>0.45520000000000005</v>
-      </c>
-      <c r="J50" s="4" t="s">
-        <v>38</v>
-      </c>
-    </row>
-    <row r="51" spans="1:10" x14ac:dyDescent="0.2">
-      <c r="B51" t="s">
-        <v>28</v>
-      </c>
-      <c r="D51" t="s">
-        <v>53</v>
-      </c>
-      <c r="E51" t="s">
-        <v>54</v>
-      </c>
-      <c r="F51">
-        <v>1</v>
-      </c>
-      <c r="G51" s="1" t="s">
-        <v>21</v>
-      </c>
-      <c r="I51" s="1">
-        <f>Table1[[#This Row],[Qty]]*Table1[[#This Row],[Unit Cost]]</f>
-        <v>0</v>
-      </c>
-      <c r="J51" s="4" t="s">
-        <v>55</v>
-      </c>
-    </row>
-    <row r="52" spans="1:10" x14ac:dyDescent="0.2">
-      <c r="B52" t="s">
-        <v>28</v>
-      </c>
-      <c r="D52" t="s">
-        <v>110</v>
-      </c>
-      <c r="F52">
-        <v>1</v>
-      </c>
-      <c r="G52" s="1" t="s">
-        <v>21</v>
-      </c>
-      <c r="I52" s="1">
-        <f>Table1[[#This Row],[Qty]]*Table1[[#This Row],[Unit Cost]]</f>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="53" spans="1:10" x14ac:dyDescent="0.2">
-      <c r="A53" t="s">
-        <v>20</v>
-      </c>
-      <c r="B53" t="s">
-        <v>28</v>
-      </c>
-      <c r="C53" s="5" t="s">
-        <v>123</v>
-      </c>
-      <c r="D53" t="s">
-        <v>121</v>
-      </c>
-      <c r="E53" t="s">
-        <v>33</v>
-      </c>
-      <c r="F53">
-        <v>3</v>
-      </c>
-      <c r="G53" s="1" t="s">
-        <v>21</v>
-      </c>
-      <c r="H53" s="1">
-        <f>7.57/100</f>
-        <v>7.5700000000000003E-2</v>
-      </c>
-      <c r="I53" s="1">
-        <f>Table1[[#This Row],[Qty]]*Table1[[#This Row],[Unit Cost]]</f>
-        <v>0.22710000000000002</v>
-      </c>
-      <c r="J53" t="s">
-        <v>124</v>
-      </c>
-    </row>
-    <row r="54" spans="1:10" x14ac:dyDescent="0.2">
-      <c r="A54" t="s">
-        <v>20</v>
-      </c>
-      <c r="B54" t="s">
-        <v>28</v>
-      </c>
-      <c r="C54" s="5" t="s">
-        <v>126</v>
-      </c>
-      <c r="D54" t="s">
-        <v>122</v>
-      </c>
-      <c r="E54" t="s">
-        <v>33</v>
-      </c>
-      <c r="F54">
-        <v>3</v>
-      </c>
-      <c r="G54" s="1" t="s">
-        <v>21</v>
-      </c>
-      <c r="H54" s="1">
-        <f>7.41/100</f>
-        <v>7.4099999999999999E-2</v>
-      </c>
-      <c r="I54" s="1">
-        <f>Table1[[#This Row],[Qty]]*Table1[[#This Row],[Unit Cost]]</f>
-        <v>0.2223</v>
-      </c>
-      <c r="J54" s="4" t="s">
-        <v>125</v>
-      </c>
-    </row>
-    <row r="55" spans="1:10" x14ac:dyDescent="0.2">
-      <c r="B55" t="s">
-        <v>68</v>
-      </c>
-      <c r="D55" t="s">
-        <v>64</v>
-      </c>
-      <c r="I55" s="1">
-        <f>Table1[[#This Row],[Qty]]*Table1[[#This Row],[Unit Cost]]</f>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="56" spans="1:10" x14ac:dyDescent="0.2">
-      <c r="B56" t="s">
-        <v>68</v>
-      </c>
-      <c r="C56" s="5" t="s">
-        <v>66</v>
-      </c>
-      <c r="D56" t="s">
-        <v>65</v>
-      </c>
-      <c r="E56" t="s">
-        <v>37</v>
-      </c>
-      <c r="F56">
-        <v>1</v>
-      </c>
-      <c r="G56" s="1" t="s">
-        <v>21</v>
-      </c>
-      <c r="H56" s="1">
-        <v>1.08</v>
-      </c>
-      <c r="I56" s="1">
-        <f>Table1[[#This Row],[Qty]]*Table1[[#This Row],[Unit Cost]]</f>
-        <v>1.08</v>
-      </c>
-      <c r="J56" t="s">
-        <v>67</v>
-      </c>
-    </row>
-    <row r="57" spans="1:10" x14ac:dyDescent="0.2">
-      <c r="B57" t="s">
-        <v>68</v>
-      </c>
-      <c r="D57" t="s">
-        <v>69</v>
-      </c>
-      <c r="I57" s="1">
-        <f>Table1[[#This Row],[Qty]]*Table1[[#This Row],[Unit Cost]]</f>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="58" spans="1:10" x14ac:dyDescent="0.2">
-      <c r="B58" t="s">
-        <v>68</v>
-      </c>
-      <c r="D58" t="s">
-        <v>70</v>
-      </c>
-      <c r="I58" s="1">
-        <f>Table1[[#This Row],[Qty]]*Table1[[#This Row],[Unit Cost]]</f>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="59" spans="1:10" x14ac:dyDescent="0.2">
-      <c r="A59" t="s">
-        <v>92</v>
-      </c>
-      <c r="B59" t="s">
-        <v>92</v>
-      </c>
-      <c r="C59" s="5" t="s">
-        <v>115</v>
-      </c>
-      <c r="D59" t="s">
-        <v>114</v>
-      </c>
-      <c r="E59" t="s">
-        <v>71</v>
-      </c>
-      <c r="F59">
-        <v>1</v>
-      </c>
-      <c r="G59" s="1" t="s">
-        <v>21</v>
-      </c>
-      <c r="H59" s="1">
-        <v>1.49</v>
-      </c>
-      <c r="I59" s="1">
-        <f>Table1[[#This Row],[Qty]]*Table1[[#This Row],[Unit Cost]]</f>
-        <v>1.49</v>
-      </c>
-      <c r="J59" s="4" t="s">
-        <v>116</v>
+      <c r="F62">
+        <v>0.5</v>
+      </c>
+      <c r="G62" s="1" t="s">
+        <v>21</v>
+      </c>
+      <c r="H62" s="1">
+        <v>9.65</v>
+      </c>
+      <c r="I62" s="1">
+        <f>Table1[[#This Row],[Qty]]*Table1[[#This Row],[Unit Cost]]</f>
+        <v>4.8250000000000002</v>
+      </c>
+      <c r="J62" t="s">
+        <v>135</v>
+      </c>
+      <c r="K62" t="s">
+        <v>139</v>
       </c>
     </row>
   </sheetData>
   <hyperlinks>
-    <hyperlink ref="J43" r:id="rId1" xr:uid="{7232EB30-30F6-A44D-A099-36A36F85D531}"/>
-    <hyperlink ref="J45" r:id="rId2" xr:uid="{27DD5690-F388-A048-A20A-B068A8B5D504}"/>
-    <hyperlink ref="J47" r:id="rId3" xr:uid="{331E0A82-5FA5-414B-9807-F2B18A4F0C7D}"/>
-    <hyperlink ref="J44" r:id="rId4" xr:uid="{14163A79-9220-954E-B070-3F59DBA5CAD5}"/>
-    <hyperlink ref="J50" r:id="rId5" xr:uid="{0BD55709-6453-5C45-B817-BE190D9BC47D}"/>
-    <hyperlink ref="J48" r:id="rId6" xr:uid="{39651285-9062-AE46-8CEE-CB2502E2250C}"/>
+    <hyperlink ref="J41" r:id="rId1" xr:uid="{7232EB30-30F6-A44D-A099-36A36F85D531}"/>
+    <hyperlink ref="J43" r:id="rId2" xr:uid="{27DD5690-F388-A048-A20A-B068A8B5D504}"/>
+    <hyperlink ref="J45" r:id="rId3" xr:uid="{331E0A82-5FA5-414B-9807-F2B18A4F0C7D}"/>
+    <hyperlink ref="J42" r:id="rId4" xr:uid="{14163A79-9220-954E-B070-3F59DBA5CAD5}"/>
+    <hyperlink ref="J49" r:id="rId5" xr:uid="{0BD55709-6453-5C45-B817-BE190D9BC47D}"/>
+    <hyperlink ref="J46" r:id="rId6" xr:uid="{39651285-9062-AE46-8CEE-CB2502E2250C}"/>
     <hyperlink ref="J11" r:id="rId7" xr:uid="{AEA8C86A-2AF5-954D-AD6C-68528ADFACB4}"/>
     <hyperlink ref="J13" r:id="rId8" xr:uid="{D04300F4-D466-DE4C-87BE-1085E3419DD2}"/>
     <hyperlink ref="J15" r:id="rId9" xr:uid="{FAEC562D-C427-2046-8C55-C0E64FA01D73}"/>
@@ -2252,12 +2400,14 @@
     <hyperlink ref="J22" r:id="rId13" xr:uid="{F7B7AD27-F42E-7843-B388-0AAA3554A341}"/>
     <hyperlink ref="J12" r:id="rId14" xr:uid="{00954120-3DFF-124A-B8CE-0910D138CBD6}"/>
     <hyperlink ref="J29" r:id="rId15" xr:uid="{8C561801-202F-1A49-9E4D-58E07ADA24E3}"/>
-    <hyperlink ref="J59" r:id="rId16" xr:uid="{8087BC0F-FFD5-CD4E-ADFE-1EA4780F0490}"/>
-    <hyperlink ref="J54" r:id="rId17" xr:uid="{820CF3C4-6327-B742-A1A3-106AA8E81F7B}"/>
+    <hyperlink ref="J58" r:id="rId16" xr:uid="{8087BC0F-FFD5-CD4E-ADFE-1EA4780F0490}"/>
+    <hyperlink ref="J53" r:id="rId17" xr:uid="{820CF3C4-6327-B742-A1A3-106AA8E81F7B}"/>
+    <hyperlink ref="J59" r:id="rId18" xr:uid="{D871B945-B618-6344-8A01-6EC7344361E7}"/>
+    <hyperlink ref="J48" r:id="rId19" xr:uid="{E2D038F6-E31B-7A4D-995A-482D86DDD91D}"/>
   </hyperlinks>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <tableParts count="1">
-    <tablePart r:id="rId18"/>
+    <tablePart r:id="rId20"/>
   </tableParts>
 </worksheet>
 </file>
--- a/Walking-Setup/G6-Integration-Bill-of-Materials.xlsx
+++ b/Walking-Setup/G6-Integration-Bill-of-Materials.xlsx
@@ -1,25 +1,22 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="10628"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="10703"/>
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/lehenbaueri/Documents/GitHub/Fly-Lab-Gear/Walking-Setup/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{2B84DA0F-7DE9-5B46-B031-2272896AF708}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{50363D00-03FF-BB4E-9D05-0301A7584635}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="6460" yWindow="1600" windowWidth="27460" windowHeight="18980" xr2:uid="{1DD35749-F480-5B49-A82C-F7D601ECF748}"/>
+    <workbookView xWindow="6460" yWindow="1600" windowWidth="27460" windowHeight="18980" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
   </sheets>
   <calcPr calcId="191029"/>
   <extLst>
-    <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{140A7094-0E35-4892-8432-C4D2E57EDEB5}">
-      <x15:workbookPr chartTrackingRefBase="1"/>
-    </ext>
     <ext xmlns:xcalcf="http://schemas.microsoft.com/office/spreadsheetml/2018/calcfeatures" uri="{B58B0392-4F1F-4190-BB64-5DF3571DCE5F}">
       <xcalcf:calcFeatures>
         <xcalcf:feature name="microsoft.com:RD"/>
@@ -31,62 +28,74 @@
         <xcalcf:feature name="microsoft.com:ARRAYTEXT_WF"/>
       </xcalcf:calcFeatures>
     </ext>
-    <ext xmlns:xlwcv="http://schemas.microsoft.com/office/spreadsheetml/2024/workbookCompatibilityVersion" uri="{D14903EA-33C4-47F7-8F05-3474C54BE107}">
-      <xlwcv:version setVersion="2"/>
-    </ext>
   </extLst>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="283" uniqueCount="140">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="305" uniqueCount="152">
+  <si>
+    <t>Name</t>
+  </si>
+  <si>
+    <t>G6 Fly on Ball Walking Setup</t>
+  </si>
+  <si>
+    <t>Number</t>
+  </si>
+  <si>
+    <t>Revision</t>
+  </si>
+  <si>
+    <t>Engineer</t>
+  </si>
+  <si>
+    <t>Isabel Lehenbauer</t>
+  </si>
+  <si>
+    <t>Approval date</t>
+  </si>
+  <si>
+    <t>Part count</t>
+  </si>
+  <si>
+    <t>Total cost</t>
+  </si>
+  <si>
+    <t>Category</t>
+  </si>
+  <si>
+    <t>Subassembly</t>
+  </si>
   <si>
     <t>Part No.</t>
   </si>
   <si>
+    <t>Part Name</t>
+  </si>
+  <si>
+    <t>Supplier</t>
+  </si>
+  <si>
     <t>Qty</t>
   </si>
   <si>
+    <t>Units</t>
+  </si>
+  <si>
+    <t>Unit Cost</t>
+  </si>
+  <si>
     <t>Cost</t>
   </si>
   <si>
-    <t>Category</t>
-  </si>
-  <si>
-    <t>Part Name</t>
-  </si>
-  <si>
-    <t>Units</t>
-  </si>
-  <si>
-    <t>Unit Cost</t>
-  </si>
-  <si>
-    <t>Supplier</t>
-  </si>
-  <si>
-    <t>Name</t>
-  </si>
-  <si>
-    <t>Number</t>
-  </si>
-  <si>
-    <t>Revision</t>
-  </si>
-  <si>
-    <t>Approval date</t>
-  </si>
-  <si>
-    <t>Part count</t>
-  </si>
-  <si>
-    <t>Total cost</t>
-  </si>
-  <si>
-    <t>Engineer</t>
-  </si>
-  <si>
-    <t>Isabel Lehenbauer</t>
+    <t>Link</t>
+  </si>
+  <si>
+    <t>Note</t>
+  </si>
+  <si>
+    <t>MB12</t>
   </si>
   <si>
     <t>12" x 12" Breadboard</t>
@@ -95,19 +104,175 @@
     <t>Thorlabs</t>
   </si>
   <si>
-    <t>Subassembly</t>
+    <t>each</t>
+  </si>
+  <si>
+    <t>https://www.thorlabs.com/item/MB12</t>
+  </si>
+  <si>
+    <t>G6 Arena</t>
+  </si>
+  <si>
+    <t>https://reiserlab.github.io/Modular-LED-Display/G6/</t>
+  </si>
+  <si>
+    <t>TR1</t>
+  </si>
+  <si>
+    <t>1" post</t>
+  </si>
+  <si>
+    <t>https://www.thorlabs.com/item/TR1</t>
+  </si>
+  <si>
+    <t>Hardware</t>
+  </si>
+  <si>
+    <t>92311A197</t>
+  </si>
+  <si>
+    <t>#8-32 set screw 3/4"</t>
+  </si>
+  <si>
+    <t>McMaster Carr</t>
+  </si>
+  <si>
+    <t>https://www.mcmaster.com/92311A197/</t>
+  </si>
+  <si>
+    <t>90480A009</t>
+  </si>
+  <si>
+    <t>#8-32 nuts</t>
+  </si>
+  <si>
+    <t>https://www.mcmaster.com/90480A009/</t>
+  </si>
+  <si>
+    <t>J011595</t>
+  </si>
+  <si>
+    <t>Spacer posts</t>
+  </si>
+  <si>
+    <t>3D printed</t>
+  </si>
+  <si>
+    <t>g</t>
+  </si>
+  <si>
+    <t>../Miscellaneous/G6-Spacer/production/Panel-Spacer-2Panels.stl</t>
+  </si>
+  <si>
+    <t>Electrical</t>
+  </si>
+  <si>
+    <t>Barrel jack power supply (5V, 10A)</t>
+  </si>
+  <si>
+    <t>Micro USB to USB cable</t>
+  </si>
+  <si>
+    <t>https://www.amazon.com/Smays-5-Pack-Micro-Transfer-Charging/dp/B0DZ6QRRHJ/ref=sr_1_2_sspa</t>
   </si>
   <si>
     <t>Optostim</t>
   </si>
   <si>
-    <t>Hardware</t>
-  </si>
-  <si>
-    <t>each</t>
-  </si>
-  <si>
-    <t>Link</t>
+    <t>91185A293</t>
+  </si>
+  <si>
+    <t>#8-32 thumb screws</t>
+  </si>
+  <si>
+    <t>https://www.mcmaster.com/91185A293-91185A442/</t>
+  </si>
+  <si>
+    <t>91251A194</t>
+  </si>
+  <si>
+    <t>#8-32 cap screw 1/2"</t>
+  </si>
+  <si>
+    <t>https://www.mcmaster.com/91251A194/</t>
+  </si>
+  <si>
+    <t>8974K24</t>
+  </si>
+  <si>
+    <t>Rail 3/8" dia aluminum rod</t>
+  </si>
+  <si>
+    <t>https://www.mcmaster.com/8974K24-8974K241/</t>
+  </si>
+  <si>
+    <t>Optostim light rail holder</t>
+  </si>
+  <si>
+    <t>Optostimulation/production/optostim-light-rail-holder.stl</t>
+  </si>
+  <si>
+    <t>90 deg rail slider</t>
+  </si>
+  <si>
+    <t>Optostimulation/production/90Deg-Rail-Slider.stl</t>
+  </si>
+  <si>
+    <t>Optostim light guide</t>
+  </si>
+  <si>
+    <t>Optostimulation/production/optostim-light-guide.stl</t>
+  </si>
+  <si>
+    <t>Barrel jack (M) to screw terminals</t>
+  </si>
+  <si>
+    <t xml:space="preserve">BNC (m) to screw terminals </t>
+  </si>
+  <si>
+    <t>On-off switch</t>
+  </si>
+  <si>
+    <t>DLH-xUP-EH</t>
+  </si>
+  <si>
+    <t>LED lamp housing</t>
+  </si>
+  <si>
+    <t>LED Supply</t>
+  </si>
+  <si>
+    <t>https://www.ledsupply.com/led-heatsinks/dynamic-led-heatsink-housing</t>
+  </si>
+  <si>
+    <t>CREEXPE2-RED-1</t>
+  </si>
+  <si>
+    <t>Cree XLamp XP-E2 Color High Power LED Star</t>
+  </si>
+  <si>
+    <t>10193 Carclo 20mm Lens - Plain Tight Spot LED Optic</t>
+  </si>
+  <si>
+    <t>DLH-XL-NPLE</t>
+  </si>
+  <si>
+    <t>Dynamic LED Housing All Thread Nipple</t>
+  </si>
+  <si>
+    <t>03023-D-E-350</t>
+  </si>
+  <si>
+    <t>Buckpuck Luxdrive</t>
+  </si>
+  <si>
+    <t>LO-X-H2-2</t>
+  </si>
+  <si>
+    <t>Butt Splice Quick Wire Connectors</t>
+  </si>
+  <si>
+    <t>Barrel jack to screw terminal</t>
   </si>
   <si>
     <t>Fly Holder</t>
@@ -116,349 +281,214 @@
     <t>Micromanipulator</t>
   </si>
   <si>
+    <t>Micromanipulator adapter plate</t>
+  </si>
+  <si>
     <t>Fly holder stand</t>
   </si>
   <si>
+    <t>Fly-Holder/production/Friction-Mount-Stand.stl</t>
+  </si>
+  <si>
+    <t>Fly holder arm R</t>
+  </si>
+  <si>
+    <t>Fly-Holder/production/Friction-Mount-Arm-R.stl</t>
+  </si>
+  <si>
+    <t>Blunt Needle for Tethering</t>
+  </si>
+  <si>
+    <t>91290A125</t>
+  </si>
+  <si>
+    <t>M3x0.5 screws, 25 mm</t>
+  </si>
+  <si>
+    <t>https://www.mcmaster.com/91290A125/</t>
+  </si>
+  <si>
+    <t>90591A250</t>
+  </si>
+  <si>
+    <t>M3x0.5 nut, 2mm</t>
+  </si>
+  <si>
+    <t>https://www.mcmaster.com/90591A250/</t>
+  </si>
+  <si>
     <t>Camera</t>
   </si>
   <si>
+    <t>FFY-U3-04S2M-S</t>
+  </si>
+  <si>
+    <t>Flir Firefly S USB3: 0.4 MP, Mono, S-mount</t>
+  </si>
+  <si>
+    <t>Teledyne Flir</t>
+  </si>
+  <si>
+    <t>https://www.teledynevisionsolutions.com/products/firefly-s/?model=FFY-U3-04S2M-S</t>
+  </si>
+  <si>
+    <t>S-mount Lens</t>
+  </si>
+  <si>
+    <t>91290A011</t>
+  </si>
+  <si>
+    <t>M2x0.4, 4mm cap screw</t>
+  </si>
+  <si>
+    <t>https://www.mcmaster.com/91290A011/</t>
+  </si>
+  <si>
+    <t>91166A180</t>
+  </si>
+  <si>
+    <t>M2 washer</t>
+  </si>
+  <si>
+    <t>https://www.mcmaster.com/91166A180/</t>
+  </si>
+  <si>
+    <t>USB3 Micro B to USB cable</t>
+  </si>
+  <si>
+    <t>https://www.amazon.com/External-Seagate-Toshiba-Western-Passport/dp/B0F1N5W6VW/ref=sr_1_1_sspa</t>
+  </si>
+  <si>
     <t>Treadmill</t>
   </si>
   <si>
-    <t>Teledyne Flir</t>
-  </si>
-  <si>
-    <t>FFY-U3-04S2M-S</t>
-  </si>
-  <si>
-    <t>Flir Firefly S USB3: 0.4 MP, Mono, S-mount</t>
-  </si>
-  <si>
-    <t>1/4-20 by 3/4" cap screw</t>
-  </si>
-  <si>
-    <t>McMaster Carr</t>
-  </si>
-  <si>
     <t>Integrated Camera + treadmill</t>
   </si>
   <si>
-    <t>M2x0.4, 4mm cap screw</t>
-  </si>
-  <si>
-    <t>g</t>
+    <t>3D printed, resin</t>
+  </si>
+  <si>
+    <t>Inexpensive-Treadmill_Assembly/production/G6-Integrated-Inexpensive-Treadmill.stl</t>
+  </si>
+  <si>
+    <t>1/4-20 cap screw, 3/4"</t>
+  </si>
+  <si>
+    <t>https://www.mcmaster.com/91251A540/</t>
+  </si>
+  <si>
+    <t>Ball</t>
+  </si>
+  <si>
+    <t>General Plastics</t>
+  </si>
+  <si>
+    <t>https://www.generalplastics.com/products/fr-7100</t>
+  </si>
+  <si>
+    <t>Illumination panel</t>
+  </si>
+  <si>
+    <t>Treadmill-Illumination/</t>
+  </si>
+  <si>
+    <t>91292A833</t>
+  </si>
+  <si>
+    <t>M2x0.4 screws, 10 mm</t>
+  </si>
+  <si>
+    <t>https://www.mcmaster.com/91292A833/</t>
+  </si>
+  <si>
+    <t>91828A111</t>
+  </si>
+  <si>
+    <t>M2x0.4 nuts</t>
+  </si>
+  <si>
+    <t>https://www.mcmaster.com/91828A111/</t>
+  </si>
+  <si>
+    <t>Heater</t>
+  </si>
+  <si>
+    <t>70 mm circular heating pad</t>
+  </si>
+  <si>
+    <t>https://www.amazon.com/XIITIA-70mmx70mm-Adhesive-Elements-Polyimide/dp/B0D5DC9VWB/ref=sr_1_2?</t>
+  </si>
+  <si>
+    <t>Heating baseplate</t>
+  </si>
+  <si>
+    <t>../Miscellaneous/Baseplate/production/heat_baseplate_sketch.svg</t>
+  </si>
+  <si>
+    <t>Laser cut</t>
+  </si>
+  <si>
+    <t>56-NTCLE350E4103FLB0-ND</t>
+  </si>
+  <si>
+    <t>Thermometer</t>
   </si>
   <si>
     <t>Digikey</t>
   </si>
   <si>
-    <t>https://www.mcmaster.com/91251A540/</t>
-  </si>
-  <si>
-    <t>https://www.mcmaster.com/91290A125/</t>
-  </si>
-  <si>
-    <t>M3x0.5 screws, 25 mm</t>
-  </si>
-  <si>
-    <t>M3x0.5 nut, 2mm</t>
-  </si>
-  <si>
-    <t>https://www.mcmaster.com/91290A011/</t>
-  </si>
-  <si>
-    <t>M2 washer</t>
-  </si>
-  <si>
-    <t>91290A011</t>
-  </si>
-  <si>
-    <t>91290A125</t>
-  </si>
-  <si>
-    <t>https://www.mcmaster.com/90591A250/</t>
-  </si>
-  <si>
-    <t>90591A250</t>
-  </si>
-  <si>
-    <t>https://www.mcmaster.com/91166A180/</t>
-  </si>
-  <si>
-    <t>91166A180</t>
-  </si>
-  <si>
-    <t>https://www.thorlabs.com/item/MB12</t>
-  </si>
-  <si>
-    <t>MB12</t>
-  </si>
-  <si>
-    <t>G6 Arena</t>
-  </si>
-  <si>
-    <t>Ball</t>
-  </si>
-  <si>
-    <t>General Plastics</t>
-  </si>
-  <si>
-    <t>https://www.generalplastics.com/products/fr-7100</t>
-  </si>
-  <si>
-    <t>1" post</t>
-  </si>
-  <si>
-    <t>https://www.thorlabs.com/item/TR1</t>
-  </si>
-  <si>
-    <t>TR1</t>
-  </si>
-  <si>
-    <t>https://www.mcmaster.com/90480A009/</t>
-  </si>
-  <si>
-    <t>https://www.teledynevisionsolutions.com/products/firefly-s/?model=FFY-U3-04S2M-S</t>
-  </si>
-  <si>
-    <t>J011595</t>
-  </si>
-  <si>
-    <t>Spacer posts</t>
-  </si>
-  <si>
-    <t>3D printed</t>
-  </si>
-  <si>
-    <t>Thermometer</t>
-  </si>
-  <si>
-    <t>56-NTCLE350E4103FLB0-ND</t>
-  </si>
-  <si>
     <t>https://www.digikey.com/en/products/detail/vishay-beyschlag-draloric-bc-components/NTCLE350E4103FLB0/12612895</t>
   </si>
   <si>
-    <t>Heater</t>
-  </si>
-  <si>
     <t>Control panel</t>
   </si>
   <si>
-    <t>Barrel jack to screw terminal</t>
-  </si>
-  <si>
-    <t>LED Supply</t>
-  </si>
-  <si>
-    <t>Buckpuck Luxdrive</t>
-  </si>
-  <si>
-    <t>On-off switch</t>
-  </si>
-  <si>
-    <t xml:space="preserve">BNC (m) to screw terminals </t>
-  </si>
-  <si>
-    <t>90 deg rail slider</t>
-  </si>
-  <si>
-    <t>https://www.ledsupply.com/led-heatsinks/dynamic-led-heatsink-housing</t>
-  </si>
-  <si>
-    <t>LED lamp housing</t>
-  </si>
-  <si>
-    <t>Dynamic LED Housing All Thread Nipple</t>
-  </si>
-  <si>
-    <t>DLH-XL-NPLE</t>
-  </si>
-  <si>
-    <t>DLH-xUP-EH</t>
-  </si>
-  <si>
-    <t>10193 Carclo 20mm Lens - Plain Tight Spot LED Optic</t>
-  </si>
-  <si>
-    <t>03023-D-E-350</t>
-  </si>
-  <si>
-    <t>Cree XLamp XP-E2 Color High Power LED Star</t>
-  </si>
-  <si>
-    <t>CREEXPE2-RED-1</t>
-  </si>
-  <si>
-    <t>Optostim light guide</t>
-  </si>
-  <si>
-    <t>Butt Splice Quick Wire Connectors</t>
-  </si>
-  <si>
-    <t>LO-X-H2-2</t>
-  </si>
-  <si>
-    <t>Fly holder arm R</t>
-  </si>
-  <si>
-    <t>Electrical</t>
-  </si>
-  <si>
-    <t>Micromanipulator adapter plate</t>
-  </si>
-  <si>
-    <t>Laser cut</t>
-  </si>
-  <si>
-    <t>#8-32 nuts</t>
-  </si>
-  <si>
-    <t>91185A293</t>
-  </si>
-  <si>
-    <t>#8-32 thumb screws</t>
-  </si>
-  <si>
-    <t>https://www.mcmaster.com/91185A293-91185A442/</t>
-  </si>
-  <si>
-    <t>90480A009</t>
-  </si>
-  <si>
-    <t>#8-32 cap screw 1/2"</t>
-  </si>
-  <si>
-    <t>91251A194</t>
-  </si>
-  <si>
-    <t>https://www.mcmaster.com/91251A194/</t>
-  </si>
-  <si>
-    <t>8974K24</t>
-  </si>
-  <si>
-    <t>Rail 3/8" dia aluminum rod</t>
-  </si>
-  <si>
-    <t>https://www.mcmaster.com/8974K24-8974K241/</t>
-  </si>
-  <si>
-    <t>#8-32 set screw 3/4"</t>
-  </si>
-  <si>
-    <t>92311A197</t>
-  </si>
-  <si>
-    <t>https://www.mcmaster.com/92311A197/</t>
-  </si>
-  <si>
-    <t>Illumination panel</t>
-  </si>
-  <si>
-    <t>https://reiserlab.github.io/Modular-LED-Display/G6/</t>
-  </si>
-  <si>
-    <t>Barrel jack (M) to screw terminals</t>
-  </si>
-  <si>
-    <t>G6 Fly on Ball Walking Setup</t>
+    <t>Electrical Box 12V</t>
+  </si>
+  <si>
+    <t>LO-CONSPLIT-2</t>
   </si>
   <si>
     <t>Power splitter</t>
   </si>
   <si>
-    <t>LO-CONSPLIT-2</t>
-  </si>
-  <si>
     <t>https://www.ledsupply.com/accessories/lever-splitter-wire-connectors</t>
   </si>
   <si>
-    <t>S-mount Lens</t>
-  </si>
-  <si>
-    <t>M2x0.4 screws, 10 mm</t>
-  </si>
-  <si>
-    <t>M2x0.4 nuts</t>
-  </si>
-  <si>
-    <t>91292A833</t>
-  </si>
-  <si>
-    <t>https://www.mcmaster.com/91292A833/</t>
-  </si>
-  <si>
-    <t>https://www.mcmaster.com/91828A111/</t>
-  </si>
-  <si>
-    <t>91828A111</t>
-  </si>
-  <si>
-    <t>3D printed, resin</t>
-  </si>
-  <si>
-    <t>Electrical Box 12V</t>
-  </si>
-  <si>
-    <t>Note</t>
+    <t>91292A115</t>
   </si>
   <si>
     <t>M3x0.5 screws, 16 mm</t>
   </si>
   <si>
+    <t>https://www.mcmaster.com/91292A115/</t>
+  </si>
+  <si>
     <t>M3x0.5 nut</t>
   </si>
   <si>
-    <t>https://www.mcmaster.com/91292A115/</t>
-  </si>
-  <si>
-    <t>91292A115</t>
-  </si>
-  <si>
     <t>12V, &gt;2W power supply</t>
   </si>
   <si>
-    <t>Blunt Needle for Tethering</t>
-  </si>
-  <si>
-    <t>Optostim light rail holder</t>
-  </si>
-  <si>
-    <t>USB3 Micro B to USB cable</t>
-  </si>
-  <si>
-    <t>https://www.amazon.com/External-Seagate-Toshiba-Western-Passport/dp/B0F1N5W6VW/ref=sr_1_1_sspa</t>
-  </si>
-  <si>
-    <t>https://www.amazon.com/Smays-5-Pack-Micro-Transfer-Charging/dp/B0DZ6QRRHJ/ref=sr_1_2_sspa</t>
-  </si>
-  <si>
-    <t>Barrel jack power supply (5V, 10A)</t>
-  </si>
-  <si>
-    <t>Micro USB to USB cable</t>
+    <t>8505K721</t>
   </si>
   <si>
     <t>12" x 12" Acrylic sheet</t>
   </si>
   <si>
-    <t>8505K721</t>
-  </si>
-  <si>
     <t>https://www.mcmaster.com/8505K721-8505K112/</t>
   </si>
   <si>
-    <t>70 mm circular heating pad</t>
-  </si>
-  <si>
-    <t>https://www.amazon.com/XIITIA-70mmx70mm-Adhesive-Elements-Polyimide/dp/B0D5DC9VWB/ref=sr_1_2?</t>
-  </si>
-  <si>
-    <t>Heating baseplate</t>
-  </si>
-  <si>
     <t>12"x12" is enough for 2 laser cut boxes, or one box and the heating baseplate. Color choice up to the user</t>
+  </si>
+  <si>
+    <t>https://www.mcmaster.com/5779K108/</t>
+  </si>
+  <si>
+    <t>Push-to-Connect Tube Fitting for Air, Straight Adapter, for 1/4" Tube OD x 1/8 NPT Male</t>
+  </si>
+  <si>
+    <t>5779K108</t>
   </si>
 </sst>
 </file>
@@ -518,10 +548,10 @@
   </borders>
   <cellStyleXfs count="3">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
-    <xf numFmtId="44" fontId="1" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="44" fontId="1" fillId="0" borderId="0"/>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="7">
+  <cellXfs count="8">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="44" fontId="0" fillId="0" borderId="0" xfId="1" applyFont="1"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
@@ -532,24 +562,22 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="2" applyFill="1"/>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="44" fontId="0" fillId="0" borderId="0" xfId="1" applyFont="1" applyFill="1"/>
   </cellXfs>
   <cellStyles count="3">
     <cellStyle name="Currency" xfId="1" builtinId="4"/>
     <cellStyle name="Hyperlink" xfId="2" builtinId="8"/>
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
   </cellStyles>
-  <dxfs count="3">
+  <dxfs count="4">
     <dxf>
       <font>
-        <b val="0"/>
-        <i val="0"/>
         <strike val="0"/>
         <condense val="0"/>
         <extend val="0"/>
         <outline val="0"/>
         <shadow val="0"/>
-        <u val="none"/>
         <vertAlign val="baseline"/>
         <sz val="12"/>
         <color theme="1"/>
@@ -560,14 +588,11 @@
     </dxf>
     <dxf>
       <font>
-        <b val="0"/>
-        <i val="0"/>
         <strike val="0"/>
         <condense val="0"/>
         <extend val="0"/>
         <outline val="0"/>
         <shadow val="0"/>
-        <u val="none"/>
         <vertAlign val="baseline"/>
         <sz val="12"/>
         <color theme="1"/>
@@ -577,7 +602,10 @@
       </font>
     </dxf>
     <dxf>
-      <alignment horizontal="left" vertical="bottom" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+      <alignment horizontal="left" vertical="bottom"/>
+    </dxf>
+    <dxf>
+      <alignment horizontal="left" vertical="bottom"/>
     </dxf>
   </dxfs>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium2" defaultPivotStyle="PivotStyleLight16"/>
@@ -593,22 +621,22 @@
 </file>
 
 <file path=xl/tables/table1.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="1" xr:uid="{031F9794-3422-E94F-8BF0-DD73732413E3}" name="Table1" displayName="Table1" ref="A10:K62" totalsRowShown="0">
-  <autoFilter ref="A10:K62" xr:uid="{031F9794-3422-E94F-8BF0-DD73732413E3}"/>
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="1" xr:uid="{00000000-000C-0000-FFFF-FFFF00000000}" name="Table1" displayName="Table1" ref="A10:K63" totalsRowShown="0">
+  <autoFilter ref="A10:K63" xr:uid="{00000000-0009-0000-0100-000001000000}"/>
   <tableColumns count="11">
-    <tableColumn id="1" xr3:uid="{B56D842A-6524-6042-A636-27D25523BBC2}" name="Category"/>
-    <tableColumn id="9" xr3:uid="{A5067F63-B27C-2445-8796-A1DED8D638AE}" name="Subassembly"/>
-    <tableColumn id="2" xr3:uid="{9DD3C2A2-C34C-7B4C-86FE-FB0DCD196ADD}" name="Part No." dataDxfId="2"/>
-    <tableColumn id="7" xr3:uid="{7DA51295-7121-D94A-8431-445E594AFC08}" name="Part Name"/>
-    <tableColumn id="3" xr3:uid="{F134BF34-512E-8641-9585-99339119CC82}" name="Supplier"/>
-    <tableColumn id="4" xr3:uid="{605B3DEE-242F-4E44-A370-2658F0B921A5}" name="Qty"/>
-    <tableColumn id="8" xr3:uid="{FA37817B-123A-6A46-AC4B-2C15D8E84883}" name="Units"/>
-    <tableColumn id="5" xr3:uid="{27BC1AA3-7A39-0F48-B5EB-C8C877F8F656}" name="Unit Cost" dataDxfId="1" dataCellStyle="Currency"/>
-    <tableColumn id="6" xr3:uid="{24B69E50-898A-7A4D-9161-94EDA1BF9959}" name="Cost" dataDxfId="0" dataCellStyle="Currency">
+    <tableColumn id="1" xr3:uid="{00000000-0010-0000-0000-000001000000}" name="Category"/>
+    <tableColumn id="9" xr3:uid="{00000000-0010-0000-0000-000009000000}" name="Subassembly"/>
+    <tableColumn id="2" xr3:uid="{00000000-0010-0000-0000-000002000000}" name="Part No." dataDxfId="3"/>
+    <tableColumn id="7" xr3:uid="{00000000-0010-0000-0000-000007000000}" name="Part Name"/>
+    <tableColumn id="3" xr3:uid="{00000000-0010-0000-0000-000003000000}" name="Supplier"/>
+    <tableColumn id="4" xr3:uid="{00000000-0010-0000-0000-000004000000}" name="Qty"/>
+    <tableColumn id="8" xr3:uid="{00000000-0010-0000-0000-000008000000}" name="Units" dataDxfId="2"/>
+    <tableColumn id="5" xr3:uid="{00000000-0010-0000-0000-000005000000}" name="Unit Cost" dataDxfId="1" dataCellStyle="Currency"/>
+    <tableColumn id="6" xr3:uid="{00000000-0010-0000-0000-000006000000}" name="Cost" dataDxfId="0" dataCellStyle="Currency">
       <calculatedColumnFormula>Table1[[#This Row],[Qty]]*Table1[[#This Row],[Unit Cost]]</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="10" xr3:uid="{4704FBC5-16A6-2E46-8B58-60DFB166C669}" name="Link"/>
-    <tableColumn id="13" xr3:uid="{77349C88-CEAA-F945-9E95-011D61FC3D13}" name="Note"/>
+    <tableColumn id="10" xr3:uid="{00000000-0010-0000-0000-00000A000000}" name="Link"/>
+    <tableColumn id="13" xr3:uid="{00000000-0010-0000-0000-00000D000000}" name="Note"/>
   </tableColumns>
   <tableStyleInfo name="TableStyleLight2" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
 </table>
@@ -930,8 +958,8 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{53CCC03A-E2D2-064D-930B-8D8B4BDB230C}">
-  <dimension ref="A1:K62"/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
+  <dimension ref="A1:K63"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="16" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="22" customWidth="1"/>
@@ -947,20 +975,20 @@
   <sheetData>
     <row r="1" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A1" s="2" t="s">
-        <v>8</v>
+        <v>0</v>
       </c>
       <c r="B1" t="s">
-        <v>107</v>
+        <v>1</v>
       </c>
     </row>
     <row r="2" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A2" s="2" t="s">
-        <v>9</v>
+        <v>2</v>
       </c>
     </row>
     <row r="3" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A3" s="2" t="s">
-        <v>10</v>
+        <v>3</v>
       </c>
       <c r="B3">
         <v>2</v>
@@ -968,85 +996,85 @@
     </row>
     <row r="4" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A4" s="2" t="s">
-        <v>14</v>
+        <v>4</v>
       </c>
       <c r="B4" t="s">
-        <v>15</v>
+        <v>5</v>
       </c>
     </row>
     <row r="5" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A5" s="2" t="s">
-        <v>11</v>
+        <v>6</v>
       </c>
     </row>
     <row r="6" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A6" s="2" t="s">
-        <v>12</v>
+        <v>7</v>
       </c>
       <c r="B6">
         <f>SUM(Table1[Qty])</f>
-        <v>101.5</v>
+        <v>104.5</v>
       </c>
     </row>
     <row r="7" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A7" s="2" t="s">
-        <v>13</v>
+        <v>8</v>
       </c>
       <c r="B7" s="3">
         <f>SUM(Table1[Cost])</f>
-        <v>583.59019999999987</v>
+        <v>588.54019999999991</v>
       </c>
     </row>
     <row r="10" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A10" t="s">
-        <v>3</v>
+        <v>9</v>
       </c>
       <c r="B10" t="s">
+        <v>10</v>
+      </c>
+      <c r="C10" s="5" t="s">
+        <v>11</v>
+      </c>
+      <c r="D10" t="s">
+        <v>12</v>
+      </c>
+      <c r="E10" t="s">
+        <v>13</v>
+      </c>
+      <c r="F10" t="s">
+        <v>14</v>
+      </c>
+      <c r="G10" t="s">
+        <v>15</v>
+      </c>
+      <c r="H10" s="1" t="s">
+        <v>16</v>
+      </c>
+      <c r="I10" s="1" t="s">
+        <v>17</v>
+      </c>
+      <c r="J10" t="s">
         <v>18</v>
       </c>
-      <c r="C10" s="5" t="s">
-        <v>0</v>
-      </c>
-      <c r="D10" t="s">
-        <v>4</v>
-      </c>
-      <c r="E10" t="s">
-        <v>7</v>
-      </c>
-      <c r="F10" t="s">
-        <v>1</v>
-      </c>
-      <c r="G10" t="s">
-        <v>5</v>
-      </c>
-      <c r="H10" s="1" t="s">
-        <v>6</v>
-      </c>
-      <c r="I10" s="1" t="s">
-        <v>2</v>
-      </c>
-      <c r="J10" t="s">
-        <v>22</v>
-      </c>
       <c r="K10" t="s">
-        <v>120</v>
+        <v>19</v>
       </c>
     </row>
     <row r="11" spans="1:11" x14ac:dyDescent="0.2">
       <c r="C11" s="5" t="s">
-        <v>50</v>
+        <v>20</v>
       </c>
       <c r="D11" t="s">
-        <v>16</v>
+        <v>21</v>
       </c>
       <c r="E11" t="s">
-        <v>17</v>
+        <v>22</v>
       </c>
       <c r="F11">
         <v>1</v>
       </c>
-      <c r="G11" t="s">
-        <v>21</v>
+      <c r="G11" s="5" t="s">
+        <v>23</v>
       </c>
       <c r="H11" s="1">
         <v>184.47</v>
@@ -1056,48 +1084,48 @@
         <v>184.47</v>
       </c>
       <c r="J11" s="4" t="s">
-        <v>49</v>
+        <v>24</v>
       </c>
     </row>
     <row r="12" spans="1:11" x14ac:dyDescent="0.2">
       <c r="B12" t="s">
-        <v>51</v>
+        <v>25</v>
       </c>
       <c r="D12" t="s">
-        <v>51</v>
+        <v>25</v>
       </c>
       <c r="F12">
         <v>1</v>
       </c>
-      <c r="G12" t="s">
-        <v>21</v>
+      <c r="G12" s="5" t="s">
+        <v>23</v>
       </c>
       <c r="I12" s="1">
         <f>Table1[[#This Row],[Qty]]*Table1[[#This Row],[Unit Cost]]</f>
         <v>0</v>
       </c>
       <c r="J12" s="4" t="s">
-        <v>105</v>
+        <v>26</v>
       </c>
     </row>
     <row r="13" spans="1:11" x14ac:dyDescent="0.2">
       <c r="B13" t="s">
-        <v>51</v>
+        <v>25</v>
       </c>
       <c r="C13" s="5" t="s">
-        <v>57</v>
+        <v>27</v>
       </c>
       <c r="D13" t="s">
-        <v>55</v>
+        <v>28</v>
       </c>
       <c r="E13" t="s">
-        <v>17</v>
+        <v>22</v>
       </c>
       <c r="F13">
         <v>4</v>
       </c>
-      <c r="G13" t="s">
-        <v>21</v>
+      <c r="G13" s="5" t="s">
+        <v>23</v>
       </c>
       <c r="H13" s="1">
         <v>5.76</v>
@@ -1107,30 +1135,30 @@
         <v>23.04</v>
       </c>
       <c r="J13" s="4" t="s">
-        <v>56</v>
+        <v>29</v>
       </c>
     </row>
     <row r="14" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A14" t="s">
-        <v>20</v>
+        <v>30</v>
       </c>
       <c r="B14" t="s">
-        <v>51</v>
+        <v>25</v>
       </c>
       <c r="C14" s="5" t="s">
-        <v>102</v>
+        <v>31</v>
       </c>
       <c r="D14" t="s">
-        <v>101</v>
+        <v>32</v>
       </c>
       <c r="E14" t="s">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="F14">
         <v>4</v>
       </c>
-      <c r="G14" t="s">
-        <v>21</v>
+      <c r="G14" s="5" t="s">
+        <v>23</v>
       </c>
       <c r="H14" s="1">
         <f>14.44/100</f>
@@ -1141,30 +1169,30 @@
         <v>0.5776</v>
       </c>
       <c r="J14" s="4" t="s">
-        <v>103</v>
+        <v>34</v>
       </c>
     </row>
     <row r="15" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A15" t="s">
-        <v>20</v>
+        <v>30</v>
       </c>
       <c r="B15" t="s">
-        <v>51</v>
+        <v>25</v>
       </c>
       <c r="C15" s="5" t="s">
-        <v>94</v>
+        <v>35</v>
       </c>
       <c r="D15" t="s">
-        <v>90</v>
+        <v>36</v>
       </c>
       <c r="E15" t="s">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="F15">
         <v>8</v>
       </c>
-      <c r="G15" t="s">
-        <v>21</v>
+      <c r="G15" s="5" t="s">
+        <v>23</v>
       </c>
       <c r="H15" s="1">
         <f>2.02/100</f>
@@ -1175,49 +1203,51 @@
         <v>0.16159999999999999</v>
       </c>
       <c r="J15" s="4" t="s">
-        <v>58</v>
+        <v>37</v>
       </c>
     </row>
     <row r="16" spans="1:11" x14ac:dyDescent="0.2">
       <c r="B16" t="s">
-        <v>51</v>
+        <v>25</v>
       </c>
       <c r="C16" s="5" t="s">
-        <v>60</v>
+        <v>38</v>
       </c>
       <c r="D16" t="s">
-        <v>61</v>
+        <v>39</v>
       </c>
       <c r="E16" t="s">
-        <v>62</v>
+        <v>40</v>
       </c>
       <c r="F16">
         <v>4</v>
       </c>
-      <c r="G16" t="s">
-        <v>35</v>
+      <c r="G16" s="5" t="s">
+        <v>41</v>
       </c>
       <c r="I16" s="1">
         <f>Table1[[#This Row],[Qty]]*Table1[[#This Row],[Unit Cost]]</f>
         <v>0</v>
       </c>
-      <c r="J16" s="4"/>
+      <c r="J16" s="4" t="s">
+        <v>42</v>
+      </c>
     </row>
     <row r="17" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A17" t="s">
-        <v>87</v>
+        <v>43</v>
       </c>
       <c r="B17" t="s">
-        <v>51</v>
+        <v>25</v>
       </c>
       <c r="D17" t="s">
-        <v>131</v>
+        <v>44</v>
       </c>
       <c r="F17">
         <v>1</v>
       </c>
-      <c r="G17" t="s">
-        <v>21</v>
+      <c r="G17" s="5" t="s">
+        <v>23</v>
       </c>
       <c r="I17" s="1">
         <f>Table1[[#This Row],[Qty]]*Table1[[#This Row],[Unit Cost]]</f>
@@ -1227,19 +1257,19 @@
     </row>
     <row r="18" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A18" t="s">
-        <v>87</v>
+        <v>43</v>
       </c>
       <c r="B18" t="s">
-        <v>51</v>
+        <v>25</v>
       </c>
       <c r="D18" t="s">
-        <v>132</v>
+        <v>45</v>
       </c>
       <c r="F18">
         <v>1</v>
       </c>
-      <c r="G18" t="s">
-        <v>21</v>
+      <c r="G18" s="5" t="s">
+        <v>23</v>
       </c>
       <c r="H18" s="1">
         <v>4.5</v>
@@ -1249,30 +1279,30 @@
         <v>4.5</v>
       </c>
       <c r="J18" s="4" t="s">
-        <v>130</v>
+        <v>46</v>
       </c>
     </row>
     <row r="19" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A19" t="s">
-        <v>20</v>
+        <v>30</v>
       </c>
       <c r="B19" t="s">
-        <v>19</v>
+        <v>47</v>
       </c>
       <c r="C19" s="5" t="s">
-        <v>91</v>
+        <v>48</v>
       </c>
       <c r="D19" t="s">
-        <v>92</v>
+        <v>49</v>
       </c>
       <c r="E19" t="s">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="F19">
         <v>4</v>
       </c>
-      <c r="G19" t="s">
-        <v>21</v>
+      <c r="G19" s="5" t="s">
+        <v>23</v>
       </c>
       <c r="H19" s="1">
         <f>13.88/25</f>
@@ -1283,30 +1313,30 @@
         <v>2.2208000000000001</v>
       </c>
       <c r="J19" s="4" t="s">
-        <v>93</v>
+        <v>50</v>
       </c>
     </row>
     <row r="20" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A20" t="s">
-        <v>20</v>
+        <v>30</v>
       </c>
       <c r="B20" t="s">
-        <v>19</v>
+        <v>47</v>
       </c>
       <c r="C20" s="5" t="s">
-        <v>94</v>
+        <v>35</v>
       </c>
       <c r="D20" t="s">
-        <v>90</v>
+        <v>36</v>
       </c>
       <c r="E20" t="s">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="F20">
         <v>4</v>
       </c>
-      <c r="G20" t="s">
-        <v>21</v>
+      <c r="G20" s="5" t="s">
+        <v>23</v>
       </c>
       <c r="H20" s="1">
         <v>0.02</v>
@@ -1315,31 +1345,31 @@
         <f>Table1[[#This Row],[Qty]]*Table1[[#This Row],[Unit Cost]]</f>
         <v>0.08</v>
       </c>
-      <c r="J20" s="6" t="s">
-        <v>58</v>
+      <c r="J20" s="4" t="s">
+        <v>37</v>
       </c>
     </row>
     <row r="21" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A21" t="s">
-        <v>20</v>
+        <v>30</v>
       </c>
       <c r="B21" t="s">
+        <v>25</v>
+      </c>
+      <c r="C21" s="5" t="s">
         <v>51</v>
       </c>
-      <c r="C21" s="5" t="s">
-        <v>96</v>
-      </c>
       <c r="D21" t="s">
-        <v>95</v>
+        <v>52</v>
       </c>
       <c r="E21" t="s">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="F21">
         <v>4</v>
       </c>
-      <c r="G21" t="s">
-        <v>21</v>
+      <c r="G21" s="5" t="s">
+        <v>23</v>
       </c>
       <c r="H21" s="1">
         <f>14.83/100</f>
@@ -1350,27 +1380,27 @@
         <v>0.59319999999999995</v>
       </c>
       <c r="J21" s="4" t="s">
-        <v>97</v>
+        <v>53</v>
       </c>
     </row>
     <row r="22" spans="1:10" x14ac:dyDescent="0.2">
       <c r="B22" t="s">
-        <v>19</v>
+        <v>47</v>
       </c>
       <c r="C22" s="5" t="s">
-        <v>98</v>
+        <v>54</v>
       </c>
       <c r="D22" t="s">
-        <v>99</v>
+        <v>55</v>
       </c>
       <c r="E22" t="s">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="F22">
         <v>1</v>
       </c>
-      <c r="G22" t="s">
-        <v>21</v>
+      <c r="G22" s="5" t="s">
+        <v>23</v>
       </c>
       <c r="H22" s="1">
         <v>2.89</v>
@@ -1380,146 +1410,152 @@
         <v>2.89</v>
       </c>
       <c r="J22" s="4" t="s">
-        <v>100</v>
+        <v>56</v>
       </c>
     </row>
     <row r="23" spans="1:10" x14ac:dyDescent="0.2">
       <c r="B23" t="s">
-        <v>19</v>
+        <v>47</v>
       </c>
       <c r="D23" t="s">
-        <v>127</v>
+        <v>57</v>
       </c>
       <c r="E23" t="s">
-        <v>62</v>
+        <v>40</v>
       </c>
       <c r="F23">
         <v>2</v>
       </c>
-      <c r="G23" t="s">
-        <v>21</v>
+      <c r="G23" s="5" t="s">
+        <v>23</v>
       </c>
       <c r="I23" s="1">
         <f>Table1[[#This Row],[Qty]]*Table1[[#This Row],[Unit Cost]]</f>
         <v>0</v>
       </c>
-      <c r="J23" s="4"/>
+      <c r="J23" s="4" t="s">
+        <v>58</v>
+      </c>
     </row>
     <row r="24" spans="1:10" x14ac:dyDescent="0.2">
       <c r="B24" t="s">
-        <v>19</v>
+        <v>47</v>
       </c>
       <c r="D24" t="s">
-        <v>73</v>
+        <v>59</v>
       </c>
       <c r="E24" t="s">
-        <v>62</v>
+        <v>40</v>
       </c>
       <c r="F24">
         <v>1</v>
       </c>
-      <c r="G24" t="s">
-        <v>21</v>
+      <c r="G24" s="5" t="s">
+        <v>23</v>
       </c>
       <c r="I24" s="1">
         <f>Table1[[#This Row],[Qty]]*Table1[[#This Row],[Unit Cost]]</f>
         <v>0</v>
       </c>
-      <c r="J24" s="4"/>
+      <c r="J24" s="4" t="s">
+        <v>60</v>
+      </c>
     </row>
     <row r="25" spans="1:10" x14ac:dyDescent="0.2">
       <c r="B25" t="s">
-        <v>19</v>
+        <v>47</v>
       </c>
       <c r="D25" t="s">
-        <v>83</v>
+        <v>61</v>
       </c>
       <c r="E25" t="s">
+        <v>40</v>
+      </c>
+      <c r="F25">
+        <v>1</v>
+      </c>
+      <c r="G25" s="5" t="s">
+        <v>23</v>
+      </c>
+      <c r="I25" s="1">
+        <f>Table1[[#This Row],[Qty]]*Table1[[#This Row],[Unit Cost]]</f>
+        <v>0</v>
+      </c>
+      <c r="J25" s="4" t="s">
         <v>62</v>
       </c>
-      <c r="F25">
-        <v>1</v>
-      </c>
-      <c r="G25" t="s">
-        <v>21</v>
-      </c>
-      <c r="I25" s="1">
-        <f>Table1[[#This Row],[Qty]]*Table1[[#This Row],[Unit Cost]]</f>
-        <v>0</v>
-      </c>
-      <c r="J25" s="4"/>
     </row>
     <row r="26" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A26" t="s">
-        <v>87</v>
+        <v>43</v>
       </c>
       <c r="B26" t="s">
-        <v>19</v>
+        <v>47</v>
       </c>
       <c r="D26" t="s">
-        <v>106</v>
+        <v>63</v>
       </c>
       <c r="F26">
         <v>1</v>
       </c>
-      <c r="G26"/>
+      <c r="G26" s="5"/>
       <c r="I26" s="1"/>
       <c r="J26" s="4"/>
     </row>
     <row r="27" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A27" t="s">
-        <v>87</v>
+        <v>43</v>
       </c>
       <c r="B27" t="s">
-        <v>19</v>
+        <v>47</v>
       </c>
       <c r="D27" t="s">
-        <v>72</v>
+        <v>64</v>
       </c>
       <c r="F27">
         <v>1</v>
       </c>
-      <c r="G27"/>
+      <c r="G27" s="5"/>
       <c r="I27" s="1"/>
       <c r="J27" s="4"/>
     </row>
     <row r="28" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A28" t="s">
-        <v>87</v>
+        <v>43</v>
       </c>
       <c r="B28" t="s">
-        <v>19</v>
+        <v>47</v>
       </c>
       <c r="D28" t="s">
-        <v>71</v>
+        <v>65</v>
       </c>
       <c r="F28">
         <v>1</v>
       </c>
-      <c r="G28" t="s">
-        <v>21</v>
+      <c r="G28" s="5" t="s">
+        <v>23</v>
       </c>
       <c r="I28" s="1"/>
       <c r="J28" s="4"/>
     </row>
     <row r="29" spans="1:10" x14ac:dyDescent="0.2">
       <c r="B29" t="s">
-        <v>19</v>
+        <v>47</v>
       </c>
       <c r="C29" s="5" t="s">
-        <v>78</v>
+        <v>66</v>
       </c>
       <c r="D29" t="s">
-        <v>75</v>
+        <v>67</v>
       </c>
       <c r="E29" t="s">
-        <v>69</v>
+        <v>68</v>
       </c>
       <c r="F29">
         <v>1</v>
       </c>
-      <c r="G29" t="s">
-        <v>21</v>
+      <c r="G29" s="5" t="s">
+        <v>23</v>
       </c>
       <c r="H29" s="1">
         <v>11.34</v>
@@ -1529,27 +1565,27 @@
         <v>11.34</v>
       </c>
       <c r="J29" s="4" t="s">
-        <v>74</v>
+        <v>69</v>
       </c>
     </row>
     <row r="30" spans="1:10" x14ac:dyDescent="0.2">
       <c r="B30" t="s">
-        <v>19</v>
+        <v>47</v>
       </c>
       <c r="C30" s="5" t="s">
-        <v>82</v>
+        <v>70</v>
       </c>
       <c r="D30" t="s">
-        <v>81</v>
+        <v>71</v>
       </c>
       <c r="E30" t="s">
-        <v>69</v>
+        <v>68</v>
       </c>
       <c r="F30">
         <v>1</v>
       </c>
-      <c r="G30" t="s">
-        <v>21</v>
+      <c r="G30" s="5" t="s">
+        <v>23</v>
       </c>
       <c r="H30" s="1">
         <v>5.14</v>
@@ -1561,22 +1597,22 @@
     </row>
     <row r="31" spans="1:10" x14ac:dyDescent="0.2">
       <c r="B31" t="s">
-        <v>19</v>
+        <v>47</v>
       </c>
       <c r="C31" s="5">
         <v>10193</v>
       </c>
       <c r="D31" t="s">
-        <v>79</v>
+        <v>72</v>
       </c>
       <c r="E31" t="s">
-        <v>69</v>
+        <v>68</v>
       </c>
       <c r="F31">
         <v>1</v>
       </c>
-      <c r="G31" t="s">
-        <v>21</v>
+      <c r="G31" s="5" t="s">
+        <v>23</v>
       </c>
       <c r="H31" s="1">
         <v>1.71</v>
@@ -1588,25 +1624,25 @@
     </row>
     <row r="32" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A32" t="s">
-        <v>20</v>
+        <v>30</v>
       </c>
       <c r="B32" t="s">
-        <v>19</v>
+        <v>47</v>
       </c>
       <c r="C32" s="5" t="s">
-        <v>77</v>
+        <v>73</v>
       </c>
       <c r="D32" t="s">
-        <v>76</v>
+        <v>74</v>
       </c>
       <c r="E32" t="s">
-        <v>69</v>
+        <v>68</v>
       </c>
       <c r="F32">
         <v>1</v>
       </c>
-      <c r="G32" t="s">
-        <v>21</v>
+      <c r="G32" s="5" t="s">
+        <v>23</v>
       </c>
       <c r="H32" s="1">
         <v>1.92</v>
@@ -1618,25 +1654,25 @@
     </row>
     <row r="33" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A33" t="s">
-        <v>87</v>
+        <v>43</v>
       </c>
       <c r="B33" t="s">
-        <v>19</v>
+        <v>47</v>
       </c>
       <c r="C33" s="5" t="s">
-        <v>80</v>
+        <v>75</v>
       </c>
       <c r="D33" t="s">
-        <v>70</v>
+        <v>76</v>
       </c>
       <c r="E33" t="s">
-        <v>69</v>
+        <v>68</v>
       </c>
       <c r="F33">
         <v>1</v>
       </c>
-      <c r="G33" t="s">
-        <v>21</v>
+      <c r="G33" s="5" t="s">
+        <v>23</v>
       </c>
       <c r="H33" s="1">
         <v>17.239999999999998</v>
@@ -1648,25 +1684,25 @@
     </row>
     <row r="34" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A34" t="s">
-        <v>87</v>
+        <v>43</v>
       </c>
       <c r="B34" t="s">
-        <v>19</v>
+        <v>47</v>
       </c>
       <c r="C34" s="5" t="s">
-        <v>85</v>
+        <v>77</v>
       </c>
       <c r="D34" t="s">
-        <v>84</v>
+        <v>78</v>
       </c>
       <c r="E34" t="s">
-        <v>69</v>
+        <v>68</v>
       </c>
       <c r="F34">
         <v>1</v>
       </c>
-      <c r="G34" t="s">
-        <v>21</v>
+      <c r="G34" s="5" t="s">
+        <v>23</v>
       </c>
       <c r="H34" s="1">
         <v>2.56</v>
@@ -1678,19 +1714,19 @@
     </row>
     <row r="35" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A35" t="s">
-        <v>87</v>
+        <v>43</v>
       </c>
       <c r="B35" t="s">
-        <v>19</v>
+        <v>47</v>
       </c>
       <c r="D35" t="s">
-        <v>68</v>
+        <v>79</v>
       </c>
       <c r="F35">
         <v>1</v>
       </c>
-      <c r="G35" t="s">
-        <v>21</v>
+      <c r="G35" s="5" t="s">
+        <v>23</v>
       </c>
       <c r="I35" s="1">
         <f>Table1[[#This Row],[Qty]]*Table1[[#This Row],[Unit Cost]]</f>
@@ -1699,16 +1735,16 @@
     </row>
     <row r="36" spans="1:10" x14ac:dyDescent="0.2">
       <c r="B36" t="s">
-        <v>23</v>
+        <v>80</v>
       </c>
       <c r="D36" t="s">
-        <v>24</v>
+        <v>81</v>
       </c>
       <c r="F36">
         <v>1</v>
       </c>
-      <c r="G36" t="s">
-        <v>21</v>
+      <c r="G36" s="5" t="s">
+        <v>23</v>
       </c>
       <c r="H36" s="1">
         <v>80</v>
@@ -1720,19 +1756,19 @@
     </row>
     <row r="37" spans="1:10" x14ac:dyDescent="0.2">
       <c r="B37" t="s">
-        <v>23</v>
+        <v>80</v>
       </c>
       <c r="D37" t="s">
-        <v>88</v>
+        <v>82</v>
       </c>
       <c r="E37" t="s">
-        <v>62</v>
+        <v>40</v>
       </c>
       <c r="F37">
         <v>1</v>
       </c>
-      <c r="G37" t="s">
-        <v>21</v>
+      <c r="G37" s="5" t="s">
+        <v>23</v>
       </c>
       <c r="I37" s="1">
         <f>Table1[[#This Row],[Qty]]*Table1[[#This Row],[Unit Cost]]</f>
@@ -1741,58 +1777,64 @@
     </row>
     <row r="38" spans="1:10" x14ac:dyDescent="0.2">
       <c r="B38" t="s">
-        <v>23</v>
+        <v>80</v>
       </c>
       <c r="D38" t="s">
-        <v>25</v>
+        <v>83</v>
       </c>
       <c r="E38" t="s">
-        <v>62</v>
+        <v>40</v>
       </c>
       <c r="F38">
         <v>1</v>
       </c>
-      <c r="G38" t="s">
-        <v>35</v>
+      <c r="G38" s="5" t="s">
+        <v>23</v>
       </c>
       <c r="I38" s="1">
         <f>Table1[[#This Row],[Qty]]*Table1[[#This Row],[Unit Cost]]</f>
         <v>0</v>
+      </c>
+      <c r="J38" s="6" t="s">
+        <v>84</v>
       </c>
     </row>
     <row r="39" spans="1:10" x14ac:dyDescent="0.2">
       <c r="B39" t="s">
-        <v>23</v>
+        <v>80</v>
       </c>
       <c r="D39" t="s">
+        <v>85</v>
+      </c>
+      <c r="E39" t="s">
+        <v>40</v>
+      </c>
+      <c r="F39">
+        <v>1</v>
+      </c>
+      <c r="G39" s="5" t="s">
+        <v>23</v>
+      </c>
+      <c r="I39" s="1">
+        <f>Table1[[#This Row],[Qty]]*Table1[[#This Row],[Unit Cost]]</f>
+        <v>0</v>
+      </c>
+      <c r="J39" s="6" t="s">
         <v>86</v>
-      </c>
-      <c r="E39" t="s">
-        <v>62</v>
-      </c>
-      <c r="F39">
-        <v>1</v>
-      </c>
-      <c r="G39" t="s">
-        <v>35</v>
-      </c>
-      <c r="I39" s="1">
-        <f>Table1[[#This Row],[Qty]]*Table1[[#This Row],[Unit Cost]]</f>
-        <v>0</v>
       </c>
     </row>
     <row r="40" spans="1:10" x14ac:dyDescent="0.2">
       <c r="B40" t="s">
-        <v>23</v>
+        <v>80</v>
       </c>
       <c r="D40" t="s">
-        <v>126</v>
+        <v>87</v>
       </c>
       <c r="F40">
         <v>1</v>
       </c>
-      <c r="G40" t="s">
-        <v>21</v>
+      <c r="G40" s="5" t="s">
+        <v>23</v>
       </c>
       <c r="I40" s="1">
         <f>Table1[[#This Row],[Qty]]*Table1[[#This Row],[Unit Cost]]</f>
@@ -1801,25 +1843,25 @@
     </row>
     <row r="41" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A41" t="s">
-        <v>20</v>
+        <v>30</v>
       </c>
       <c r="B41" t="s">
-        <v>23</v>
+        <v>80</v>
       </c>
       <c r="C41" s="5" t="s">
-        <v>44</v>
+        <v>88</v>
       </c>
       <c r="D41" t="s">
-        <v>39</v>
+        <v>89</v>
       </c>
       <c r="E41" t="s">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="F41">
         <v>5</v>
       </c>
-      <c r="G41" t="s">
-        <v>21</v>
+      <c r="G41" s="5" t="s">
+        <v>23</v>
       </c>
       <c r="H41" s="1">
         <f>17.78/100</f>
@@ -1830,30 +1872,30 @@
         <v>0.88900000000000001</v>
       </c>
       <c r="J41" s="4" t="s">
-        <v>38</v>
+        <v>90</v>
       </c>
     </row>
     <row r="42" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A42" t="s">
-        <v>20</v>
+        <v>30</v>
       </c>
       <c r="B42" t="s">
-        <v>23</v>
+        <v>80</v>
       </c>
       <c r="C42" s="5" t="s">
-        <v>46</v>
+        <v>91</v>
       </c>
       <c r="D42" t="s">
-        <v>40</v>
+        <v>92</v>
       </c>
       <c r="E42" t="s">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="F42">
         <v>1</v>
       </c>
-      <c r="G42" t="s">
-        <v>21</v>
+      <c r="G42" s="5" t="s">
+        <v>23</v>
       </c>
       <c r="H42" s="1">
         <f>3.06/100</f>
@@ -1864,30 +1906,30 @@
         <v>3.0600000000000002E-2</v>
       </c>
       <c r="J42" s="4" t="s">
-        <v>45</v>
+        <v>93</v>
       </c>
     </row>
     <row r="43" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A43" t="s">
-        <v>26</v>
+        <v>94</v>
       </c>
       <c r="B43" t="s">
-        <v>26</v>
+        <v>94</v>
       </c>
       <c r="C43" s="5" t="s">
-        <v>29</v>
+        <v>95</v>
       </c>
       <c r="D43" t="s">
-        <v>30</v>
+        <v>96</v>
       </c>
       <c r="E43" t="s">
-        <v>28</v>
+        <v>97</v>
       </c>
       <c r="F43">
         <v>1</v>
       </c>
-      <c r="G43" s="1" t="s">
-        <v>21</v>
+      <c r="G43" s="5" t="s">
+        <v>23</v>
       </c>
       <c r="H43" s="1">
         <v>229</v>
@@ -1897,15 +1939,21 @@
         <v>229</v>
       </c>
       <c r="J43" s="4" t="s">
-        <v>59</v>
+        <v>98</v>
       </c>
     </row>
     <row r="44" spans="1:10" x14ac:dyDescent="0.2">
       <c r="B44" t="s">
-        <v>26</v>
+        <v>94</v>
       </c>
       <c r="D44" t="s">
-        <v>111</v>
+        <v>99</v>
+      </c>
+      <c r="F44">
+        <v>1</v>
+      </c>
+      <c r="G44" s="5" t="s">
+        <v>23</v>
       </c>
       <c r="I44" s="1">
         <f>Table1[[#This Row],[Qty]]*Table1[[#This Row],[Unit Cost]]</f>
@@ -1915,25 +1963,25 @@
     </row>
     <row r="45" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A45" t="s">
-        <v>20</v>
+        <v>30</v>
       </c>
       <c r="B45" t="s">
-        <v>26</v>
+        <v>94</v>
       </c>
       <c r="C45" s="5" t="s">
-        <v>43</v>
+        <v>100</v>
       </c>
       <c r="D45" t="s">
-        <v>34</v>
+        <v>101</v>
       </c>
       <c r="E45" t="s">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="F45">
         <v>6</v>
       </c>
-      <c r="G45" s="1" t="s">
-        <v>21</v>
+      <c r="G45" s="5" t="s">
+        <v>23</v>
       </c>
       <c r="H45" s="1">
         <f>17.63/100</f>
@@ -1944,30 +1992,30 @@
         <v>1.0577999999999999</v>
       </c>
       <c r="J45" s="4" t="s">
-        <v>41</v>
+        <v>102</v>
       </c>
     </row>
     <row r="46" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A46" t="s">
-        <v>20</v>
+        <v>30</v>
       </c>
       <c r="B46" t="s">
-        <v>26</v>
+        <v>94</v>
       </c>
       <c r="C46" s="5" t="s">
-        <v>48</v>
+        <v>103</v>
       </c>
       <c r="D46" t="s">
-        <v>42</v>
+        <v>104</v>
       </c>
       <c r="E46" t="s">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="F46">
         <v>6</v>
       </c>
-      <c r="G46" s="1" t="s">
-        <v>21</v>
+      <c r="G46" s="5" t="s">
+        <v>23</v>
       </c>
       <c r="H46" s="1">
         <f>3/100</f>
@@ -1978,67 +2026,81 @@
         <v>0.18</v>
       </c>
       <c r="J46" s="4" t="s">
-        <v>47</v>
+        <v>105</v>
       </c>
     </row>
     <row r="47" spans="1:10" x14ac:dyDescent="0.2">
       <c r="B47" t="s">
-        <v>26</v>
+        <v>94</v>
       </c>
       <c r="D47" t="s">
-        <v>128</v>
+        <v>106</v>
+      </c>
+      <c r="F47">
+        <v>1</v>
+      </c>
+      <c r="G47" s="5" t="s">
+        <v>23</v>
+      </c>
+      <c r="H47" s="1">
+        <v>5</v>
       </c>
       <c r="I47" s="1">
         <f>Table1[[#This Row],[Qty]]*Table1[[#This Row],[Unit Cost]]</f>
-        <v>0</v>
-      </c>
-      <c r="J47" s="4"/>
+        <v>5</v>
+      </c>
+      <c r="J47" s="4" t="s">
+        <v>107</v>
+      </c>
     </row>
     <row r="48" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A48" t="s">
-        <v>87</v>
+        <v>43</v>
       </c>
       <c r="B48" t="s">
-        <v>27</v>
+        <v>108</v>
       </c>
       <c r="D48" t="s">
-        <v>33</v>
+        <v>109</v>
       </c>
       <c r="E48" t="s">
-        <v>118</v>
+        <v>110</v>
       </c>
       <c r="F48">
         <v>1</v>
       </c>
-      <c r="G48" s="1" t="s">
-        <v>21</v>
+      <c r="G48" s="5" t="s">
+        <v>23</v>
       </c>
       <c r="H48" s="1">
-        <v>5</v>
+        <v>0</v>
       </c>
       <c r="I48" s="1">
         <f>Table1[[#This Row],[Qty]]*Table1[[#This Row],[Unit Cost]]</f>
-        <v>5</v>
-      </c>
-      <c r="J48" s="4" t="s">
-        <v>129</v>
+        <v>0</v>
+      </c>
+      <c r="J48" s="6" t="s">
+        <v>111</v>
       </c>
     </row>
     <row r="49" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A49" t="s">
-        <v>20</v>
+        <v>30</v>
       </c>
       <c r="B49" t="s">
-        <v>27</v>
+        <v>108</v>
       </c>
       <c r="D49" t="s">
-        <v>31</v>
+        <v>112</v>
       </c>
       <c r="E49" t="s">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="F49">
         <v>2</v>
+      </c>
+      <c r="G49" s="5" t="s">
+        <v>23</v>
       </c>
       <c r="H49" s="1">
         <f>11.38/50</f>
@@ -2049,72 +2111,75 @@
         <v>0.45520000000000005</v>
       </c>
       <c r="J49" s="4" t="s">
-        <v>37</v>
+        <v>113</v>
       </c>
     </row>
     <row r="50" spans="1:11" x14ac:dyDescent="0.2">
       <c r="B50" t="s">
-        <v>27</v>
+        <v>108</v>
       </c>
       <c r="D50" t="s">
-        <v>52</v>
+        <v>114</v>
       </c>
       <c r="E50" t="s">
-        <v>53</v>
+        <v>115</v>
       </c>
       <c r="F50">
         <v>1</v>
       </c>
-      <c r="G50" s="1" t="s">
-        <v>21</v>
+      <c r="G50" s="5" t="s">
+        <v>23</v>
       </c>
       <c r="I50" s="1">
         <f>Table1[[#This Row],[Qty]]*Table1[[#This Row],[Unit Cost]]</f>
         <v>0</v>
       </c>
       <c r="J50" s="4" t="s">
-        <v>54</v>
+        <v>116</v>
       </c>
     </row>
     <row r="51" spans="1:11" x14ac:dyDescent="0.2">
       <c r="B51" t="s">
-        <v>27</v>
+        <v>108</v>
       </c>
       <c r="D51" t="s">
-        <v>104</v>
+        <v>117</v>
       </c>
       <c r="F51">
         <v>1</v>
       </c>
-      <c r="G51" s="1" t="s">
-        <v>21</v>
+      <c r="G51" s="5" t="s">
+        <v>23</v>
       </c>
       <c r="I51" s="1">
         <f>Table1[[#This Row],[Qty]]*Table1[[#This Row],[Unit Cost]]</f>
         <v>0</v>
+      </c>
+      <c r="J51" s="6" t="s">
+        <v>118</v>
       </c>
     </row>
     <row r="52" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A52" t="s">
-        <v>20</v>
+        <v>30</v>
       </c>
       <c r="B52" t="s">
-        <v>27</v>
+        <v>108</v>
       </c>
       <c r="C52" s="5" t="s">
-        <v>114</v>
+        <v>119</v>
       </c>
       <c r="D52" t="s">
-        <v>112</v>
+        <v>120</v>
       </c>
       <c r="E52" t="s">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="F52">
         <v>3</v>
       </c>
-      <c r="G52" s="1" t="s">
-        <v>21</v>
+      <c r="G52" s="5" t="s">
+        <v>23</v>
       </c>
       <c r="H52" s="1">
         <f>7.57/100</f>
@@ -2125,30 +2190,30 @@
         <v>0.22710000000000002</v>
       </c>
       <c r="J52" t="s">
-        <v>115</v>
+        <v>121</v>
       </c>
     </row>
     <row r="53" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A53" t="s">
-        <v>20</v>
+        <v>30</v>
       </c>
       <c r="B53" t="s">
-        <v>27</v>
+        <v>108</v>
       </c>
       <c r="C53" s="5" t="s">
-        <v>117</v>
+        <v>122</v>
       </c>
       <c r="D53" t="s">
-        <v>113</v>
+        <v>123</v>
       </c>
       <c r="E53" t="s">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="F53">
         <v>3</v>
       </c>
-      <c r="G53" s="1" t="s">
-        <v>21</v>
+      <c r="G53" s="5" t="s">
+        <v>23</v>
       </c>
       <c r="H53" s="1">
         <f>7.41/100</f>
@@ -2159,255 +2224,310 @@
         <v>0.2223</v>
       </c>
       <c r="J53" s="4" t="s">
-        <v>116</v>
+        <v>124</v>
       </c>
     </row>
     <row r="54" spans="1:11" x14ac:dyDescent="0.2">
       <c r="B54" t="s">
-        <v>66</v>
+        <v>108</v>
+      </c>
+      <c r="C54" s="5" t="s">
+        <v>151</v>
       </c>
       <c r="D54" t="s">
-        <v>136</v>
-      </c>
-      <c r="I54" s="1">
-        <f>Table1[[#This Row],[Qty]]*Table1[[#This Row],[Unit Cost]]</f>
-        <v>0</v>
-      </c>
-      <c r="J54" t="s">
-        <v>137</v>
+        <v>150</v>
+      </c>
+      <c r="E54" t="s">
+        <v>33</v>
+      </c>
+      <c r="F54">
+        <v>1</v>
+      </c>
+      <c r="G54" s="5" t="s">
+        <v>23</v>
+      </c>
+      <c r="H54" s="7">
+        <v>4.95</v>
+      </c>
+      <c r="I54" s="7">
+        <f>Table1[[#This Row],[Qty]]*Table1[[#This Row],[Unit Cost]]</f>
+        <v>4.95</v>
+      </c>
+      <c r="J54" s="4" t="s">
+        <v>149</v>
       </c>
     </row>
     <row r="55" spans="1:11" x14ac:dyDescent="0.2">
       <c r="B55" t="s">
-        <v>66</v>
+        <v>125</v>
       </c>
       <c r="D55" t="s">
-        <v>138</v>
-      </c>
-      <c r="F55">
-        <v>1</v>
+        <v>126</v>
+      </c>
+      <c r="G55" s="5" t="s">
+        <v>23</v>
       </c>
       <c r="I55" s="1">
         <f>Table1[[#This Row],[Qty]]*Table1[[#This Row],[Unit Cost]]</f>
         <v>0</v>
       </c>
-      <c r="K55" t="s">
-        <v>89</v>
+      <c r="J55" t="s">
+        <v>127</v>
       </c>
     </row>
     <row r="56" spans="1:11" x14ac:dyDescent="0.2">
       <c r="B56" t="s">
-        <v>66</v>
-      </c>
-      <c r="C56" s="5" t="s">
-        <v>64</v>
+        <v>125</v>
       </c>
       <c r="D56" t="s">
-        <v>63</v>
-      </c>
-      <c r="E56" t="s">
-        <v>36</v>
+        <v>128</v>
       </c>
       <c r="F56">
         <v>1</v>
       </c>
-      <c r="G56" s="1" t="s">
-        <v>21</v>
-      </c>
-      <c r="H56" s="1">
-        <v>1.08</v>
+      <c r="G56" s="5" t="s">
+        <v>23</v>
       </c>
       <c r="I56" s="1">
         <f>Table1[[#This Row],[Qty]]*Table1[[#This Row],[Unit Cost]]</f>
-        <v>1.08</v>
-      </c>
-      <c r="J56" t="s">
-        <v>65</v>
+        <v>0</v>
+      </c>
+      <c r="J56" s="6" t="s">
+        <v>129</v>
+      </c>
+      <c r="K56" t="s">
+        <v>130</v>
       </c>
     </row>
     <row r="57" spans="1:11" x14ac:dyDescent="0.2">
       <c r="B57" t="s">
-        <v>66</v>
+        <v>125</v>
+      </c>
+      <c r="C57" s="5" t="s">
+        <v>131</v>
       </c>
       <c r="D57" t="s">
-        <v>67</v>
+        <v>132</v>
+      </c>
+      <c r="E57" t="s">
+        <v>133</v>
+      </c>
+      <c r="F57">
+        <v>1</v>
+      </c>
+      <c r="G57" s="5" t="s">
+        <v>23</v>
+      </c>
+      <c r="H57" s="1">
+        <v>1.08</v>
       </c>
       <c r="I57" s="1">
         <f>Table1[[#This Row],[Qty]]*Table1[[#This Row],[Unit Cost]]</f>
+        <v>1.08</v>
+      </c>
+      <c r="J57" t="s">
+        <v>134</v>
+      </c>
+    </row>
+    <row r="58" spans="1:11" x14ac:dyDescent="0.2">
+      <c r="B58" t="s">
+        <v>125</v>
+      </c>
+      <c r="D58" t="s">
+        <v>135</v>
+      </c>
+      <c r="G58" s="5" t="s">
+        <v>23</v>
+      </c>
+      <c r="I58" s="1">
+        <f>Table1[[#This Row],[Qty]]*Table1[[#This Row],[Unit Cost]]</f>
         <v>0</v>
-      </c>
-    </row>
-    <row r="58" spans="1:11" x14ac:dyDescent="0.2">
-      <c r="A58" t="s">
-        <v>87</v>
-      </c>
-      <c r="B58" t="s">
-        <v>119</v>
-      </c>
-      <c r="C58" s="5" t="s">
-        <v>109</v>
-      </c>
-      <c r="D58" t="s">
-        <v>108</v>
-      </c>
-      <c r="E58" t="s">
-        <v>69</v>
-      </c>
-      <c r="F58">
-        <v>1</v>
-      </c>
-      <c r="G58" s="1" t="s">
-        <v>21</v>
-      </c>
-      <c r="H58" s="1">
-        <v>1.49</v>
-      </c>
-      <c r="I58" s="1">
-        <f>Table1[[#This Row],[Qty]]*Table1[[#This Row],[Unit Cost]]</f>
-        <v>1.49</v>
-      </c>
-      <c r="J58" s="4" t="s">
-        <v>110</v>
       </c>
     </row>
     <row r="59" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A59" t="s">
-        <v>20</v>
+        <v>43</v>
       </c>
       <c r="B59" t="s">
-        <v>119</v>
+        <v>136</v>
       </c>
       <c r="C59" s="5" t="s">
-        <v>124</v>
+        <v>137</v>
       </c>
       <c r="D59" t="s">
-        <v>121</v>
+        <v>138</v>
       </c>
       <c r="E59" t="s">
-        <v>32</v>
+        <v>68</v>
       </c>
       <c r="F59">
+        <v>1</v>
+      </c>
+      <c r="G59" s="5" t="s">
+        <v>23</v>
+      </c>
+      <c r="H59" s="1">
+        <v>1.49</v>
+      </c>
+      <c r="I59" s="1">
+        <f>Table1[[#This Row],[Qty]]*Table1[[#This Row],[Unit Cost]]</f>
+        <v>1.49</v>
+      </c>
+      <c r="J59" s="4" t="s">
+        <v>139</v>
+      </c>
+    </row>
+    <row r="60" spans="1:11" x14ac:dyDescent="0.2">
+      <c r="A60" t="s">
+        <v>30</v>
+      </c>
+      <c r="B60" t="s">
+        <v>136</v>
+      </c>
+      <c r="C60" s="5" t="s">
+        <v>140</v>
+      </c>
+      <c r="D60" t="s">
+        <v>141</v>
+      </c>
+      <c r="E60" t="s">
+        <v>33</v>
+      </c>
+      <c r="F60">
         <v>6</v>
       </c>
-      <c r="G59" s="1" t="s">
-        <v>21</v>
-      </c>
-      <c r="H59" s="1">
+      <c r="G60" s="5" t="s">
+        <v>23</v>
+      </c>
+      <c r="H60" s="1">
         <f>8.44/100</f>
         <v>8.4399999999999989E-2</v>
       </c>
-      <c r="I59" s="1">
+      <c r="I60" s="1">
         <f>Table1[[#This Row],[Qty]]*Table1[[#This Row],[Unit Cost]]</f>
         <v>0.50639999999999996</v>
       </c>
-      <c r="J59" s="4" t="s">
-        <v>123</v>
-      </c>
-    </row>
-    <row r="60" spans="1:11" x14ac:dyDescent="0.2">
-      <c r="A60" t="s">
-        <v>20</v>
-      </c>
-      <c r="B60" t="s">
-        <v>119</v>
-      </c>
-      <c r="C60" s="5" t="s">
-        <v>46</v>
-      </c>
-      <c r="D60" t="s">
-        <v>122</v>
-      </c>
-      <c r="E60" t="s">
-        <v>32</v>
-      </c>
-      <c r="F60">
+      <c r="J60" s="4" t="s">
+        <v>142</v>
+      </c>
+    </row>
+    <row r="61" spans="1:11" x14ac:dyDescent="0.2">
+      <c r="A61" t="s">
+        <v>30</v>
+      </c>
+      <c r="B61" t="s">
+        <v>136</v>
+      </c>
+      <c r="C61" s="5" t="s">
+        <v>91</v>
+      </c>
+      <c r="D61" t="s">
+        <v>143</v>
+      </c>
+      <c r="E61" t="s">
+        <v>33</v>
+      </c>
+      <c r="F61">
         <v>6</v>
       </c>
-      <c r="G60" t="s">
-        <v>21</v>
-      </c>
-      <c r="H60" s="1">
+      <c r="G61" s="5" t="s">
+        <v>23</v>
+      </c>
+      <c r="H61" s="1">
         <f>3.06/100</f>
         <v>3.0600000000000002E-2</v>
       </c>
-      <c r="I60" s="1">
+      <c r="I61" s="1">
         <f>Table1[[#This Row],[Qty]]*Table1[[#This Row],[Unit Cost]]</f>
         <v>0.18360000000000001</v>
       </c>
     </row>
-    <row r="61" spans="1:11" x14ac:dyDescent="0.2">
-      <c r="A61" t="s">
-        <v>87</v>
-      </c>
-      <c r="B61" t="s">
-        <v>119</v>
-      </c>
-      <c r="D61" t="s">
-        <v>125</v>
-      </c>
-      <c r="I61" s="1">
+    <row r="62" spans="1:11" x14ac:dyDescent="0.2">
+      <c r="A62" t="s">
+        <v>43</v>
+      </c>
+      <c r="B62" t="s">
+        <v>136</v>
+      </c>
+      <c r="D62" t="s">
+        <v>144</v>
+      </c>
+      <c r="G62" s="5" t="s">
+        <v>23</v>
+      </c>
+      <c r="I62" s="1">
         <f>Table1[[#This Row],[Qty]]*Table1[[#This Row],[Unit Cost]]</f>
         <v>0</v>
       </c>
     </row>
-    <row r="62" spans="1:11" x14ac:dyDescent="0.2">
-      <c r="B62" t="s">
-        <v>119</v>
-      </c>
-      <c r="C62" s="5" t="s">
-        <v>134</v>
-      </c>
-      <c r="D62" t="s">
-        <v>133</v>
-      </c>
-      <c r="E62" t="s">
-        <v>32</v>
-      </c>
-      <c r="F62">
+    <row r="63" spans="1:11" x14ac:dyDescent="0.2">
+      <c r="B63" t="s">
+        <v>136</v>
+      </c>
+      <c r="C63" s="5" t="s">
+        <v>145</v>
+      </c>
+      <c r="D63" t="s">
+        <v>146</v>
+      </c>
+      <c r="E63" t="s">
+        <v>33</v>
+      </c>
+      <c r="F63">
         <v>0.5</v>
       </c>
-      <c r="G62" s="1" t="s">
-        <v>21</v>
-      </c>
-      <c r="H62" s="1">
+      <c r="G63" s="5" t="s">
+        <v>23</v>
+      </c>
+      <c r="H63" s="1">
         <v>9.65</v>
       </c>
-      <c r="I62" s="1">
+      <c r="I63" s="1">
         <f>Table1[[#This Row],[Qty]]*Table1[[#This Row],[Unit Cost]]</f>
         <v>4.8250000000000002</v>
       </c>
-      <c r="J62" t="s">
-        <v>135</v>
-      </c>
-      <c r="K62" t="s">
-        <v>139</v>
+      <c r="J63" t="s">
+        <v>147</v>
+      </c>
+      <c r="K63" t="s">
+        <v>148</v>
       </c>
     </row>
   </sheetData>
   <hyperlinks>
-    <hyperlink ref="J41" r:id="rId1" xr:uid="{7232EB30-30F6-A44D-A099-36A36F85D531}"/>
-    <hyperlink ref="J43" r:id="rId2" xr:uid="{27DD5690-F388-A048-A20A-B068A8B5D504}"/>
-    <hyperlink ref="J45" r:id="rId3" xr:uid="{331E0A82-5FA5-414B-9807-F2B18A4F0C7D}"/>
-    <hyperlink ref="J42" r:id="rId4" xr:uid="{14163A79-9220-954E-B070-3F59DBA5CAD5}"/>
-    <hyperlink ref="J49" r:id="rId5" xr:uid="{0BD55709-6453-5C45-B817-BE190D9BC47D}"/>
-    <hyperlink ref="J46" r:id="rId6" xr:uid="{39651285-9062-AE46-8CEE-CB2502E2250C}"/>
-    <hyperlink ref="J11" r:id="rId7" xr:uid="{AEA8C86A-2AF5-954D-AD6C-68528ADFACB4}"/>
-    <hyperlink ref="J13" r:id="rId8" xr:uid="{D04300F4-D466-DE4C-87BE-1085E3419DD2}"/>
-    <hyperlink ref="J15" r:id="rId9" xr:uid="{FAEC562D-C427-2046-8C55-C0E64FA01D73}"/>
-    <hyperlink ref="J20" r:id="rId10" xr:uid="{D2A0390A-1F9C-F549-A7E2-D4F7EE7B93B1}"/>
-    <hyperlink ref="J21" r:id="rId11" xr:uid="{0FD0A703-5545-BE43-872C-994E58031B5D}"/>
-    <hyperlink ref="J19" r:id="rId12" xr:uid="{B6C2B4C0-40B1-954A-BDF4-C33FC25BD2CE}"/>
-    <hyperlink ref="J22" r:id="rId13" xr:uid="{F7B7AD27-F42E-7843-B388-0AAA3554A341}"/>
-    <hyperlink ref="J12" r:id="rId14" xr:uid="{00954120-3DFF-124A-B8CE-0910D138CBD6}"/>
-    <hyperlink ref="J29" r:id="rId15" xr:uid="{8C561801-202F-1A49-9E4D-58E07ADA24E3}"/>
-    <hyperlink ref="J58" r:id="rId16" xr:uid="{8087BC0F-FFD5-CD4E-ADFE-1EA4780F0490}"/>
-    <hyperlink ref="J53" r:id="rId17" xr:uid="{820CF3C4-6327-B742-A1A3-106AA8E81F7B}"/>
-    <hyperlink ref="J59" r:id="rId18" xr:uid="{D871B945-B618-6344-8A01-6EC7344361E7}"/>
-    <hyperlink ref="J48" r:id="rId19" xr:uid="{E2D038F6-E31B-7A4D-995A-482D86DDD91D}"/>
+    <hyperlink ref="J11" r:id="rId1" xr:uid="{00000000-0004-0000-0000-000000000000}"/>
+    <hyperlink ref="J12" r:id="rId2" xr:uid="{00000000-0004-0000-0000-000001000000}"/>
+    <hyperlink ref="J13" r:id="rId3" xr:uid="{00000000-0004-0000-0000-000002000000}"/>
+    <hyperlink ref="J15" r:id="rId4" xr:uid="{00000000-0004-0000-0000-000003000000}"/>
+    <hyperlink ref="J16" r:id="rId5" xr:uid="{00000000-0004-0000-0000-000004000000}"/>
+    <hyperlink ref="J19" r:id="rId6" xr:uid="{00000000-0004-0000-0000-000005000000}"/>
+    <hyperlink ref="J20" r:id="rId7" xr:uid="{00000000-0004-0000-0000-000006000000}"/>
+    <hyperlink ref="J21" r:id="rId8" xr:uid="{00000000-0004-0000-0000-000007000000}"/>
+    <hyperlink ref="J22" r:id="rId9" xr:uid="{00000000-0004-0000-0000-000008000000}"/>
+    <hyperlink ref="J23" r:id="rId10" xr:uid="{00000000-0004-0000-0000-000009000000}"/>
+    <hyperlink ref="J24" r:id="rId11" xr:uid="{00000000-0004-0000-0000-00000A000000}"/>
+    <hyperlink ref="J25" r:id="rId12" xr:uid="{00000000-0004-0000-0000-00000B000000}"/>
+    <hyperlink ref="J29" r:id="rId13" xr:uid="{00000000-0004-0000-0000-00000C000000}"/>
+    <hyperlink ref="J38" r:id="rId14" xr:uid="{00000000-0004-0000-0000-00000D000000}"/>
+    <hyperlink ref="J39" r:id="rId15" xr:uid="{00000000-0004-0000-0000-00000E000000}"/>
+    <hyperlink ref="J41" r:id="rId16" xr:uid="{00000000-0004-0000-0000-00000F000000}"/>
+    <hyperlink ref="J42" r:id="rId17" xr:uid="{00000000-0004-0000-0000-000010000000}"/>
+    <hyperlink ref="J43" r:id="rId18" xr:uid="{00000000-0004-0000-0000-000011000000}"/>
+    <hyperlink ref="J45" r:id="rId19" xr:uid="{00000000-0004-0000-0000-000012000000}"/>
+    <hyperlink ref="J46" r:id="rId20" xr:uid="{00000000-0004-0000-0000-000013000000}"/>
+    <hyperlink ref="J47" r:id="rId21" xr:uid="{00000000-0004-0000-0000-000014000000}"/>
+    <hyperlink ref="J48" r:id="rId22" xr:uid="{00000000-0004-0000-0000-000015000000}"/>
+    <hyperlink ref="J49" r:id="rId23" xr:uid="{00000000-0004-0000-0000-000016000000}"/>
+    <hyperlink ref="J51" r:id="rId24" xr:uid="{00000000-0004-0000-0000-000017000000}"/>
+    <hyperlink ref="J53" r:id="rId25" xr:uid="{00000000-0004-0000-0000-000018000000}"/>
+    <hyperlink ref="J56" r:id="rId26" xr:uid="{00000000-0004-0000-0000-000019000000}"/>
+    <hyperlink ref="J59" r:id="rId27" xr:uid="{00000000-0004-0000-0000-00001A000000}"/>
+    <hyperlink ref="J60" r:id="rId28" xr:uid="{00000000-0004-0000-0000-00001B000000}"/>
+    <hyperlink ref="J54" r:id="rId29" xr:uid="{E0F0E1BC-BF9F-EC41-B567-F34F9756DE29}"/>
   </hyperlinks>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <tableParts count="1">
-    <tablePart r:id="rId20"/>
+    <tablePart r:id="rId30"/>
   </tableParts>
 </worksheet>
 </file>
--- a/Walking-Setup/G6-Integration-Bill-of-Materials.xlsx
+++ b/Walking-Setup/G6-Integration-Bill-of-Materials.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="10703"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="10713"/>
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/lehenbaueri/Documents/GitHub/Fly-Lab-Gear/Walking-Setup/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{50363D00-03FF-BB4E-9D05-0301A7584635}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{6A04A191-27BF-7F49-95A7-8C52F28F758E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="6460" yWindow="1600" windowWidth="27460" windowHeight="18980" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="1640" yWindow="660" windowWidth="27460" windowHeight="18980" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -33,15 +33,12 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="305" uniqueCount="152">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="306" uniqueCount="151">
   <si>
     <t>Name</t>
   </si>
   <si>
     <t>G6 Fly on Ball Walking Setup</t>
-  </si>
-  <si>
-    <t>Number</t>
   </si>
   <si>
     <t>Revision</t>
@@ -551,7 +548,7 @@
     <xf numFmtId="44" fontId="1" fillId="0" borderId="0"/>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="8">
+  <cellXfs count="7">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="44" fontId="0" fillId="0" borderId="0" xfId="1" applyFont="1"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
@@ -563,7 +560,6 @@
       <alignment horizontal="left"/>
     </xf>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="44" fontId="0" fillId="0" borderId="0" xfId="1" applyFont="1" applyFill="1"/>
   </cellXfs>
   <cellStyles count="3">
     <cellStyle name="Currency" xfId="1" builtinId="4"/>
@@ -621,8 +617,8 @@
 </file>
 
 <file path=xl/tables/table1.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="1" xr:uid="{00000000-000C-0000-FFFF-FFFF00000000}" name="Table1" displayName="Table1" ref="A10:K63" totalsRowShown="0">
-  <autoFilter ref="A10:K63" xr:uid="{00000000-0009-0000-0100-000001000000}"/>
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="1" xr:uid="{00000000-000C-0000-FFFF-FFFF00000000}" name="Table1" displayName="Table1" ref="A9:K62" totalsRowShown="0">
+  <autoFilter ref="A9:K62" xr:uid="{00000000-0009-0000-0100-000001000000}"/>
   <tableColumns count="11">
     <tableColumn id="1" xr3:uid="{00000000-0010-0000-0000-000001000000}" name="Category"/>
     <tableColumn id="9" xr3:uid="{00000000-0010-0000-0000-000009000000}" name="Subassembly"/>
@@ -959,7 +955,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:K63"/>
+  <dimension ref="A1:K62"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="16" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="22" customWidth="1"/>
@@ -985,20 +981,20 @@
       <c r="A2" s="2" t="s">
         <v>2</v>
       </c>
+      <c r="B2">
+        <v>2</v>
+      </c>
     </row>
     <row r="3" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A3" s="2" t="s">
         <v>3</v>
       </c>
-      <c r="B3">
-        <v>2</v>
+      <c r="B3" t="s">
+        <v>4</v>
       </c>
     </row>
     <row r="4" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A4" s="2" t="s">
-        <v>4</v>
-      </c>
-      <c r="B4" t="s">
         <v>5</v>
       </c>
     </row>
@@ -1006,239 +1002,256 @@
       <c r="A5" s="2" t="s">
         <v>6</v>
       </c>
+      <c r="B5">
+        <f>SUM(Table1[Qty])</f>
+        <v>104.5</v>
+      </c>
     </row>
     <row r="6" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A6" s="2" t="s">
         <v>7</v>
       </c>
-      <c r="B6">
-        <f>SUM(Table1[Qty])</f>
-        <v>104.5</v>
-      </c>
-    </row>
-    <row r="7" spans="1:11" x14ac:dyDescent="0.2">
-      <c r="A7" s="2" t="s">
-        <v>8</v>
-      </c>
-      <c r="B7" s="3">
+      <c r="B6" s="3">
         <f>SUM(Table1[Cost])</f>
         <v>588.54019999999991</v>
       </c>
     </row>
+    <row r="9" spans="1:11" x14ac:dyDescent="0.2">
+      <c r="A9" t="s">
+        <v>8</v>
+      </c>
+      <c r="B9" t="s">
+        <v>9</v>
+      </c>
+      <c r="C9" s="5" t="s">
+        <v>10</v>
+      </c>
+      <c r="D9" t="s">
+        <v>11</v>
+      </c>
+      <c r="E9" t="s">
+        <v>12</v>
+      </c>
+      <c r="F9" t="s">
+        <v>13</v>
+      </c>
+      <c r="G9" t="s">
+        <v>14</v>
+      </c>
+      <c r="H9" s="1" t="s">
+        <v>15</v>
+      </c>
+      <c r="I9" s="1" t="s">
+        <v>16</v>
+      </c>
+      <c r="J9" t="s">
+        <v>17</v>
+      </c>
+      <c r="K9" t="s">
+        <v>18</v>
+      </c>
+    </row>
     <row r="10" spans="1:11" x14ac:dyDescent="0.2">
-      <c r="A10" t="s">
-        <v>9</v>
-      </c>
-      <c r="B10" t="s">
-        <v>10</v>
-      </c>
       <c r="C10" s="5" t="s">
-        <v>11</v>
+        <v>19</v>
       </c>
       <c r="D10" t="s">
-        <v>12</v>
+        <v>20</v>
       </c>
       <c r="E10" t="s">
-        <v>13</v>
-      </c>
-      <c r="F10" t="s">
-        <v>14</v>
-      </c>
-      <c r="G10" t="s">
-        <v>15</v>
-      </c>
-      <c r="H10" s="1" t="s">
-        <v>16</v>
-      </c>
-      <c r="I10" s="1" t="s">
-        <v>17</v>
-      </c>
-      <c r="J10" t="s">
-        <v>18</v>
-      </c>
-      <c r="K10" t="s">
-        <v>19</v>
+        <v>21</v>
+      </c>
+      <c r="F10">
+        <v>1</v>
+      </c>
+      <c r="G10" s="5" t="s">
+        <v>22</v>
+      </c>
+      <c r="H10" s="1">
+        <v>184.47</v>
+      </c>
+      <c r="I10" s="1">
+        <f>Table1[[#This Row],[Qty]]*Table1[[#This Row],[Unit Cost]]</f>
+        <v>184.47</v>
+      </c>
+      <c r="J10" s="4" t="s">
+        <v>23</v>
       </c>
     </row>
     <row r="11" spans="1:11" x14ac:dyDescent="0.2">
-      <c r="C11" s="5" t="s">
-        <v>20</v>
+      <c r="B11" t="s">
+        <v>24</v>
       </c>
       <c r="D11" t="s">
-        <v>21</v>
-      </c>
-      <c r="E11" t="s">
-        <v>22</v>
+        <v>24</v>
       </c>
       <c r="F11">
         <v>1</v>
       </c>
       <c r="G11" s="5" t="s">
-        <v>23</v>
-      </c>
-      <c r="H11" s="1">
-        <v>184.47</v>
+        <v>22</v>
       </c>
       <c r="I11" s="1">
         <f>Table1[[#This Row],[Qty]]*Table1[[#This Row],[Unit Cost]]</f>
-        <v>184.47</v>
+        <v>0</v>
       </c>
       <c r="J11" s="4" t="s">
-        <v>24</v>
+        <v>25</v>
       </c>
     </row>
     <row r="12" spans="1:11" x14ac:dyDescent="0.2">
       <c r="B12" t="s">
-        <v>25</v>
+        <v>24</v>
+      </c>
+      <c r="C12" s="5" t="s">
+        <v>26</v>
       </c>
       <c r="D12" t="s">
-        <v>25</v>
+        <v>27</v>
+      </c>
+      <c r="E12" t="s">
+        <v>21</v>
       </c>
       <c r="F12">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="G12" s="5" t="s">
-        <v>23</v>
+        <v>22</v>
+      </c>
+      <c r="H12" s="1">
+        <v>5.76</v>
       </c>
       <c r="I12" s="1">
         <f>Table1[[#This Row],[Qty]]*Table1[[#This Row],[Unit Cost]]</f>
-        <v>0</v>
+        <v>23.04</v>
       </c>
       <c r="J12" s="4" t="s">
-        <v>26</v>
+        <v>28</v>
       </c>
     </row>
     <row r="13" spans="1:11" x14ac:dyDescent="0.2">
+      <c r="A13" t="s">
+        <v>29</v>
+      </c>
       <c r="B13" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="C13" s="5" t="s">
-        <v>27</v>
+        <v>30</v>
       </c>
       <c r="D13" t="s">
-        <v>28</v>
+        <v>31</v>
       </c>
       <c r="E13" t="s">
-        <v>22</v>
+        <v>32</v>
       </c>
       <c r="F13">
         <v>4</v>
       </c>
       <c r="G13" s="5" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="H13" s="1">
-        <v>5.76</v>
+        <f>14.44/100</f>
+        <v>0.1444</v>
       </c>
       <c r="I13" s="1">
         <f>Table1[[#This Row],[Qty]]*Table1[[#This Row],[Unit Cost]]</f>
-        <v>23.04</v>
+        <v>0.5776</v>
       </c>
       <c r="J13" s="4" t="s">
-        <v>29</v>
+        <v>33</v>
       </c>
     </row>
     <row r="14" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A14" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="B14" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="C14" s="5" t="s">
-        <v>31</v>
+        <v>34</v>
       </c>
       <c r="D14" t="s">
+        <v>35</v>
+      </c>
+      <c r="E14" t="s">
         <v>32</v>
       </c>
-      <c r="E14" t="s">
-        <v>33</v>
-      </c>
       <c r="F14">
-        <v>4</v>
+        <v>8</v>
       </c>
       <c r="G14" s="5" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="H14" s="1">
-        <f>14.44/100</f>
-        <v>0.1444</v>
-      </c>
-      <c r="I14" s="1">
-        <f>Table1[[#This Row],[Qty]]*Table1[[#This Row],[Unit Cost]]</f>
-        <v>0.5776</v>
-      </c>
-      <c r="J14" s="4" t="s">
-        <v>34</v>
-      </c>
-    </row>
-    <row r="15" spans="1:11" x14ac:dyDescent="0.2">
-      <c r="A15" t="s">
-        <v>30</v>
-      </c>
-      <c r="B15" t="s">
-        <v>25</v>
-      </c>
-      <c r="C15" s="5" t="s">
-        <v>35</v>
-      </c>
-      <c r="D15" t="s">
-        <v>36</v>
-      </c>
-      <c r="E15" t="s">
-        <v>33</v>
-      </c>
-      <c r="F15">
-        <v>8</v>
-      </c>
-      <c r="G15" s="5" t="s">
-        <v>23</v>
-      </c>
-      <c r="H15" s="1">
         <f>2.02/100</f>
         <v>2.0199999999999999E-2</v>
       </c>
+      <c r="I14" s="1">
+        <f>Table1[[#This Row],[Qty]]*Table1[[#This Row],[Unit Cost]]</f>
+        <v>0.16159999999999999</v>
+      </c>
+      <c r="J14" s="4" t="s">
+        <v>36</v>
+      </c>
+    </row>
+    <row r="15" spans="1:11" x14ac:dyDescent="0.2">
+      <c r="B15" t="s">
+        <v>24</v>
+      </c>
+      <c r="C15" s="5" t="s">
+        <v>37</v>
+      </c>
+      <c r="D15" t="s">
+        <v>38</v>
+      </c>
+      <c r="E15" t="s">
+        <v>39</v>
+      </c>
+      <c r="F15">
+        <v>4</v>
+      </c>
+      <c r="G15" s="5" t="s">
+        <v>40</v>
+      </c>
       <c r="I15" s="1">
         <f>Table1[[#This Row],[Qty]]*Table1[[#This Row],[Unit Cost]]</f>
-        <v>0.16159999999999999</v>
+        <v>0</v>
       </c>
       <c r="J15" s="4" t="s">
-        <v>37</v>
+        <v>41</v>
       </c>
     </row>
     <row r="16" spans="1:11" x14ac:dyDescent="0.2">
+      <c r="A16" t="s">
+        <v>42</v>
+      </c>
       <c r="B16" t="s">
-        <v>25</v>
-      </c>
-      <c r="C16" s="5" t="s">
-        <v>38</v>
+        <v>24</v>
       </c>
       <c r="D16" t="s">
-        <v>39</v>
-      </c>
-      <c r="E16" t="s">
-        <v>40</v>
+        <v>43</v>
       </c>
       <c r="F16">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="G16" s="5" t="s">
-        <v>41</v>
+        <v>22</v>
       </c>
       <c r="I16" s="1">
         <f>Table1[[#This Row],[Qty]]*Table1[[#This Row],[Unit Cost]]</f>
         <v>0</v>
       </c>
-      <c r="J16" s="4" t="s">
-        <v>42</v>
-      </c>
+      <c r="J16" s="4"/>
     </row>
     <row r="17" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A17" t="s">
-        <v>43</v>
+        <v>42</v>
       </c>
       <c r="B17" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="D17" t="s">
         <v>44</v>
@@ -1247,250 +1260,247 @@
         <v>1</v>
       </c>
       <c r="G17" s="5" t="s">
-        <v>23</v>
+        <v>22</v>
+      </c>
+      <c r="H17" s="1">
+        <v>4.5</v>
       </c>
       <c r="I17" s="1">
         <f>Table1[[#This Row],[Qty]]*Table1[[#This Row],[Unit Cost]]</f>
-        <v>0</v>
-      </c>
-      <c r="J17" s="4"/>
+        <v>4.5</v>
+      </c>
+      <c r="J17" s="4" t="s">
+        <v>45</v>
+      </c>
     </row>
     <row r="18" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A18" t="s">
-        <v>43</v>
+        <v>29</v>
       </c>
       <c r="B18" t="s">
-        <v>25</v>
+        <v>46</v>
+      </c>
+      <c r="C18" s="5" t="s">
+        <v>47</v>
       </c>
       <c r="D18" t="s">
-        <v>45</v>
+        <v>48</v>
+      </c>
+      <c r="E18" t="s">
+        <v>32</v>
       </c>
       <c r="F18">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="G18" s="5" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="H18" s="1">
-        <v>4.5</v>
+        <f>13.88/25</f>
+        <v>0.55520000000000003</v>
       </c>
       <c r="I18" s="1">
         <f>Table1[[#This Row],[Qty]]*Table1[[#This Row],[Unit Cost]]</f>
-        <v>4.5</v>
+        <v>2.2208000000000001</v>
       </c>
       <c r="J18" s="4" t="s">
-        <v>46</v>
+        <v>49</v>
       </c>
     </row>
     <row r="19" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A19" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="B19" t="s">
-        <v>47</v>
+        <v>46</v>
       </c>
       <c r="C19" s="5" t="s">
-        <v>48</v>
+        <v>34</v>
       </c>
       <c r="D19" t="s">
-        <v>49</v>
+        <v>35</v>
       </c>
       <c r="E19" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="F19">
         <v>4</v>
       </c>
       <c r="G19" s="5" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="H19" s="1">
-        <f>13.88/25</f>
-        <v>0.55520000000000003</v>
+        <v>0.02</v>
       </c>
       <c r="I19" s="1">
         <f>Table1[[#This Row],[Qty]]*Table1[[#This Row],[Unit Cost]]</f>
-        <v>2.2208000000000001</v>
+        <v>0.08</v>
       </c>
       <c r="J19" s="4" t="s">
-        <v>50</v>
+        <v>36</v>
       </c>
     </row>
     <row r="20" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A20" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="B20" t="s">
-        <v>47</v>
+        <v>24</v>
       </c>
       <c r="C20" s="5" t="s">
-        <v>35</v>
+        <v>50</v>
       </c>
       <c r="D20" t="s">
-        <v>36</v>
+        <v>51</v>
       </c>
       <c r="E20" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="F20">
         <v>4</v>
       </c>
       <c r="G20" s="5" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="H20" s="1">
-        <v>0.02</v>
-      </c>
-      <c r="I20" s="1">
-        <f>Table1[[#This Row],[Qty]]*Table1[[#This Row],[Unit Cost]]</f>
-        <v>0.08</v>
-      </c>
-      <c r="J20" s="4" t="s">
-        <v>37</v>
-      </c>
-    </row>
-    <row r="21" spans="1:10" x14ac:dyDescent="0.2">
-      <c r="A21" t="s">
-        <v>30</v>
-      </c>
-      <c r="B21" t="s">
-        <v>25</v>
-      </c>
-      <c r="C21" s="5" t="s">
-        <v>51</v>
-      </c>
-      <c r="D21" t="s">
-        <v>52</v>
-      </c>
-      <c r="E21" t="s">
-        <v>33</v>
-      </c>
-      <c r="F21">
-        <v>4</v>
-      </c>
-      <c r="G21" s="5" t="s">
-        <v>23</v>
-      </c>
-      <c r="H21" s="1">
         <f>14.83/100</f>
         <v>0.14829999999999999</v>
       </c>
+      <c r="I20" s="1">
+        <f>Table1[[#This Row],[Qty]]*Table1[[#This Row],[Unit Cost]]</f>
+        <v>0.59319999999999995</v>
+      </c>
+      <c r="J20" s="4" t="s">
+        <v>52</v>
+      </c>
+    </row>
+    <row r="21" spans="1:10" x14ac:dyDescent="0.2">
+      <c r="B21" t="s">
+        <v>46</v>
+      </c>
+      <c r="C21" s="5" t="s">
+        <v>53</v>
+      </c>
+      <c r="D21" t="s">
+        <v>54</v>
+      </c>
+      <c r="E21" t="s">
+        <v>32</v>
+      </c>
+      <c r="F21">
+        <v>1</v>
+      </c>
+      <c r="G21" s="5" t="s">
+        <v>22</v>
+      </c>
+      <c r="H21" s="1">
+        <v>2.89</v>
+      </c>
       <c r="I21" s="1">
         <f>Table1[[#This Row],[Qty]]*Table1[[#This Row],[Unit Cost]]</f>
-        <v>0.59319999999999995</v>
+        <v>2.89</v>
       </c>
       <c r="J21" s="4" t="s">
-        <v>53</v>
+        <v>55</v>
       </c>
     </row>
     <row r="22" spans="1:10" x14ac:dyDescent="0.2">
       <c r="B22" t="s">
-        <v>47</v>
-      </c>
-      <c r="C22" s="5" t="s">
-        <v>54</v>
+        <v>46</v>
       </c>
       <c r="D22" t="s">
-        <v>55</v>
+        <v>56</v>
       </c>
       <c r="E22" t="s">
-        <v>33</v>
+        <v>39</v>
       </c>
       <c r="F22">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="G22" s="5" t="s">
-        <v>23</v>
-      </c>
-      <c r="H22" s="1">
-        <v>2.89</v>
+        <v>22</v>
       </c>
       <c r="I22" s="1">
         <f>Table1[[#This Row],[Qty]]*Table1[[#This Row],[Unit Cost]]</f>
-        <v>2.89</v>
+        <v>0</v>
       </c>
       <c r="J22" s="4" t="s">
-        <v>56</v>
+        <v>57</v>
       </c>
     </row>
     <row r="23" spans="1:10" x14ac:dyDescent="0.2">
       <c r="B23" t="s">
-        <v>47</v>
+        <v>46</v>
       </c>
       <c r="D23" t="s">
-        <v>57</v>
+        <v>58</v>
       </c>
       <c r="E23" t="s">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="F23">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="G23" s="5" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="I23" s="1">
         <f>Table1[[#This Row],[Qty]]*Table1[[#This Row],[Unit Cost]]</f>
         <v>0</v>
       </c>
       <c r="J23" s="4" t="s">
-        <v>58</v>
+        <v>59</v>
       </c>
     </row>
     <row r="24" spans="1:10" x14ac:dyDescent="0.2">
       <c r="B24" t="s">
-        <v>47</v>
+        <v>46</v>
       </c>
       <c r="D24" t="s">
-        <v>59</v>
+        <v>60</v>
       </c>
       <c r="E24" t="s">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="F24">
         <v>1</v>
       </c>
       <c r="G24" s="5" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="I24" s="1">
         <f>Table1[[#This Row],[Qty]]*Table1[[#This Row],[Unit Cost]]</f>
         <v>0</v>
       </c>
       <c r="J24" s="4" t="s">
-        <v>60</v>
+        <v>61</v>
       </c>
     </row>
     <row r="25" spans="1:10" x14ac:dyDescent="0.2">
+      <c r="A25" t="s">
+        <v>42</v>
+      </c>
       <c r="B25" t="s">
-        <v>47</v>
+        <v>46</v>
       </c>
       <c r="D25" t="s">
-        <v>61</v>
-      </c>
-      <c r="E25" t="s">
-        <v>40</v>
+        <v>62</v>
       </c>
       <c r="F25">
         <v>1</v>
       </c>
       <c r="G25" s="5" t="s">
-        <v>23</v>
-      </c>
-      <c r="I25" s="1">
-        <f>Table1[[#This Row],[Qty]]*Table1[[#This Row],[Unit Cost]]</f>
-        <v>0</v>
-      </c>
-      <c r="J25" s="4" t="s">
-        <v>62</v>
-      </c>
+        <v>22</v>
+      </c>
+      <c r="I25" s="1"/>
+      <c r="J25" s="4"/>
     </row>
     <row r="26" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A26" t="s">
-        <v>43</v>
+        <v>42</v>
       </c>
       <c r="B26" t="s">
-        <v>47</v>
+        <v>46</v>
       </c>
       <c r="D26" t="s">
         <v>63</v>
@@ -1498,16 +1508,18 @@
       <c r="F26">
         <v>1</v>
       </c>
-      <c r="G26" s="5"/>
+      <c r="G26" s="5" t="s">
+        <v>22</v>
+      </c>
       <c r="I26" s="1"/>
       <c r="J26" s="4"/>
     </row>
     <row r="27" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A27" t="s">
-        <v>43</v>
+        <v>42</v>
       </c>
       <c r="B27" t="s">
-        <v>47</v>
+        <v>46</v>
       </c>
       <c r="D27" t="s">
         <v>64</v>
@@ -1515,1015 +1527,998 @@
       <c r="F27">
         <v>1</v>
       </c>
-      <c r="G27" s="5"/>
+      <c r="G27" s="5" t="s">
+        <v>22</v>
+      </c>
       <c r="I27" s="1"/>
       <c r="J27" s="4"/>
     </row>
     <row r="28" spans="1:10" x14ac:dyDescent="0.2">
-      <c r="A28" t="s">
-        <v>43</v>
-      </c>
       <c r="B28" t="s">
-        <v>47</v>
+        <v>46</v>
+      </c>
+      <c r="C28" s="5" t="s">
+        <v>65</v>
       </c>
       <c r="D28" t="s">
-        <v>65</v>
+        <v>66</v>
+      </c>
+      <c r="E28" t="s">
+        <v>67</v>
       </c>
       <c r="F28">
         <v>1</v>
       </c>
       <c r="G28" s="5" t="s">
-        <v>23</v>
-      </c>
-      <c r="I28" s="1"/>
-      <c r="J28" s="4"/>
+        <v>22</v>
+      </c>
+      <c r="H28" s="1">
+        <v>11.34</v>
+      </c>
+      <c r="I28" s="1">
+        <f>Table1[[#This Row],[Qty]]*Table1[[#This Row],[Unit Cost]]</f>
+        <v>11.34</v>
+      </c>
+      <c r="J28" s="4" t="s">
+        <v>68</v>
+      </c>
     </row>
     <row r="29" spans="1:10" x14ac:dyDescent="0.2">
       <c r="B29" t="s">
-        <v>47</v>
+        <v>46</v>
       </c>
       <c r="C29" s="5" t="s">
-        <v>66</v>
+        <v>69</v>
       </c>
       <c r="D29" t="s">
+        <v>70</v>
+      </c>
+      <c r="E29" t="s">
         <v>67</v>
       </c>
-      <c r="E29" t="s">
-        <v>68</v>
-      </c>
       <c r="F29">
         <v>1</v>
       </c>
       <c r="G29" s="5" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="H29" s="1">
-        <v>11.34</v>
+        <v>5.14</v>
       </c>
       <c r="I29" s="1">
         <f>Table1[[#This Row],[Qty]]*Table1[[#This Row],[Unit Cost]]</f>
-        <v>11.34</v>
-      </c>
-      <c r="J29" s="4" t="s">
-        <v>69</v>
+        <v>5.14</v>
       </c>
     </row>
     <row r="30" spans="1:10" x14ac:dyDescent="0.2">
       <c r="B30" t="s">
-        <v>47</v>
-      </c>
-      <c r="C30" s="5" t="s">
-        <v>70</v>
+        <v>46</v>
+      </c>
+      <c r="C30" s="5">
+        <v>10193</v>
       </c>
       <c r="D30" t="s">
         <v>71</v>
       </c>
       <c r="E30" t="s">
-        <v>68</v>
+        <v>67</v>
       </c>
       <c r="F30">
         <v>1</v>
       </c>
       <c r="G30" s="5" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="H30" s="1">
-        <v>5.14</v>
+        <v>1.71</v>
       </c>
       <c r="I30" s="1">
         <f>Table1[[#This Row],[Qty]]*Table1[[#This Row],[Unit Cost]]</f>
-        <v>5.14</v>
+        <v>1.71</v>
       </c>
     </row>
     <row r="31" spans="1:10" x14ac:dyDescent="0.2">
+      <c r="A31" t="s">
+        <v>29</v>
+      </c>
       <c r="B31" t="s">
-        <v>47</v>
-      </c>
-      <c r="C31" s="5">
-        <v>10193</v>
+        <v>46</v>
+      </c>
+      <c r="C31" s="5" t="s">
+        <v>72</v>
       </c>
       <c r="D31" t="s">
-        <v>72</v>
+        <v>73</v>
       </c>
       <c r="E31" t="s">
-        <v>68</v>
+        <v>67</v>
       </c>
       <c r="F31">
         <v>1</v>
       </c>
       <c r="G31" s="5" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="H31" s="1">
-        <v>1.71</v>
+        <v>1.92</v>
       </c>
       <c r="I31" s="1">
         <f>Table1[[#This Row],[Qty]]*Table1[[#This Row],[Unit Cost]]</f>
-        <v>1.71</v>
+        <v>1.92</v>
       </c>
     </row>
     <row r="32" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A32" t="s">
-        <v>30</v>
+        <v>42</v>
       </c>
       <c r="B32" t="s">
-        <v>47</v>
+        <v>46</v>
       </c>
       <c r="C32" s="5" t="s">
-        <v>73</v>
+        <v>74</v>
       </c>
       <c r="D32" t="s">
-        <v>74</v>
+        <v>75</v>
       </c>
       <c r="E32" t="s">
-        <v>68</v>
+        <v>67</v>
       </c>
       <c r="F32">
         <v>1</v>
       </c>
       <c r="G32" s="5" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="H32" s="1">
-        <v>1.92</v>
+        <v>17.239999999999998</v>
       </c>
       <c r="I32" s="1">
         <f>Table1[[#This Row],[Qty]]*Table1[[#This Row],[Unit Cost]]</f>
-        <v>1.92</v>
+        <v>17.239999999999998</v>
       </c>
     </row>
     <row r="33" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A33" t="s">
-        <v>43</v>
+        <v>42</v>
       </c>
       <c r="B33" t="s">
-        <v>47</v>
+        <v>46</v>
       </c>
       <c r="C33" s="5" t="s">
-        <v>75</v>
+        <v>76</v>
       </c>
       <c r="D33" t="s">
-        <v>76</v>
+        <v>77</v>
       </c>
       <c r="E33" t="s">
-        <v>68</v>
+        <v>67</v>
       </c>
       <c r="F33">
         <v>1</v>
       </c>
       <c r="G33" s="5" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="H33" s="1">
-        <v>17.239999999999998</v>
+        <v>2.56</v>
       </c>
       <c r="I33" s="1">
         <f>Table1[[#This Row],[Qty]]*Table1[[#This Row],[Unit Cost]]</f>
-        <v>17.239999999999998</v>
+        <v>2.56</v>
       </c>
     </row>
     <row r="34" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A34" t="s">
-        <v>43</v>
+        <v>42</v>
       </c>
       <c r="B34" t="s">
-        <v>47</v>
-      </c>
-      <c r="C34" s="5" t="s">
-        <v>77</v>
+        <v>46</v>
       </c>
       <c r="D34" t="s">
         <v>78</v>
       </c>
-      <c r="E34" t="s">
-        <v>68</v>
-      </c>
       <c r="F34">
         <v>1</v>
       </c>
       <c r="G34" s="5" t="s">
-        <v>23</v>
-      </c>
-      <c r="H34" s="1">
-        <v>2.56</v>
+        <v>22</v>
       </c>
       <c r="I34" s="1">
         <f>Table1[[#This Row],[Qty]]*Table1[[#This Row],[Unit Cost]]</f>
-        <v>2.56</v>
+        <v>0</v>
       </c>
     </row>
     <row r="35" spans="1:10" x14ac:dyDescent="0.2">
-      <c r="A35" t="s">
-        <v>43</v>
-      </c>
       <c r="B35" t="s">
-        <v>47</v>
+        <v>79</v>
       </c>
       <c r="D35" t="s">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="F35">
         <v>1</v>
       </c>
       <c r="G35" s="5" t="s">
-        <v>23</v>
+        <v>22</v>
+      </c>
+      <c r="H35" s="1">
+        <v>80</v>
       </c>
       <c r="I35" s="1">
         <f>Table1[[#This Row],[Qty]]*Table1[[#This Row],[Unit Cost]]</f>
-        <v>0</v>
+        <v>80</v>
       </c>
     </row>
     <row r="36" spans="1:10" x14ac:dyDescent="0.2">
       <c r="B36" t="s">
-        <v>80</v>
+        <v>79</v>
       </c>
       <c r="D36" t="s">
         <v>81</v>
       </c>
+      <c r="E36" t="s">
+        <v>39</v>
+      </c>
       <c r="F36">
         <v>1</v>
       </c>
       <c r="G36" s="5" t="s">
-        <v>23</v>
-      </c>
-      <c r="H36" s="1">
-        <v>80</v>
+        <v>22</v>
       </c>
       <c r="I36" s="1">
         <f>Table1[[#This Row],[Qty]]*Table1[[#This Row],[Unit Cost]]</f>
-        <v>80</v>
+        <v>0</v>
       </c>
     </row>
     <row r="37" spans="1:10" x14ac:dyDescent="0.2">
       <c r="B37" t="s">
-        <v>80</v>
+        <v>79</v>
       </c>
       <c r="D37" t="s">
         <v>82</v>
       </c>
       <c r="E37" t="s">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="F37">
         <v>1</v>
       </c>
       <c r="G37" s="5" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="I37" s="1">
         <f>Table1[[#This Row],[Qty]]*Table1[[#This Row],[Unit Cost]]</f>
         <v>0</v>
+      </c>
+      <c r="J37" s="6" t="s">
+        <v>83</v>
       </c>
     </row>
     <row r="38" spans="1:10" x14ac:dyDescent="0.2">
       <c r="B38" t="s">
-        <v>80</v>
+        <v>79</v>
       </c>
       <c r="D38" t="s">
-        <v>83</v>
+        <v>84</v>
       </c>
       <c r="E38" t="s">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="F38">
         <v>1</v>
       </c>
       <c r="G38" s="5" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="I38" s="1">
         <f>Table1[[#This Row],[Qty]]*Table1[[#This Row],[Unit Cost]]</f>
         <v>0</v>
       </c>
       <c r="J38" s="6" t="s">
-        <v>84</v>
+        <v>85</v>
       </c>
     </row>
     <row r="39" spans="1:10" x14ac:dyDescent="0.2">
       <c r="B39" t="s">
-        <v>80</v>
+        <v>79</v>
       </c>
       <c r="D39" t="s">
-        <v>85</v>
-      </c>
-      <c r="E39" t="s">
-        <v>40</v>
+        <v>86</v>
       </c>
       <c r="F39">
         <v>1</v>
       </c>
       <c r="G39" s="5" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="I39" s="1">
         <f>Table1[[#This Row],[Qty]]*Table1[[#This Row],[Unit Cost]]</f>
         <v>0</v>
       </c>
-      <c r="J39" s="6" t="s">
-        <v>86</v>
-      </c>
     </row>
     <row r="40" spans="1:10" x14ac:dyDescent="0.2">
+      <c r="A40" t="s">
+        <v>29</v>
+      </c>
       <c r="B40" t="s">
-        <v>80</v>
+        <v>79</v>
+      </c>
+      <c r="C40" s="5" t="s">
+        <v>87</v>
       </c>
       <c r="D40" t="s">
-        <v>87</v>
+        <v>88</v>
+      </c>
+      <c r="E40" t="s">
+        <v>32</v>
       </c>
       <c r="F40">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="G40" s="5" t="s">
-        <v>23</v>
+        <v>22</v>
+      </c>
+      <c r="H40" s="1">
+        <f>17.78/100</f>
+        <v>0.17780000000000001</v>
       </c>
       <c r="I40" s="1">
         <f>Table1[[#This Row],[Qty]]*Table1[[#This Row],[Unit Cost]]</f>
-        <v>0</v>
+        <v>0.88900000000000001</v>
+      </c>
+      <c r="J40" s="4" t="s">
+        <v>89</v>
       </c>
     </row>
     <row r="41" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A41" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="B41" t="s">
-        <v>80</v>
+        <v>79</v>
       </c>
       <c r="C41" s="5" t="s">
-        <v>88</v>
+        <v>90</v>
       </c>
       <c r="D41" t="s">
-        <v>89</v>
+        <v>91</v>
       </c>
       <c r="E41" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="F41">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="G41" s="5" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="H41" s="1">
-        <f>17.78/100</f>
-        <v>0.17780000000000001</v>
+        <f>3.06/100</f>
+        <v>3.0600000000000002E-2</v>
       </c>
       <c r="I41" s="1">
         <f>Table1[[#This Row],[Qty]]*Table1[[#This Row],[Unit Cost]]</f>
-        <v>0.88900000000000001</v>
+        <v>3.0600000000000002E-2</v>
       </c>
       <c r="J41" s="4" t="s">
-        <v>90</v>
+        <v>92</v>
       </c>
     </row>
     <row r="42" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A42" t="s">
-        <v>30</v>
+        <v>93</v>
       </c>
       <c r="B42" t="s">
-        <v>80</v>
+        <v>93</v>
       </c>
       <c r="C42" s="5" t="s">
-        <v>91</v>
+        <v>94</v>
       </c>
       <c r="D42" t="s">
-        <v>92</v>
+        <v>95</v>
       </c>
       <c r="E42" t="s">
-        <v>33</v>
+        <v>96</v>
       </c>
       <c r="F42">
         <v>1</v>
       </c>
       <c r="G42" s="5" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="H42" s="1">
+        <v>229</v>
+      </c>
+      <c r="I42" s="1">
+        <f>Table1[[#This Row],[Qty]]*Table1[[#This Row],[Unit Cost]]</f>
+        <v>229</v>
+      </c>
+      <c r="J42" s="4" t="s">
+        <v>97</v>
+      </c>
+    </row>
+    <row r="43" spans="1:10" x14ac:dyDescent="0.2">
+      <c r="B43" t="s">
+        <v>93</v>
+      </c>
+      <c r="D43" t="s">
+        <v>98</v>
+      </c>
+      <c r="F43">
+        <v>1</v>
+      </c>
+      <c r="G43" s="5" t="s">
+        <v>22</v>
+      </c>
+      <c r="I43" s="1">
+        <f>Table1[[#This Row],[Qty]]*Table1[[#This Row],[Unit Cost]]</f>
+        <v>0</v>
+      </c>
+      <c r="J43" s="4"/>
+    </row>
+    <row r="44" spans="1:10" x14ac:dyDescent="0.2">
+      <c r="A44" t="s">
+        <v>29</v>
+      </c>
+      <c r="B44" t="s">
+        <v>93</v>
+      </c>
+      <c r="C44" s="5" t="s">
+        <v>99</v>
+      </c>
+      <c r="D44" t="s">
+        <v>100</v>
+      </c>
+      <c r="E44" t="s">
+        <v>32</v>
+      </c>
+      <c r="F44">
+        <v>6</v>
+      </c>
+      <c r="G44" s="5" t="s">
+        <v>22</v>
+      </c>
+      <c r="H44" s="1">
+        <f>17.63/100</f>
+        <v>0.17629999999999998</v>
+      </c>
+      <c r="I44" s="1">
+        <f>Table1[[#This Row],[Qty]]*Table1[[#This Row],[Unit Cost]]</f>
+        <v>1.0577999999999999</v>
+      </c>
+      <c r="J44" s="4" t="s">
+        <v>101</v>
+      </c>
+    </row>
+    <row r="45" spans="1:10" x14ac:dyDescent="0.2">
+      <c r="A45" t="s">
+        <v>29</v>
+      </c>
+      <c r="B45" t="s">
+        <v>93</v>
+      </c>
+      <c r="C45" s="5" t="s">
+        <v>102</v>
+      </c>
+      <c r="D45" t="s">
+        <v>103</v>
+      </c>
+      <c r="E45" t="s">
+        <v>32</v>
+      </c>
+      <c r="F45">
+        <v>6</v>
+      </c>
+      <c r="G45" s="5" t="s">
+        <v>22</v>
+      </c>
+      <c r="H45" s="1">
+        <f>3/100</f>
+        <v>0.03</v>
+      </c>
+      <c r="I45" s="1">
+        <f>Table1[[#This Row],[Qty]]*Table1[[#This Row],[Unit Cost]]</f>
+        <v>0.18</v>
+      </c>
+      <c r="J45" s="4" t="s">
+        <v>104</v>
+      </c>
+    </row>
+    <row r="46" spans="1:10" x14ac:dyDescent="0.2">
+      <c r="B46" t="s">
+        <v>93</v>
+      </c>
+      <c r="D46" t="s">
+        <v>105</v>
+      </c>
+      <c r="F46">
+        <v>1</v>
+      </c>
+      <c r="G46" s="5" t="s">
+        <v>22</v>
+      </c>
+      <c r="H46" s="1">
+        <v>5</v>
+      </c>
+      <c r="I46" s="1">
+        <f>Table1[[#This Row],[Qty]]*Table1[[#This Row],[Unit Cost]]</f>
+        <v>5</v>
+      </c>
+      <c r="J46" s="4" t="s">
+        <v>106</v>
+      </c>
+    </row>
+    <row r="47" spans="1:10" x14ac:dyDescent="0.2">
+      <c r="A47" t="s">
+        <v>42</v>
+      </c>
+      <c r="B47" t="s">
+        <v>107</v>
+      </c>
+      <c r="D47" t="s">
+        <v>108</v>
+      </c>
+      <c r="E47" t="s">
+        <v>109</v>
+      </c>
+      <c r="F47">
+        <v>1</v>
+      </c>
+      <c r="G47" s="5" t="s">
+        <v>22</v>
+      </c>
+      <c r="H47" s="1">
+        <v>0</v>
+      </c>
+      <c r="I47" s="1">
+        <f>Table1[[#This Row],[Qty]]*Table1[[#This Row],[Unit Cost]]</f>
+        <v>0</v>
+      </c>
+      <c r="J47" s="6" t="s">
+        <v>110</v>
+      </c>
+    </row>
+    <row r="48" spans="1:10" x14ac:dyDescent="0.2">
+      <c r="A48" t="s">
+        <v>29</v>
+      </c>
+      <c r="B48" t="s">
+        <v>107</v>
+      </c>
+      <c r="D48" t="s">
+        <v>111</v>
+      </c>
+      <c r="E48" t="s">
+        <v>32</v>
+      </c>
+      <c r="F48">
+        <v>2</v>
+      </c>
+      <c r="G48" s="5" t="s">
+        <v>22</v>
+      </c>
+      <c r="H48" s="1">
+        <f>11.38/50</f>
+        <v>0.22760000000000002</v>
+      </c>
+      <c r="I48" s="1">
+        <f>Table1[[#This Row],[Qty]]*Table1[[#This Row],[Unit Cost]]</f>
+        <v>0.45520000000000005</v>
+      </c>
+      <c r="J48" s="4" t="s">
+        <v>112</v>
+      </c>
+    </row>
+    <row r="49" spans="1:11" x14ac:dyDescent="0.2">
+      <c r="B49" t="s">
+        <v>107</v>
+      </c>
+      <c r="D49" t="s">
+        <v>113</v>
+      </c>
+      <c r="E49" t="s">
+        <v>114</v>
+      </c>
+      <c r="F49">
+        <v>1</v>
+      </c>
+      <c r="G49" s="5" t="s">
+        <v>22</v>
+      </c>
+      <c r="I49" s="1">
+        <f>Table1[[#This Row],[Qty]]*Table1[[#This Row],[Unit Cost]]</f>
+        <v>0</v>
+      </c>
+      <c r="J49" s="4" t="s">
+        <v>115</v>
+      </c>
+    </row>
+    <row r="50" spans="1:11" x14ac:dyDescent="0.2">
+      <c r="B50" t="s">
+        <v>107</v>
+      </c>
+      <c r="D50" t="s">
+        <v>116</v>
+      </c>
+      <c r="F50">
+        <v>1</v>
+      </c>
+      <c r="G50" s="5" t="s">
+        <v>22</v>
+      </c>
+      <c r="I50" s="1">
+        <f>Table1[[#This Row],[Qty]]*Table1[[#This Row],[Unit Cost]]</f>
+        <v>0</v>
+      </c>
+      <c r="J50" s="6" t="s">
+        <v>117</v>
+      </c>
+    </row>
+    <row r="51" spans="1:11" x14ac:dyDescent="0.2">
+      <c r="A51" t="s">
+        <v>29</v>
+      </c>
+      <c r="B51" t="s">
+        <v>107</v>
+      </c>
+      <c r="C51" s="5" t="s">
+        <v>118</v>
+      </c>
+      <c r="D51" t="s">
+        <v>119</v>
+      </c>
+      <c r="E51" t="s">
+        <v>32</v>
+      </c>
+      <c r="F51">
+        <v>3</v>
+      </c>
+      <c r="G51" s="5" t="s">
+        <v>22</v>
+      </c>
+      <c r="H51" s="1">
+        <f>7.57/100</f>
+        <v>7.5700000000000003E-2</v>
+      </c>
+      <c r="I51" s="1">
+        <f>Table1[[#This Row],[Qty]]*Table1[[#This Row],[Unit Cost]]</f>
+        <v>0.22710000000000002</v>
+      </c>
+      <c r="J51" t="s">
+        <v>120</v>
+      </c>
+    </row>
+    <row r="52" spans="1:11" x14ac:dyDescent="0.2">
+      <c r="A52" t="s">
+        <v>29</v>
+      </c>
+      <c r="B52" t="s">
+        <v>107</v>
+      </c>
+      <c r="C52" s="5" t="s">
+        <v>121</v>
+      </c>
+      <c r="D52" t="s">
+        <v>122</v>
+      </c>
+      <c r="E52" t="s">
+        <v>32</v>
+      </c>
+      <c r="F52">
+        <v>3</v>
+      </c>
+      <c r="G52" s="5" t="s">
+        <v>22</v>
+      </c>
+      <c r="H52" s="1">
+        <f>7.41/100</f>
+        <v>7.4099999999999999E-2</v>
+      </c>
+      <c r="I52" s="1">
+        <f>Table1[[#This Row],[Qty]]*Table1[[#This Row],[Unit Cost]]</f>
+        <v>0.2223</v>
+      </c>
+      <c r="J52" s="4" t="s">
+        <v>123</v>
+      </c>
+    </row>
+    <row r="53" spans="1:11" x14ac:dyDescent="0.2">
+      <c r="B53" t="s">
+        <v>107</v>
+      </c>
+      <c r="C53" s="5" t="s">
+        <v>150</v>
+      </c>
+      <c r="D53" t="s">
+        <v>149</v>
+      </c>
+      <c r="E53" t="s">
+        <v>32</v>
+      </c>
+      <c r="F53">
+        <v>1</v>
+      </c>
+      <c r="G53" s="5" t="s">
+        <v>22</v>
+      </c>
+      <c r="H53" s="1">
+        <v>4.95</v>
+      </c>
+      <c r="I53" s="1">
+        <f>Table1[[#This Row],[Qty]]*Table1[[#This Row],[Unit Cost]]</f>
+        <v>4.95</v>
+      </c>
+      <c r="J53" s="4" t="s">
+        <v>148</v>
+      </c>
+    </row>
+    <row r="54" spans="1:11" x14ac:dyDescent="0.2">
+      <c r="B54" t="s">
+        <v>124</v>
+      </c>
+      <c r="D54" t="s">
+        <v>125</v>
+      </c>
+      <c r="G54" s="5" t="s">
+        <v>22</v>
+      </c>
+      <c r="I54" s="1">
+        <f>Table1[[#This Row],[Qty]]*Table1[[#This Row],[Unit Cost]]</f>
+        <v>0</v>
+      </c>
+      <c r="J54" t="s">
+        <v>126</v>
+      </c>
+    </row>
+    <row r="55" spans="1:11" x14ac:dyDescent="0.2">
+      <c r="B55" t="s">
+        <v>124</v>
+      </c>
+      <c r="D55" t="s">
+        <v>127</v>
+      </c>
+      <c r="F55">
+        <v>1</v>
+      </c>
+      <c r="G55" s="5" t="s">
+        <v>22</v>
+      </c>
+      <c r="I55" s="1">
+        <f>Table1[[#This Row],[Qty]]*Table1[[#This Row],[Unit Cost]]</f>
+        <v>0</v>
+      </c>
+      <c r="J55" s="6" t="s">
+        <v>128</v>
+      </c>
+      <c r="K55" t="s">
+        <v>129</v>
+      </c>
+    </row>
+    <row r="56" spans="1:11" x14ac:dyDescent="0.2">
+      <c r="B56" t="s">
+        <v>124</v>
+      </c>
+      <c r="C56" s="5" t="s">
+        <v>130</v>
+      </c>
+      <c r="D56" t="s">
+        <v>131</v>
+      </c>
+      <c r="E56" t="s">
+        <v>132</v>
+      </c>
+      <c r="F56">
+        <v>1</v>
+      </c>
+      <c r="G56" s="5" t="s">
+        <v>22</v>
+      </c>
+      <c r="H56" s="1">
+        <v>1.08</v>
+      </c>
+      <c r="I56" s="1">
+        <f>Table1[[#This Row],[Qty]]*Table1[[#This Row],[Unit Cost]]</f>
+        <v>1.08</v>
+      </c>
+      <c r="J56" t="s">
+        <v>133</v>
+      </c>
+    </row>
+    <row r="57" spans="1:11" x14ac:dyDescent="0.2">
+      <c r="B57" t="s">
+        <v>124</v>
+      </c>
+      <c r="D57" t="s">
+        <v>134</v>
+      </c>
+      <c r="G57" s="5" t="s">
+        <v>22</v>
+      </c>
+      <c r="I57" s="1">
+        <f>Table1[[#This Row],[Qty]]*Table1[[#This Row],[Unit Cost]]</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="58" spans="1:11" x14ac:dyDescent="0.2">
+      <c r="A58" t="s">
+        <v>42</v>
+      </c>
+      <c r="B58" t="s">
+        <v>135</v>
+      </c>
+      <c r="C58" s="5" t="s">
+        <v>136</v>
+      </c>
+      <c r="D58" t="s">
+        <v>137</v>
+      </c>
+      <c r="E58" t="s">
+        <v>67</v>
+      </c>
+      <c r="F58">
+        <v>1</v>
+      </c>
+      <c r="G58" s="5" t="s">
+        <v>22</v>
+      </c>
+      <c r="H58" s="1">
+        <v>1.49</v>
+      </c>
+      <c r="I58" s="1">
+        <f>Table1[[#This Row],[Qty]]*Table1[[#This Row],[Unit Cost]]</f>
+        <v>1.49</v>
+      </c>
+      <c r="J58" s="4" t="s">
+        <v>138</v>
+      </c>
+    </row>
+    <row r="59" spans="1:11" x14ac:dyDescent="0.2">
+      <c r="A59" t="s">
+        <v>29</v>
+      </c>
+      <c r="B59" t="s">
+        <v>135</v>
+      </c>
+      <c r="C59" s="5" t="s">
+        <v>139</v>
+      </c>
+      <c r="D59" t="s">
+        <v>140</v>
+      </c>
+      <c r="E59" t="s">
+        <v>32</v>
+      </c>
+      <c r="F59">
+        <v>6</v>
+      </c>
+      <c r="G59" s="5" t="s">
+        <v>22</v>
+      </c>
+      <c r="H59" s="1">
+        <f>8.44/100</f>
+        <v>8.4399999999999989E-2</v>
+      </c>
+      <c r="I59" s="1">
+        <f>Table1[[#This Row],[Qty]]*Table1[[#This Row],[Unit Cost]]</f>
+        <v>0.50639999999999996</v>
+      </c>
+      <c r="J59" s="4" t="s">
+        <v>141</v>
+      </c>
+    </row>
+    <row r="60" spans="1:11" x14ac:dyDescent="0.2">
+      <c r="A60" t="s">
+        <v>29</v>
+      </c>
+      <c r="B60" t="s">
+        <v>135</v>
+      </c>
+      <c r="C60" s="5" t="s">
+        <v>90</v>
+      </c>
+      <c r="D60" t="s">
+        <v>142</v>
+      </c>
+      <c r="E60" t="s">
+        <v>32</v>
+      </c>
+      <c r="F60">
+        <v>6</v>
+      </c>
+      <c r="G60" s="5" t="s">
+        <v>22</v>
+      </c>
+      <c r="H60" s="1">
         <f>3.06/100</f>
         <v>3.0600000000000002E-2</v>
       </c>
-      <c r="I42" s="1">
-        <f>Table1[[#This Row],[Qty]]*Table1[[#This Row],[Unit Cost]]</f>
-        <v>3.0600000000000002E-2</v>
-      </c>
-      <c r="J42" s="4" t="s">
-        <v>93</v>
-      </c>
-    </row>
-    <row r="43" spans="1:10" x14ac:dyDescent="0.2">
-      <c r="A43" t="s">
-        <v>94</v>
-      </c>
-      <c r="B43" t="s">
-        <v>94</v>
-      </c>
-      <c r="C43" s="5" t="s">
-        <v>95</v>
-      </c>
-      <c r="D43" t="s">
-        <v>96</v>
-      </c>
-      <c r="E43" t="s">
-        <v>97</v>
-      </c>
-      <c r="F43">
-        <v>1</v>
-      </c>
-      <c r="G43" s="5" t="s">
-        <v>23</v>
-      </c>
-      <c r="H43" s="1">
-        <v>229</v>
-      </c>
-      <c r="I43" s="1">
-        <f>Table1[[#This Row],[Qty]]*Table1[[#This Row],[Unit Cost]]</f>
-        <v>229</v>
-      </c>
-      <c r="J43" s="4" t="s">
-        <v>98</v>
-      </c>
-    </row>
-    <row r="44" spans="1:10" x14ac:dyDescent="0.2">
-      <c r="B44" t="s">
-        <v>94</v>
-      </c>
-      <c r="D44" t="s">
-        <v>99</v>
-      </c>
-      <c r="F44">
-        <v>1</v>
-      </c>
-      <c r="G44" s="5" t="s">
-        <v>23</v>
-      </c>
-      <c r="I44" s="1">
-        <f>Table1[[#This Row],[Qty]]*Table1[[#This Row],[Unit Cost]]</f>
-        <v>0</v>
-      </c>
-      <c r="J44" s="4"/>
-    </row>
-    <row r="45" spans="1:10" x14ac:dyDescent="0.2">
-      <c r="A45" t="s">
-        <v>30</v>
-      </c>
-      <c r="B45" t="s">
-        <v>94</v>
-      </c>
-      <c r="C45" s="5" t="s">
-        <v>100</v>
-      </c>
-      <c r="D45" t="s">
-        <v>101</v>
-      </c>
-      <c r="E45" t="s">
-        <v>33</v>
-      </c>
-      <c r="F45">
-        <v>6</v>
-      </c>
-      <c r="G45" s="5" t="s">
-        <v>23</v>
-      </c>
-      <c r="H45" s="1">
-        <f>17.63/100</f>
-        <v>0.17629999999999998</v>
-      </c>
-      <c r="I45" s="1">
-        <f>Table1[[#This Row],[Qty]]*Table1[[#This Row],[Unit Cost]]</f>
-        <v>1.0577999999999999</v>
-      </c>
-      <c r="J45" s="4" t="s">
-        <v>102</v>
-      </c>
-    </row>
-    <row r="46" spans="1:10" x14ac:dyDescent="0.2">
-      <c r="A46" t="s">
-        <v>30</v>
-      </c>
-      <c r="B46" t="s">
-        <v>94</v>
-      </c>
-      <c r="C46" s="5" t="s">
-        <v>103</v>
-      </c>
-      <c r="D46" t="s">
-        <v>104</v>
-      </c>
-      <c r="E46" t="s">
-        <v>33</v>
-      </c>
-      <c r="F46">
-        <v>6</v>
-      </c>
-      <c r="G46" s="5" t="s">
-        <v>23</v>
-      </c>
-      <c r="H46" s="1">
-        <f>3/100</f>
-        <v>0.03</v>
-      </c>
-      <c r="I46" s="1">
-        <f>Table1[[#This Row],[Qty]]*Table1[[#This Row],[Unit Cost]]</f>
-        <v>0.18</v>
-      </c>
-      <c r="J46" s="4" t="s">
-        <v>105</v>
-      </c>
-    </row>
-    <row r="47" spans="1:10" x14ac:dyDescent="0.2">
-      <c r="B47" t="s">
-        <v>94</v>
-      </c>
-      <c r="D47" t="s">
-        <v>106</v>
-      </c>
-      <c r="F47">
-        <v>1</v>
-      </c>
-      <c r="G47" s="5" t="s">
-        <v>23</v>
-      </c>
-      <c r="H47" s="1">
-        <v>5</v>
-      </c>
-      <c r="I47" s="1">
-        <f>Table1[[#This Row],[Qty]]*Table1[[#This Row],[Unit Cost]]</f>
-        <v>5</v>
-      </c>
-      <c r="J47" s="4" t="s">
-        <v>107</v>
-      </c>
-    </row>
-    <row r="48" spans="1:10" x14ac:dyDescent="0.2">
-      <c r="A48" t="s">
-        <v>43</v>
-      </c>
-      <c r="B48" t="s">
-        <v>108</v>
-      </c>
-      <c r="D48" t="s">
-        <v>109</v>
-      </c>
-      <c r="E48" t="s">
-        <v>110</v>
-      </c>
-      <c r="F48">
-        <v>1</v>
-      </c>
-      <c r="G48" s="5" t="s">
-        <v>23</v>
-      </c>
-      <c r="H48" s="1">
-        <v>0</v>
-      </c>
-      <c r="I48" s="1">
-        <f>Table1[[#This Row],[Qty]]*Table1[[#This Row],[Unit Cost]]</f>
-        <v>0</v>
-      </c>
-      <c r="J48" s="6" t="s">
-        <v>111</v>
-      </c>
-    </row>
-    <row r="49" spans="1:11" x14ac:dyDescent="0.2">
-      <c r="A49" t="s">
-        <v>30</v>
-      </c>
-      <c r="B49" t="s">
-        <v>108</v>
-      </c>
-      <c r="D49" t="s">
-        <v>112</v>
-      </c>
-      <c r="E49" t="s">
-        <v>33</v>
-      </c>
-      <c r="F49">
-        <v>2</v>
-      </c>
-      <c r="G49" s="5" t="s">
-        <v>23</v>
-      </c>
-      <c r="H49" s="1">
-        <f>11.38/50</f>
-        <v>0.22760000000000002</v>
-      </c>
-      <c r="I49" s="1">
-        <f>Table1[[#This Row],[Qty]]*Table1[[#This Row],[Unit Cost]]</f>
-        <v>0.45520000000000005</v>
-      </c>
-      <c r="J49" s="4" t="s">
-        <v>113</v>
-      </c>
-    </row>
-    <row r="50" spans="1:11" x14ac:dyDescent="0.2">
-      <c r="B50" t="s">
-        <v>108</v>
-      </c>
-      <c r="D50" t="s">
-        <v>114</v>
-      </c>
-      <c r="E50" t="s">
-        <v>115</v>
-      </c>
-      <c r="F50">
-        <v>1</v>
-      </c>
-      <c r="G50" s="5" t="s">
-        <v>23</v>
-      </c>
-      <c r="I50" s="1">
-        <f>Table1[[#This Row],[Qty]]*Table1[[#This Row],[Unit Cost]]</f>
-        <v>0</v>
-      </c>
-      <c r="J50" s="4" t="s">
-        <v>116</v>
-      </c>
-    </row>
-    <row r="51" spans="1:11" x14ac:dyDescent="0.2">
-      <c r="B51" t="s">
-        <v>108</v>
-      </c>
-      <c r="D51" t="s">
-        <v>117</v>
-      </c>
-      <c r="F51">
-        <v>1</v>
-      </c>
-      <c r="G51" s="5" t="s">
-        <v>23</v>
-      </c>
-      <c r="I51" s="1">
-        <f>Table1[[#This Row],[Qty]]*Table1[[#This Row],[Unit Cost]]</f>
-        <v>0</v>
-      </c>
-      <c r="J51" s="6" t="s">
-        <v>118</v>
-      </c>
-    </row>
-    <row r="52" spans="1:11" x14ac:dyDescent="0.2">
-      <c r="A52" t="s">
-        <v>30</v>
-      </c>
-      <c r="B52" t="s">
-        <v>108</v>
-      </c>
-      <c r="C52" s="5" t="s">
-        <v>119</v>
-      </c>
-      <c r="D52" t="s">
-        <v>120</v>
-      </c>
-      <c r="E52" t="s">
-        <v>33</v>
-      </c>
-      <c r="F52">
-        <v>3</v>
-      </c>
-      <c r="G52" s="5" t="s">
-        <v>23</v>
-      </c>
-      <c r="H52" s="1">
-        <f>7.57/100</f>
-        <v>7.5700000000000003E-2</v>
-      </c>
-      <c r="I52" s="1">
-        <f>Table1[[#This Row],[Qty]]*Table1[[#This Row],[Unit Cost]]</f>
-        <v>0.22710000000000002</v>
-      </c>
-      <c r="J52" t="s">
-        <v>121</v>
-      </c>
-    </row>
-    <row r="53" spans="1:11" x14ac:dyDescent="0.2">
-      <c r="A53" t="s">
-        <v>30</v>
-      </c>
-      <c r="B53" t="s">
-        <v>108</v>
-      </c>
-      <c r="C53" s="5" t="s">
-        <v>122</v>
-      </c>
-      <c r="D53" t="s">
-        <v>123</v>
-      </c>
-      <c r="E53" t="s">
-        <v>33</v>
-      </c>
-      <c r="F53">
-        <v>3</v>
-      </c>
-      <c r="G53" s="5" t="s">
-        <v>23</v>
-      </c>
-      <c r="H53" s="1">
-        <f>7.41/100</f>
-        <v>7.4099999999999999E-2</v>
-      </c>
-      <c r="I53" s="1">
-        <f>Table1[[#This Row],[Qty]]*Table1[[#This Row],[Unit Cost]]</f>
-        <v>0.2223</v>
-      </c>
-      <c r="J53" s="4" t="s">
-        <v>124</v>
-      </c>
-    </row>
-    <row r="54" spans="1:11" x14ac:dyDescent="0.2">
-      <c r="B54" t="s">
-        <v>108</v>
-      </c>
-      <c r="C54" s="5" t="s">
-        <v>151</v>
-      </c>
-      <c r="D54" t="s">
-        <v>150</v>
-      </c>
-      <c r="E54" t="s">
-        <v>33</v>
-      </c>
-      <c r="F54">
-        <v>1</v>
-      </c>
-      <c r="G54" s="5" t="s">
-        <v>23</v>
-      </c>
-      <c r="H54" s="7">
-        <v>4.95</v>
-      </c>
-      <c r="I54" s="7">
-        <f>Table1[[#This Row],[Qty]]*Table1[[#This Row],[Unit Cost]]</f>
-        <v>4.95</v>
-      </c>
-      <c r="J54" s="4" t="s">
-        <v>149</v>
-      </c>
-    </row>
-    <row r="55" spans="1:11" x14ac:dyDescent="0.2">
-      <c r="B55" t="s">
-        <v>125</v>
-      </c>
-      <c r="D55" t="s">
-        <v>126</v>
-      </c>
-      <c r="G55" s="5" t="s">
-        <v>23</v>
-      </c>
-      <c r="I55" s="1">
-        <f>Table1[[#This Row],[Qty]]*Table1[[#This Row],[Unit Cost]]</f>
-        <v>0</v>
-      </c>
-      <c r="J55" t="s">
-        <v>127</v>
-      </c>
-    </row>
-    <row r="56" spans="1:11" x14ac:dyDescent="0.2">
-      <c r="B56" t="s">
-        <v>125</v>
-      </c>
-      <c r="D56" t="s">
-        <v>128</v>
-      </c>
-      <c r="F56">
-        <v>1</v>
-      </c>
-      <c r="G56" s="5" t="s">
-        <v>23</v>
-      </c>
-      <c r="I56" s="1">
-        <f>Table1[[#This Row],[Qty]]*Table1[[#This Row],[Unit Cost]]</f>
-        <v>0</v>
-      </c>
-      <c r="J56" s="6" t="s">
-        <v>129</v>
-      </c>
-      <c r="K56" t="s">
-        <v>130</v>
-      </c>
-    </row>
-    <row r="57" spans="1:11" x14ac:dyDescent="0.2">
-      <c r="B57" t="s">
-        <v>125</v>
-      </c>
-      <c r="C57" s="5" t="s">
-        <v>131</v>
-      </c>
-      <c r="D57" t="s">
-        <v>132</v>
-      </c>
-      <c r="E57" t="s">
-        <v>133</v>
-      </c>
-      <c r="F57">
-        <v>1</v>
-      </c>
-      <c r="G57" s="5" t="s">
-        <v>23</v>
-      </c>
-      <c r="H57" s="1">
-        <v>1.08</v>
-      </c>
-      <c r="I57" s="1">
-        <f>Table1[[#This Row],[Qty]]*Table1[[#This Row],[Unit Cost]]</f>
-        <v>1.08</v>
-      </c>
-      <c r="J57" t="s">
-        <v>134</v>
-      </c>
-    </row>
-    <row r="58" spans="1:11" x14ac:dyDescent="0.2">
-      <c r="B58" t="s">
-        <v>125</v>
-      </c>
-      <c r="D58" t="s">
-        <v>135</v>
-      </c>
-      <c r="G58" s="5" t="s">
-        <v>23</v>
-      </c>
-      <c r="I58" s="1">
-        <f>Table1[[#This Row],[Qty]]*Table1[[#This Row],[Unit Cost]]</f>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="59" spans="1:11" x14ac:dyDescent="0.2">
-      <c r="A59" t="s">
-        <v>43</v>
-      </c>
-      <c r="B59" t="s">
-        <v>136</v>
-      </c>
-      <c r="C59" s="5" t="s">
-        <v>137</v>
-      </c>
-      <c r="D59" t="s">
-        <v>138</v>
-      </c>
-      <c r="E59" t="s">
-        <v>68</v>
-      </c>
-      <c r="F59">
-        <v>1</v>
-      </c>
-      <c r="G59" s="5" t="s">
-        <v>23</v>
-      </c>
-      <c r="H59" s="1">
-        <v>1.49</v>
-      </c>
-      <c r="I59" s="1">
-        <f>Table1[[#This Row],[Qty]]*Table1[[#This Row],[Unit Cost]]</f>
-        <v>1.49</v>
-      </c>
-      <c r="J59" s="4" t="s">
-        <v>139</v>
-      </c>
-    </row>
-    <row r="60" spans="1:11" x14ac:dyDescent="0.2">
-      <c r="A60" t="s">
-        <v>30</v>
-      </c>
-      <c r="B60" t="s">
-        <v>136</v>
-      </c>
-      <c r="C60" s="5" t="s">
-        <v>140</v>
-      </c>
-      <c r="D60" t="s">
-        <v>141</v>
-      </c>
-      <c r="E60" t="s">
-        <v>33</v>
-      </c>
-      <c r="F60">
-        <v>6</v>
-      </c>
-      <c r="G60" s="5" t="s">
-        <v>23</v>
-      </c>
-      <c r="H60" s="1">
-        <f>8.44/100</f>
-        <v>8.4399999999999989E-2</v>
-      </c>
       <c r="I60" s="1">
         <f>Table1[[#This Row],[Qty]]*Table1[[#This Row],[Unit Cost]]</f>
-        <v>0.50639999999999996</v>
-      </c>
-      <c r="J60" s="4" t="s">
-        <v>142</v>
+        <v>0.18360000000000001</v>
       </c>
     </row>
     <row r="61" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A61" t="s">
-        <v>30</v>
+        <v>42</v>
       </c>
       <c r="B61" t="s">
-        <v>136</v>
-      </c>
-      <c r="C61" s="5" t="s">
-        <v>91</v>
+        <v>135</v>
       </c>
       <c r="D61" t="s">
         <v>143</v>
       </c>
-      <c r="E61" t="s">
-        <v>33</v>
-      </c>
-      <c r="F61">
-        <v>6</v>
-      </c>
       <c r="G61" s="5" t="s">
-        <v>23</v>
-      </c>
-      <c r="H61" s="1">
-        <f>3.06/100</f>
-        <v>3.0600000000000002E-2</v>
+        <v>22</v>
       </c>
       <c r="I61" s="1">
         <f>Table1[[#This Row],[Qty]]*Table1[[#This Row],[Unit Cost]]</f>
-        <v>0.18360000000000001</v>
+        <v>0</v>
       </c>
     </row>
     <row r="62" spans="1:11" x14ac:dyDescent="0.2">
-      <c r="A62" t="s">
-        <v>43</v>
-      </c>
       <c r="B62" t="s">
-        <v>136</v>
+        <v>135</v>
+      </c>
+      <c r="C62" s="5" t="s">
+        <v>144</v>
       </c>
       <c r="D62" t="s">
-        <v>144</v>
+        <v>145</v>
+      </c>
+      <c r="E62" t="s">
+        <v>32</v>
+      </c>
+      <c r="F62">
+        <v>0.5</v>
       </c>
       <c r="G62" s="5" t="s">
-        <v>23</v>
+        <v>22</v>
+      </c>
+      <c r="H62" s="1">
+        <v>9.65</v>
       </c>
       <c r="I62" s="1">
         <f>Table1[[#This Row],[Qty]]*Table1[[#This Row],[Unit Cost]]</f>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="63" spans="1:11" x14ac:dyDescent="0.2">
-      <c r="B63" t="s">
-        <v>136</v>
-      </c>
-      <c r="C63" s="5" t="s">
-        <v>145</v>
-      </c>
-      <c r="D63" t="s">
+        <v>4.8250000000000002</v>
+      </c>
+      <c r="J62" t="s">
         <v>146</v>
       </c>
-      <c r="E63" t="s">
-        <v>33</v>
-      </c>
-      <c r="F63">
-        <v>0.5</v>
-      </c>
-      <c r="G63" s="5" t="s">
-        <v>23</v>
-      </c>
-      <c r="H63" s="1">
-        <v>9.65</v>
-      </c>
-      <c r="I63" s="1">
-        <f>Table1[[#This Row],[Qty]]*Table1[[#This Row],[Unit Cost]]</f>
-        <v>4.8250000000000002</v>
-      </c>
-      <c r="J63" t="s">
+      <c r="K62" t="s">
         <v>147</v>
-      </c>
-      <c r="K63" t="s">
-        <v>148</v>
       </c>
     </row>
   </sheetData>
   <hyperlinks>
-    <hyperlink ref="J11" r:id="rId1" xr:uid="{00000000-0004-0000-0000-000000000000}"/>
-    <hyperlink ref="J12" r:id="rId2" xr:uid="{00000000-0004-0000-0000-000001000000}"/>
-    <hyperlink ref="J13" r:id="rId3" xr:uid="{00000000-0004-0000-0000-000002000000}"/>
-    <hyperlink ref="J15" r:id="rId4" xr:uid="{00000000-0004-0000-0000-000003000000}"/>
-    <hyperlink ref="J16" r:id="rId5" xr:uid="{00000000-0004-0000-0000-000004000000}"/>
-    <hyperlink ref="J19" r:id="rId6" xr:uid="{00000000-0004-0000-0000-000005000000}"/>
-    <hyperlink ref="J20" r:id="rId7" xr:uid="{00000000-0004-0000-0000-000006000000}"/>
-    <hyperlink ref="J21" r:id="rId8" xr:uid="{00000000-0004-0000-0000-000007000000}"/>
-    <hyperlink ref="J22" r:id="rId9" xr:uid="{00000000-0004-0000-0000-000008000000}"/>
-    <hyperlink ref="J23" r:id="rId10" xr:uid="{00000000-0004-0000-0000-000009000000}"/>
-    <hyperlink ref="J24" r:id="rId11" xr:uid="{00000000-0004-0000-0000-00000A000000}"/>
-    <hyperlink ref="J25" r:id="rId12" xr:uid="{00000000-0004-0000-0000-00000B000000}"/>
-    <hyperlink ref="J29" r:id="rId13" xr:uid="{00000000-0004-0000-0000-00000C000000}"/>
-    <hyperlink ref="J38" r:id="rId14" xr:uid="{00000000-0004-0000-0000-00000D000000}"/>
-    <hyperlink ref="J39" r:id="rId15" xr:uid="{00000000-0004-0000-0000-00000E000000}"/>
-    <hyperlink ref="J41" r:id="rId16" xr:uid="{00000000-0004-0000-0000-00000F000000}"/>
-    <hyperlink ref="J42" r:id="rId17" xr:uid="{00000000-0004-0000-0000-000010000000}"/>
-    <hyperlink ref="J43" r:id="rId18" xr:uid="{00000000-0004-0000-0000-000011000000}"/>
-    <hyperlink ref="J45" r:id="rId19" xr:uid="{00000000-0004-0000-0000-000012000000}"/>
-    <hyperlink ref="J46" r:id="rId20" xr:uid="{00000000-0004-0000-0000-000013000000}"/>
-    <hyperlink ref="J47" r:id="rId21" xr:uid="{00000000-0004-0000-0000-000014000000}"/>
-    <hyperlink ref="J48" r:id="rId22" xr:uid="{00000000-0004-0000-0000-000015000000}"/>
-    <hyperlink ref="J49" r:id="rId23" xr:uid="{00000000-0004-0000-0000-000016000000}"/>
-    <hyperlink ref="J51" r:id="rId24" xr:uid="{00000000-0004-0000-0000-000017000000}"/>
-    <hyperlink ref="J53" r:id="rId25" xr:uid="{00000000-0004-0000-0000-000018000000}"/>
-    <hyperlink ref="J56" r:id="rId26" xr:uid="{00000000-0004-0000-0000-000019000000}"/>
-    <hyperlink ref="J59" r:id="rId27" xr:uid="{00000000-0004-0000-0000-00001A000000}"/>
-    <hyperlink ref="J60" r:id="rId28" xr:uid="{00000000-0004-0000-0000-00001B000000}"/>
-    <hyperlink ref="J54" r:id="rId29" xr:uid="{E0F0E1BC-BF9F-EC41-B567-F34F9756DE29}"/>
+    <hyperlink ref="J10" r:id="rId1" xr:uid="{00000000-0004-0000-0000-000000000000}"/>
+    <hyperlink ref="J11" r:id="rId2" xr:uid="{00000000-0004-0000-0000-000001000000}"/>
+    <hyperlink ref="J12" r:id="rId3" xr:uid="{00000000-0004-0000-0000-000002000000}"/>
+    <hyperlink ref="J14" r:id="rId4" xr:uid="{00000000-0004-0000-0000-000003000000}"/>
+    <hyperlink ref="J15" r:id="rId5" xr:uid="{00000000-0004-0000-0000-000004000000}"/>
+    <hyperlink ref="J18" r:id="rId6" xr:uid="{00000000-0004-0000-0000-000005000000}"/>
+    <hyperlink ref="J19" r:id="rId7" xr:uid="{00000000-0004-0000-0000-000006000000}"/>
+    <hyperlink ref="J20" r:id="rId8" xr:uid="{00000000-0004-0000-0000-000007000000}"/>
+    <hyperlink ref="J21" r:id="rId9" xr:uid="{00000000-0004-0000-0000-000008000000}"/>
+    <hyperlink ref="J22" r:id="rId10" xr:uid="{00000000-0004-0000-0000-000009000000}"/>
+    <hyperlink ref="J23" r:id="rId11" xr:uid="{00000000-0004-0000-0000-00000A000000}"/>
+    <hyperlink ref="J24" r:id="rId12" xr:uid="{00000000-0004-0000-0000-00000B000000}"/>
+    <hyperlink ref="J28" r:id="rId13" xr:uid="{00000000-0004-0000-0000-00000C000000}"/>
+    <hyperlink ref="J37" r:id="rId14" xr:uid="{00000000-0004-0000-0000-00000D000000}"/>
+    <hyperlink ref="J38" r:id="rId15" xr:uid="{00000000-0004-0000-0000-00000E000000}"/>
+    <hyperlink ref="J40" r:id="rId16" xr:uid="{00000000-0004-0000-0000-00000F000000}"/>
+    <hyperlink ref="J41" r:id="rId17" xr:uid="{00000000-0004-0000-0000-000010000000}"/>
+    <hyperlink ref="J42" r:id="rId18" xr:uid="{00000000-0004-0000-0000-000011000000}"/>
+    <hyperlink ref="J44" r:id="rId19" xr:uid="{00000000-0004-0000-0000-000012000000}"/>
+    <hyperlink ref="J45" r:id="rId20" xr:uid="{00000000-0004-0000-0000-000013000000}"/>
+    <hyperlink ref="J46" r:id="rId21" xr:uid="{00000000-0004-0000-0000-000014000000}"/>
+    <hyperlink ref="J47" r:id="rId22" xr:uid="{00000000-0004-0000-0000-000015000000}"/>
+    <hyperlink ref="J48" r:id="rId23" xr:uid="{00000000-0004-0000-0000-000016000000}"/>
+    <hyperlink ref="J50" r:id="rId24" xr:uid="{00000000-0004-0000-0000-000017000000}"/>
+    <hyperlink ref="J52" r:id="rId25" xr:uid="{00000000-0004-0000-0000-000018000000}"/>
+    <hyperlink ref="J55" r:id="rId26" xr:uid="{00000000-0004-0000-0000-000019000000}"/>
+    <hyperlink ref="J58" r:id="rId27" xr:uid="{00000000-0004-0000-0000-00001A000000}"/>
+    <hyperlink ref="J59" r:id="rId28" xr:uid="{00000000-0004-0000-0000-00001B000000}"/>
+    <hyperlink ref="J53" r:id="rId29" xr:uid="{E0F0E1BC-BF9F-EC41-B567-F34F9756DE29}"/>
   </hyperlinks>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <tableParts count="1">

--- a/Walking-Setup/G6-Integration-Bill-of-Materials.xlsx
+++ b/Walking-Setup/G6-Integration-Bill-of-Materials.xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="10713"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="10719"/>
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/lehenbaueri/Documents/GitHub/Fly-Lab-Gear/Walking-Setup/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{6A04A191-27BF-7F49-95A7-8C52F28F758E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{D3E5C8D6-42D6-5142-A83B-334A4CBC9E0F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="1640" yWindow="660" windowWidth="27460" windowHeight="18980" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -33,7 +33,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="306" uniqueCount="151">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="307" uniqueCount="152">
   <si>
     <t>Name</t>
   </si>
@@ -275,9 +275,6 @@
     <t>Fly Holder</t>
   </si>
   <si>
-    <t>Micromanipulator</t>
-  </si>
-  <si>
     <t>Micromanipulator adapter plate</t>
   </si>
   <si>
@@ -486,6 +483,12 @@
   </si>
   <si>
     <t>5779K108</t>
+  </si>
+  <si>
+    <t>LD40 Micromanipulator</t>
+  </si>
+  <si>
+    <t>../Miscellaneous/Adapter_metric-imperial_manipulator/production/LD40_Adapter_3in.step</t>
   </si>
 </sst>
 </file>
@@ -1733,7 +1736,7 @@
         <v>79</v>
       </c>
       <c r="D35" t="s">
-        <v>80</v>
+        <v>150</v>
       </c>
       <c r="F35">
         <v>1</v>
@@ -1747,6 +1750,9 @@
       <c r="I35" s="1">
         <f>Table1[[#This Row],[Qty]]*Table1[[#This Row],[Unit Cost]]</f>
         <v>80</v>
+      </c>
+      <c r="J35" t="s">
+        <v>151</v>
       </c>
     </row>
     <row r="36" spans="1:10" x14ac:dyDescent="0.2">
@@ -1754,7 +1760,7 @@
         <v>79</v>
       </c>
       <c r="D36" t="s">
-        <v>81</v>
+        <v>80</v>
       </c>
       <c r="E36" t="s">
         <v>39</v>
@@ -1775,7 +1781,7 @@
         <v>79</v>
       </c>
       <c r="D37" t="s">
-        <v>82</v>
+        <v>81</v>
       </c>
       <c r="E37" t="s">
         <v>39</v>
@@ -1791,7 +1797,7 @@
         <v>0</v>
       </c>
       <c r="J37" s="6" t="s">
-        <v>83</v>
+        <v>82</v>
       </c>
     </row>
     <row r="38" spans="1:10" x14ac:dyDescent="0.2">
@@ -1799,7 +1805,7 @@
         <v>79</v>
       </c>
       <c r="D38" t="s">
-        <v>84</v>
+        <v>83</v>
       </c>
       <c r="E38" t="s">
         <v>39</v>
@@ -1815,7 +1821,7 @@
         <v>0</v>
       </c>
       <c r="J38" s="6" t="s">
-        <v>85</v>
+        <v>84</v>
       </c>
     </row>
     <row r="39" spans="1:10" x14ac:dyDescent="0.2">
@@ -1823,7 +1829,7 @@
         <v>79</v>
       </c>
       <c r="D39" t="s">
-        <v>86</v>
+        <v>85</v>
       </c>
       <c r="F39">
         <v>1</v>
@@ -1844,10 +1850,10 @@
         <v>79</v>
       </c>
       <c r="C40" s="5" t="s">
+        <v>86</v>
+      </c>
+      <c r="D40" t="s">
         <v>87</v>
-      </c>
-      <c r="D40" t="s">
-        <v>88</v>
       </c>
       <c r="E40" t="s">
         <v>32</v>
@@ -1867,7 +1873,7 @@
         <v>0.88900000000000001</v>
       </c>
       <c r="J40" s="4" t="s">
-        <v>89</v>
+        <v>88</v>
       </c>
     </row>
     <row r="41" spans="1:10" x14ac:dyDescent="0.2">
@@ -1878,10 +1884,10 @@
         <v>79</v>
       </c>
       <c r="C41" s="5" t="s">
+        <v>89</v>
+      </c>
+      <c r="D41" t="s">
         <v>90</v>
-      </c>
-      <c r="D41" t="s">
-        <v>91</v>
       </c>
       <c r="E41" t="s">
         <v>32</v>
@@ -1901,24 +1907,24 @@
         <v>3.0600000000000002E-2</v>
       </c>
       <c r="J41" s="4" t="s">
-        <v>92</v>
+        <v>91</v>
       </c>
     </row>
     <row r="42" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A42" t="s">
+        <v>92</v>
+      </c>
+      <c r="B42" t="s">
+        <v>92</v>
+      </c>
+      <c r="C42" s="5" t="s">
         <v>93</v>
       </c>
-      <c r="B42" t="s">
-        <v>93</v>
-      </c>
-      <c r="C42" s="5" t="s">
+      <c r="D42" t="s">
         <v>94</v>
       </c>
-      <c r="D42" t="s">
+      <c r="E42" t="s">
         <v>95</v>
-      </c>
-      <c r="E42" t="s">
-        <v>96</v>
       </c>
       <c r="F42">
         <v>1</v>
@@ -1934,15 +1940,15 @@
         <v>229</v>
       </c>
       <c r="J42" s="4" t="s">
-        <v>97</v>
+        <v>96</v>
       </c>
     </row>
     <row r="43" spans="1:10" x14ac:dyDescent="0.2">
       <c r="B43" t="s">
-        <v>93</v>
+        <v>92</v>
       </c>
       <c r="D43" t="s">
-        <v>98</v>
+        <v>97</v>
       </c>
       <c r="F43">
         <v>1</v>
@@ -1961,13 +1967,13 @@
         <v>29</v>
       </c>
       <c r="B44" t="s">
-        <v>93</v>
+        <v>92</v>
       </c>
       <c r="C44" s="5" t="s">
+        <v>98</v>
+      </c>
+      <c r="D44" t="s">
         <v>99</v>
-      </c>
-      <c r="D44" t="s">
-        <v>100</v>
       </c>
       <c r="E44" t="s">
         <v>32</v>
@@ -1987,7 +1993,7 @@
         <v>1.0577999999999999</v>
       </c>
       <c r="J44" s="4" t="s">
-        <v>101</v>
+        <v>100</v>
       </c>
     </row>
     <row r="45" spans="1:10" x14ac:dyDescent="0.2">
@@ -1995,13 +2001,13 @@
         <v>29</v>
       </c>
       <c r="B45" t="s">
-        <v>93</v>
+        <v>92</v>
       </c>
       <c r="C45" s="5" t="s">
+        <v>101</v>
+      </c>
+      <c r="D45" t="s">
         <v>102</v>
-      </c>
-      <c r="D45" t="s">
-        <v>103</v>
       </c>
       <c r="E45" t="s">
         <v>32</v>
@@ -2021,15 +2027,15 @@
         <v>0.18</v>
       </c>
       <c r="J45" s="4" t="s">
-        <v>104</v>
+        <v>103</v>
       </c>
     </row>
     <row r="46" spans="1:10" x14ac:dyDescent="0.2">
       <c r="B46" t="s">
-        <v>93</v>
+        <v>92</v>
       </c>
       <c r="D46" t="s">
-        <v>105</v>
+        <v>104</v>
       </c>
       <c r="F46">
         <v>1</v>
@@ -2045,7 +2051,7 @@
         <v>5</v>
       </c>
       <c r="J46" s="4" t="s">
-        <v>106</v>
+        <v>105</v>
       </c>
     </row>
     <row r="47" spans="1:10" x14ac:dyDescent="0.2">
@@ -2053,13 +2059,13 @@
         <v>42</v>
       </c>
       <c r="B47" t="s">
+        <v>106</v>
+      </c>
+      <c r="D47" t="s">
         <v>107</v>
       </c>
-      <c r="D47" t="s">
+      <c r="E47" t="s">
         <v>108</v>
-      </c>
-      <c r="E47" t="s">
-        <v>109</v>
       </c>
       <c r="F47">
         <v>1</v>
@@ -2075,7 +2081,7 @@
         <v>0</v>
       </c>
       <c r="J47" s="6" t="s">
-        <v>110</v>
+        <v>109</v>
       </c>
     </row>
     <row r="48" spans="1:10" x14ac:dyDescent="0.2">
@@ -2083,10 +2089,10 @@
         <v>29</v>
       </c>
       <c r="B48" t="s">
-        <v>107</v>
+        <v>106</v>
       </c>
       <c r="D48" t="s">
-        <v>111</v>
+        <v>110</v>
       </c>
       <c r="E48" t="s">
         <v>32</v>
@@ -2106,52 +2112,52 @@
         <v>0.45520000000000005</v>
       </c>
       <c r="J48" s="4" t="s">
-        <v>112</v>
+        <v>111</v>
       </c>
     </row>
     <row r="49" spans="1:11" x14ac:dyDescent="0.2">
       <c r="B49" t="s">
-        <v>107</v>
+        <v>106</v>
       </c>
       <c r="D49" t="s">
+        <v>112</v>
+      </c>
+      <c r="E49" t="s">
         <v>113</v>
       </c>
-      <c r="E49" t="s">
+      <c r="F49">
+        <v>1</v>
+      </c>
+      <c r="G49" s="5" t="s">
+        <v>22</v>
+      </c>
+      <c r="I49" s="1">
+        <f>Table1[[#This Row],[Qty]]*Table1[[#This Row],[Unit Cost]]</f>
+        <v>0</v>
+      </c>
+      <c r="J49" s="4" t="s">
         <v>114</v>
-      </c>
-      <c r="F49">
-        <v>1</v>
-      </c>
-      <c r="G49" s="5" t="s">
-        <v>22</v>
-      </c>
-      <c r="I49" s="1">
-        <f>Table1[[#This Row],[Qty]]*Table1[[#This Row],[Unit Cost]]</f>
-        <v>0</v>
-      </c>
-      <c r="J49" s="4" t="s">
-        <v>115</v>
       </c>
     </row>
     <row r="50" spans="1:11" x14ac:dyDescent="0.2">
       <c r="B50" t="s">
-        <v>107</v>
+        <v>106</v>
       </c>
       <c r="D50" t="s">
+        <v>115</v>
+      </c>
+      <c r="F50">
+        <v>1</v>
+      </c>
+      <c r="G50" s="5" t="s">
+        <v>22</v>
+      </c>
+      <c r="I50" s="1">
+        <f>Table1[[#This Row],[Qty]]*Table1[[#This Row],[Unit Cost]]</f>
+        <v>0</v>
+      </c>
+      <c r="J50" s="6" t="s">
         <v>116</v>
-      </c>
-      <c r="F50">
-        <v>1</v>
-      </c>
-      <c r="G50" s="5" t="s">
-        <v>22</v>
-      </c>
-      <c r="I50" s="1">
-        <f>Table1[[#This Row],[Qty]]*Table1[[#This Row],[Unit Cost]]</f>
-        <v>0</v>
-      </c>
-      <c r="J50" s="6" t="s">
-        <v>117</v>
       </c>
     </row>
     <row r="51" spans="1:11" x14ac:dyDescent="0.2">
@@ -2159,13 +2165,13 @@
         <v>29</v>
       </c>
       <c r="B51" t="s">
-        <v>107</v>
+        <v>106</v>
       </c>
       <c r="C51" s="5" t="s">
+        <v>117</v>
+      </c>
+      <c r="D51" t="s">
         <v>118</v>
-      </c>
-      <c r="D51" t="s">
-        <v>119</v>
       </c>
       <c r="E51" t="s">
         <v>32</v>
@@ -2185,7 +2191,7 @@
         <v>0.22710000000000002</v>
       </c>
       <c r="J51" t="s">
-        <v>120</v>
+        <v>119</v>
       </c>
     </row>
     <row r="52" spans="1:11" x14ac:dyDescent="0.2">
@@ -2193,13 +2199,13 @@
         <v>29</v>
       </c>
       <c r="B52" t="s">
-        <v>107</v>
+        <v>106</v>
       </c>
       <c r="C52" s="5" t="s">
+        <v>120</v>
+      </c>
+      <c r="D52" t="s">
         <v>121</v>
-      </c>
-      <c r="D52" t="s">
-        <v>122</v>
       </c>
       <c r="E52" t="s">
         <v>32</v>
@@ -2219,18 +2225,18 @@
         <v>0.2223</v>
       </c>
       <c r="J52" s="4" t="s">
-        <v>123</v>
+        <v>122</v>
       </c>
     </row>
     <row r="53" spans="1:11" x14ac:dyDescent="0.2">
       <c r="B53" t="s">
-        <v>107</v>
+        <v>106</v>
       </c>
       <c r="C53" s="5" t="s">
-        <v>150</v>
+        <v>149</v>
       </c>
       <c r="D53" t="s">
-        <v>149</v>
+        <v>148</v>
       </c>
       <c r="E53" t="s">
         <v>32</v>
@@ -2249,63 +2255,63 @@
         <v>4.95</v>
       </c>
       <c r="J53" s="4" t="s">
-        <v>148</v>
+        <v>147</v>
       </c>
     </row>
     <row r="54" spans="1:11" x14ac:dyDescent="0.2">
       <c r="B54" t="s">
+        <v>123</v>
+      </c>
+      <c r="D54" t="s">
         <v>124</v>
       </c>
-      <c r="D54" t="s">
+      <c r="G54" s="5" t="s">
+        <v>22</v>
+      </c>
+      <c r="I54" s="1">
+        <f>Table1[[#This Row],[Qty]]*Table1[[#This Row],[Unit Cost]]</f>
+        <v>0</v>
+      </c>
+      <c r="J54" t="s">
         <v>125</v>
-      </c>
-      <c r="G54" s="5" t="s">
-        <v>22</v>
-      </c>
-      <c r="I54" s="1">
-        <f>Table1[[#This Row],[Qty]]*Table1[[#This Row],[Unit Cost]]</f>
-        <v>0</v>
-      </c>
-      <c r="J54" t="s">
-        <v>126</v>
       </c>
     </row>
     <row r="55" spans="1:11" x14ac:dyDescent="0.2">
       <c r="B55" t="s">
-        <v>124</v>
+        <v>123</v>
       </c>
       <c r="D55" t="s">
+        <v>126</v>
+      </c>
+      <c r="F55">
+        <v>1</v>
+      </c>
+      <c r="G55" s="5" t="s">
+        <v>22</v>
+      </c>
+      <c r="I55" s="1">
+        <f>Table1[[#This Row],[Qty]]*Table1[[#This Row],[Unit Cost]]</f>
+        <v>0</v>
+      </c>
+      <c r="J55" s="6" t="s">
         <v>127</v>
       </c>
-      <c r="F55">
-        <v>1</v>
-      </c>
-      <c r="G55" s="5" t="s">
-        <v>22</v>
-      </c>
-      <c r="I55" s="1">
-        <f>Table1[[#This Row],[Qty]]*Table1[[#This Row],[Unit Cost]]</f>
-        <v>0</v>
-      </c>
-      <c r="J55" s="6" t="s">
+      <c r="K55" t="s">
         <v>128</v>
-      </c>
-      <c r="K55" t="s">
-        <v>129</v>
       </c>
     </row>
     <row r="56" spans="1:11" x14ac:dyDescent="0.2">
       <c r="B56" t="s">
-        <v>124</v>
+        <v>123</v>
       </c>
       <c r="C56" s="5" t="s">
+        <v>129</v>
+      </c>
+      <c r="D56" t="s">
         <v>130</v>
       </c>
-      <c r="D56" t="s">
+      <c r="E56" t="s">
         <v>131</v>
-      </c>
-      <c r="E56" t="s">
-        <v>132</v>
       </c>
       <c r="F56">
         <v>1</v>
@@ -2321,15 +2327,15 @@
         <v>1.08</v>
       </c>
       <c r="J56" t="s">
-        <v>133</v>
+        <v>132</v>
       </c>
     </row>
     <row r="57" spans="1:11" x14ac:dyDescent="0.2">
       <c r="B57" t="s">
-        <v>124</v>
+        <v>123</v>
       </c>
       <c r="D57" t="s">
-        <v>134</v>
+        <v>133</v>
       </c>
       <c r="G57" s="5" t="s">
         <v>22</v>
@@ -2344,13 +2350,13 @@
         <v>42</v>
       </c>
       <c r="B58" t="s">
+        <v>134</v>
+      </c>
+      <c r="C58" s="5" t="s">
         <v>135</v>
       </c>
-      <c r="C58" s="5" t="s">
+      <c r="D58" t="s">
         <v>136</v>
-      </c>
-      <c r="D58" t="s">
-        <v>137</v>
       </c>
       <c r="E58" t="s">
         <v>67</v>
@@ -2369,7 +2375,7 @@
         <v>1.49</v>
       </c>
       <c r="J58" s="4" t="s">
-        <v>138</v>
+        <v>137</v>
       </c>
     </row>
     <row r="59" spans="1:11" x14ac:dyDescent="0.2">
@@ -2377,13 +2383,13 @@
         <v>29</v>
       </c>
       <c r="B59" t="s">
-        <v>135</v>
+        <v>134</v>
       </c>
       <c r="C59" s="5" t="s">
+        <v>138</v>
+      </c>
+      <c r="D59" t="s">
         <v>139</v>
-      </c>
-      <c r="D59" t="s">
-        <v>140</v>
       </c>
       <c r="E59" t="s">
         <v>32</v>
@@ -2403,7 +2409,7 @@
         <v>0.50639999999999996</v>
       </c>
       <c r="J59" s="4" t="s">
-        <v>141</v>
+        <v>140</v>
       </c>
     </row>
     <row r="60" spans="1:11" x14ac:dyDescent="0.2">
@@ -2411,13 +2417,13 @@
         <v>29</v>
       </c>
       <c r="B60" t="s">
-        <v>135</v>
+        <v>134</v>
       </c>
       <c r="C60" s="5" t="s">
-        <v>90</v>
+        <v>89</v>
       </c>
       <c r="D60" t="s">
-        <v>142</v>
+        <v>141</v>
       </c>
       <c r="E60" t="s">
         <v>32</v>
@@ -2442,10 +2448,10 @@
         <v>42</v>
       </c>
       <c r="B61" t="s">
-        <v>135</v>
+        <v>134</v>
       </c>
       <c r="D61" t="s">
-        <v>143</v>
+        <v>142</v>
       </c>
       <c r="G61" s="5" t="s">
         <v>22</v>
@@ -2457,13 +2463,13 @@
     </row>
     <row r="62" spans="1:11" x14ac:dyDescent="0.2">
       <c r="B62" t="s">
-        <v>135</v>
+        <v>134</v>
       </c>
       <c r="C62" s="5" t="s">
+        <v>143</v>
+      </c>
+      <c r="D62" t="s">
         <v>144</v>
-      </c>
-      <c r="D62" t="s">
-        <v>145</v>
       </c>
       <c r="E62" t="s">
         <v>32</v>
@@ -2482,10 +2488,10 @@
         <v>4.8250000000000002</v>
       </c>
       <c r="J62" t="s">
+        <v>145</v>
+      </c>
+      <c r="K62" t="s">
         <v>146</v>
-      </c>
-      <c r="K62" t="s">
-        <v>147</v>
       </c>
     </row>
   </sheetData>
